--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U301"/>
+  <dimension ref="A1:U303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29055,6 +29055,205 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>QfJKSBO3jf</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Senior Sales Officer</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>, work experience, or other evidence ) submitted during employment/registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Sales; Excellent communication and interpersonal skills.; Desired Skill; sals; Excellent communication and interpersonal skills.</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can register through Ethiojobs or by sending your application to: cnplcvacancy@gmail.com by Specifying Job position and vacancy number clearly in the subject line of your email. Please also attached the following documents: Updated CV and all supporting documents, Work experience from non Government organizations must be supported by proof of employment tax payment, grade 8 completion certificate and "To whom it may concern letter" from your current employer
+Forgery liability: any falsified documents ( Education, work experience, or other evidence ) submitted during employment/registration will result in legal accountability
+Perks + Benefits
+Fuel
+Housing
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/QfJKSBO3jf-senior-sales-officer</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>15 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:45:35 UTC</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ozf3ombEhD</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Social Workers – Child Protection (CP) &amp; Gender-Based Violence (GBV)</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HELP GENERATION</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Afar</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Psychology, Social Work, Gender Studies, Law</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants who meet the above requirements are invited to submit their updated CV and a cover letter through Ethiojobs by clicking the "Apply" button within the specified timeframe. Please ensure your application clearly indicates your preferred woreda (Berhale, Dallol, or Koneba).</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ozf3ombEhD-social-workers-child-protection-cp-gender-based-violence-gbv</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>31 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:45:39 UTC</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29067,7 +29266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29098,6 +29297,19 @@
       </c>
       <c r="C2" t="n">
         <v>300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:45:40 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U303"/>
+  <dimension ref="A1:U396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29254,6 +29254,8861 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>XfOUxM8mj8</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Marketer</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>NOLAWI TOUR &amp; TRAVEL</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Sales and Marketing; Business and Administra...; Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Interested candidates may apply either in person or by email . • In Person: Submit your CV and required documents, along with a non-returnable photocopy, at the office located behind Haya Hulet Debre Damo Hotel, below Arsho Laboratory . • By Email: Send your CV and required documents to theod.visionary@gmail.com For more Information +251977933333/+251968454647</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XfOUxM8mj8-marketer</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>24 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:45 UTC</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>nvQK4z1iel</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>NOLAWI TOUR &amp; TRAVEL</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Sales and Marketing; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Interested candidates may apply either in person or by email . • In Person: Submit your CV and required documents, along with a non-returnable photocopy, at the office located behind Haya Hulet Debre Damo Hotel, below Arsho Laboratory . • By Email: Send your CV and required documents to theod.visionary@gmail.com For more Information +251977933333/+251968454647</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/nvQK4z1iel-sales</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>27 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:47 UTC</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>xQPSC69QRI</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>MINTUPLAST PLASTIC RAW MATERIAL PRODUCTION PLC</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>B2B Marketing; analytical skill;; Excellent communication, interpersonal and organizational skills; Pro-active, goal-oriented, and results-driven; Communication, coordination, networking and facilitation skills; Aftermarket Strategy; Desired Skill; Ability to work under pressure and meet targets</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>All interested and qualified candidates can send their updated CVs to the below email address.
+Email Address: mintuhrho@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xQPSC69QRI-marketing-officer</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>28 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:50 UTC</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SVBzKOFL10</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>MRELA Advisor</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Quality Assurance; Development and Project...</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Monitoring, Evaluation &amp; Learning</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 04 October 2026/ 4:00 PM
+MRELA Advisor</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/SVBzKOFL10-mrela-advisor</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>28 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:53 UTC</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>k0OcQiI1ky</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Child Protection Officer</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HELP GENERATION</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Afar</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Knowledge of protection principles, GBV core concepts, and PSEA.</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants who meet the above requirements are invited to submit their updated CV and a cover letter through Ethio jobs by clicking the "Apply" button within the specified timeframe. Please ensure your application clearly indicates your preferred woreda (Berhale, Dallol, or Koneba).</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k0OcQiI1ky-child-protection-officer</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>30 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:56 UTC</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>7iZ0PJejJn</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Medical Representative</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>NOLAWI TOUR &amp; TRAVEL</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Health Care</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Interested candidates may apply either in person or by email . • In Person: Submit your CV and required documents, along with a non-returnable photocopy, at the office located behind Haya Hulet Debre Damo Hotel, below Arsho Laboratory . • By Email: Send your CV and required documents to theod.visionary@gmail.com For more Information +251977933333/+251968454647</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/7iZ0PJejJn-medical-representative</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>31 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:50:59 UTC</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>65E8RgbDgZ</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Relationship Manager (RM) Customer Relationship Officer</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>MALEDA FOAM AND PLASTIC MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business and Administra...; Business Development</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Business Administration,; Business Administration, Hospitality, Marketing, Management</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants who meet the above requirements are invited to submit the following documents in PDF format:
+Application/cover letter
+Updated CV/Resume
+Copies of educational credentials and supporting documents
+Applications should clearly indicate the position being applied for ("Internship – Sales") and be sent to:
+hr@maledafoam.com
+Application Deadline: Within 10 days from the date of this announcement.
+Only shortlisted candidates will be contacted for further stages of the selection process.</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/65E8RgbDgZ-relationship-manager-rm-customer-relationship-officer</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>34 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:02 UTC</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>6pdONZLRmS</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Junior Accountant</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ETHIO FERTILITY AND IVF CENTER</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Microsoft Office Pack: Word, Excel, Access, Publisher, Outlook, Powerpoint; Attention to detail; Proven experience using accounting software such as Peachtree, QuickBooks, or other ERP systems; Desired Skill; Adaptability; Basic knowledge of user interface communication; Team work</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through:- Ethioivf@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6pdONZLRmS-junior-accountant</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>41 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:04 UTC</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>yQoUfEhDu0</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Finance, People and Operations Manager</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>NIGAT GLOBAL INITIATIVE (NGI)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Analytical and problem-solving skills; Excellent communication and interpersonal abilities.</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Please submit a CV of no more than four pages and a concise cover letter explaining your suitability for the role and stating your expected gross salary. Send your application to careers@nigatglobal.org by 9 October 2026, using the subject line Application: Finance, People and Operations Manager.
+Only shortlisted candidates will be contacted.
+NGI is committed to safeguarding, survivor-centred practice, equal opportunity and professional integrity. We particularly welcome applications from qualified Ethiopian women, persons with disabilities and candidates with lived or directly relevant community experience</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yQoUfEhDu0-finance-people-and-operations-manager</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:08 UTC</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1C7b462zBO</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Admin Assistant</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>OPTIMUM AUDIT &amp; CONSULTING</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Ability to multitask and prioritize work</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>If you are seeking a challenging and rewarding opportunity to advance your professional career, please submit your resume, cover letter, and any other relevant documents to recruitment@optimumet.com or submit them in person at our office located on the 4th Floor of Noah Building, adjacent to Golagul Building, Haya Hulet, Addis Ababa.
+We appreciate all applications, but only candidates selected for an interview will be contacted. Thank you for considering Optimum as your next career opportunity.
+Application Deadline: within seven working days of this post.
+For additional information please call Tel. +251-11-635-25-26/ +251-920-24-25-26</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1C7b462zBO-admin-assistant</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:10 UTC</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>OpirJ9nvU2</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Programme Manager</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>NIGAT GLOBAL INITIATIVE (NGI)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.; Development Studies, Project Management, Economics, Business Administration,</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>Please submit a CV of no more than four pages and a concise cover letter explaining your suitability for the role and stating your expected gross salary. Send your application to careers@nigatglobal.org by 9 October 2026, using the subject line Application: Programme Manager.
+Only shortlisted candidates will be contacted.
+NGI is committed to safeguarding, survivor-centred practice, equal opportunity and professional integrity. We particularly welcome applications from qualified Ethiopian women, persons with disabilities and candidates with lived or directly relevant community experience.</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/OpirJ9nvU2-programme-manager</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:13 UTC</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>iWTCFPCFui</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Chief Operation Officer</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>MALEDA FOAM AND PLASTIC MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants who meet the above requirements are invited to submit the following documents in PDF format:
+Application/cover letter
+Updated CV/Resume
+Copies of educational credentials and supporting documents
+Applications should clearly indicate the position being applied for ("Internship – Sales") and be sent to:
+hr@maledafoam.com
+Application Deadline: Within 10 days from the date of this announcement.
+Only shortlisted candidates will be contacted for further stages of the selection process.</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iWTCFPCFui-chief-operation-officer</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:16 UTC</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>KQXANaSEOr</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Secretary (re-adverted)</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>MINTUPLAST PLASTIC RAW MATERIAL PRODUCTION PLC</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Analytical skills; Attention to detail; Office Administrator, Office Assistant,; communication, and MS Office skills; commitment</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>All qualified and interested applicants can send their updated CVs to the below email address.
+Email Address:- mintuhrho@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/KQXANaSEOr-secretary</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:19 UTC</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>jHu1TD5lfV</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Audit Officer</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>MALEDA FOAM AND PLASTIC MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Interested and qualified applicants who meet the above requirements are invited to submit the following documents in PDF format:
+Application/cover letter
+Updated CV/Resume
+Copies of educational credentials and supporting documents
+Applications should clearly indicate the position being applied for ("Internship – Sales") and be sent to: hr@maledafoam.com
+Application Deadline: Within 10 days from the date of this announcement. Only shortlisted candidates will be contacted for further stages of the selection process.
+Only shortlisted candidates will be contacted for further stages of the selection process.</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jHu1TD5lfV-audit-officer</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:22 UTC</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>QRHP2TEBlm</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Office Administrator (Re-Advert)</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>RIPPLE EFFECT</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving Organizational Skill. Excellent written and verbal communication skills</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>If you feel you have the qualities, passion, skills, and experience to fulfil this varied, rewarding, and vital role, we would love to hear from you. 
+Download the: 
+Job description
+Application form
+PSEA self-assessment form 
+Submit your application form and PSEA self-assessment form online (in Word or PDF format) to hrethiopia@rippleeffect.org clearing indicating the position you are applying for and using the job code OSS004 Officer Administrator in the subject line. 
+ If you require the job description or the application form in a different format, please contact Yokora.Ejigu@rippleeffect.org
+Key Dates
+Application Closing date: Friday 12th June 2026
+Interview date: To be Communicated
+Start date: As soon as Possible
+Key Contact
+Name:  Ejigu Yokora
+Email Address: Yokora.Ejigu@rippleeffect.org
+Key Contact
+Name:  Ejigu Yokora
+Email Address: Yokora.Ejigu@rippleeffect.org
+Application Form Ethiopia
+PSEA Self-Assessment Form</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/QRHP2TEBlm-office-administrator-re-advert</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:24 UTC</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ZbB9iA1cPv</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Senior, System, Data Base Administration, IST and IT security Officer</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ALLIANCE MICRO FINANCE</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>• Strong coordination and networking skills</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Application Procedure: Interested applicants are invited to submit their application with copy of credential via email:  alliancemfihr@gmail.com within 7 working days from the date of this announcement.</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ZbB9iA1cPv-senior-system-data-base-administration-ist-and-it-security-officer</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:27 UTC</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>yBAEHltRhC</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Communication Officer</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Communications, Media a...</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>, work experience, or other evidence ) submitted during employment/registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Ability to work under pressure and meet targets; Ability to work under pressure and meet deadlines; Desired Skill; Graphic design; Storytelling; Communication; Attention to detail; Ability to work under pressure and meet targets; Ability to deliver quality work within deadlines</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can register through Ethiojobs or by sending your application to cnplcvacancy@gmail.com  by specifying the job position and vacancy number clearly in the subject line of your email. Please also attach the following documents: Updated CV and all supporting documents; work experience from non-government organisations must be supported by proof of employment tax payment, grade 8 completion certificate and a "To whom it may concern letter from your current employer
+Forgery liability: any falsified documents (Education, work experience, or other evidence ) submitted during employment/registration will result in legal accountability
+Perks + Benefits
+Fuel
+Housing
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yBAEHltRhC-communication-officer</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:30 UTC</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>11tpidA6mC</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>MRELA &amp; CARM Senior Officer</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Quality assurance and compliance focus</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 04 October 2026/ 4:00 PM
+MRELA &amp; CARM Senior Officer | Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/11tpidA6mC-mrela-carm-senior-officer</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:33 UTC</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>jiRB8FDiCP</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Legal Officer</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>DINA INVESTMENT GROUP</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Management; Business and Administra...; Legal; Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>knowledge of Ethiopia’s tax laws; Knowledge of Ethiopian laws and regulations; Labor Law &amp; Employee Relations; In–depth knowledge of country substantive and procedural Laws; Familiarity with Ethiopian commercial law, labor law, and regulatory frameworks</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates who fulfill the above requirements are invited to submit their application, including an updated CV/Resume with cover Letter through careers@dinainvestmentgroup.com.
+Please indicate the Position Title “Legal Officer” the subject line of your Email.</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jiRB8FDiCP-legal-officer</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:36 UTC</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2lFt3yiwbU</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>KG, Primary, Middle and High school Teachers. School First Aid</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>STAIRWAY SCHOOL</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Education; Human Resource and Recr...; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Human Resource and Recruitment</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Communication, Teamwork; Time management; Requirement Skill; Ability to work under pressure and meet targets; Desired Skill; Communication; Good communication and interpersonal skills</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants are invited to submit their application letter, CV, relevant academic credentials, and work experience via email within 10 consecutive days from the date of this announcement.
+Email Submission: stairwayschoolinfo2@gmail.com
+Address: Jemo-2 Sheger Mazoria, Near KIru Cafe and Restaurant</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2lFt3yiwbU-kg-primary-middle-and-high-school-teachers-school-first-aid</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:39 UTC</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>U23scFIr5I</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Hotel Manager</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>DINA INVESTMENT GROUP</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Management</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management (CRM); Problem solving; customer communication and understanding capabilities; Customer Servce orienation; Customer Development; Excellent customer service; Customer-oriented with a positive service mindset.; Customer Service and Financial Literacy; Handle Customer Queries and Complaints</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to submit their CV and cover letter via email to: careers@dinainvestmentgroup.com
+Please Note: Use "Hotel Manager Application" as the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/U23scFIr5I-hotel-manager</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:42 UTC</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>TnVKM91Lt7</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Food Safety &amp; Quality Assurance Manager</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>DINA INVESTMENT GROUP</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Quality Assurance; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Effective problem-solving and decision-making skills,; Problem-solving, planning, and organizational skills.</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>If you meet the above qualifications and are ready to contribute to a leading food processing company, please submit your updated CV and cover letter.
+Email your application to: careers@dinainvestmentgroup.com
+Important: Please indicate the Job Title clearly in the subject line of your email "Application for Food Safety &amp; QA Manager"</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/TnVKM91Lt7-food-safety-quality-assurance-manager</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:45 UTC</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>yGfr9bSB8B</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Import Export Manager</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>DINA INVESTMENT GROUP</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Agriculture; Business and Administra...; Logistics, Transport an...; Management</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Ability to work under pressure and meet targets; • Strong coordination and networking skills; Problem-solving, planning, and organizational skills.; Ability to multitask and prioritize effectively.</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>If you meet the above qualifications and are ready to contribute to a leading food processing company, please submit your updated CV and cover letter.
+Email your application to: careers@dinainvestmentgroup.com
+Important: Please indicate the Job Title clearly in the subject line of your email "Application for Import Export Manager"</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yGfr9bSB8B-import-export-manager</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:48 UTC</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>c862lqgOMH</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Senior HR Officer</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>A AND M ENGINEERING PLC</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Basic knowledge of labor legislation; Ability to coordinate multiple tasks and work under pressure.; ability to build strong working relationships; Desired Skill; Attention to detail and strong administrative skills.; Ability to manage many requests at once.; ability to build strong working relationships; More Jobs by A and M Engineering PLC; የጥራት ቁጥጥር (Quality Control); Office; October 16th, 2026; ንብረት ተቆጣጣሪ (Storekeeper); Office; October 8th, 2026; የደንበኞች አገልግሎት ኦፊሰር (Customer service officer) እና ሴክሬታሪ</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/c862lqgOMH-senior-hr-officer</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:51 UTC</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>jhOoMJ1xU1</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Customer Care / Receptionist</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>DESTINY LINE TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Time management; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Address
+Summit Condominium, Ber 3
+Around Sunshine Philanthropy / Aregawuyan Merja Derejet or Ashara
+To Apply / Contact
+Temesgen — 0929 106 345
+Interested and qualified candidates are encouraged to contact us for more information and application.</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jhOoMJ1xU1-customer-care-receptionist</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:54 UTC</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>NoqtE0InXD</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Cashier Secretary 1</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>METEMAMEN MICRO FINANCING INSTITUTION S.C</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Interested &amp; qualified applicants can submit their letter of application with of CV and all educational Credentials within 5 working days from first day of announcement.
+Candidates are required to apply by scanning and submitting their educational documents by email. All scanned pages must be clear, complete, and arranged in order. Applications without scanned educational documents will not be considered.
+Our Address:-  Telephone 011-3-69-82-44/011-4-70-68-66
+Email –metemamenhr@gmail.com, Metemamen Microfinance  S.C</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NoqtE0InXD-cashier-secretary-1</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:56 UTC</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>NGaIdaZnmf</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>INVITATION TO BID FOR PROCUREMENT OF AUDIT SERVICES, BID NUMBER (054/26/SNV)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SNV</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Team work</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 
+Procedure for submission of proposal
+Submission is acceptable in both hard copies or email/ soft copies/. 
+For email /soft copies/ applicants: Both the Technical and Financial proposals should be sent separately, only through ettenders@snv.org 
+Therefore, SNV will expect two submission emails that are for the technical and financial offers. 
+Both email subjects must contain the name of the assignment and proposal type. If the consultants miss the submission procedure, they will be automatically rejected.
+ 2. For hard copy applicants: Technical and financial proposals must be submitted with separate sealed envelopes to the SNV office address below. 
+All bid prices should be valid for 90 days, and prices shall be quoted in ETB. 
+For any clarifications or questions, use the following email: atesfaye@snv.org   
+Proposals must be received by SNV no later than October 13, 2026, 17:00 PM, close of business. 
+SNV Ethiopia, Roosevelt St. on the way from AU to Mexico Square, telephone: +251 (0)11 616 6232, P.O. Box 40675, Addis Ababa | Ethiopia 
+SNV Ethiopia reserves the right to accept or reject any or all bids.</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NGaIdaZnmf-invitation-to-bid-procurement-of-audit-services-bid-number-05426snv</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:51:59 UTC</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>gMQ3deSSFm</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Junior Customer Service Officer</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>METEMAMEN MICRO FINANCING INSTITUTION S.C</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Economics; Management; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Interested &amp; qualified applicants can submit their letter of application with of CV and all educational Credentials within 5 working days from first day of announcement.
+Candidates are required to apply by scanning and submitting their educational documents by email. All scanned pages must be clear, complete, and arranged in order. Applications without scanned educational documents will not be considered.
+Our Address:-  Telephone 011-3-69-82-44/011-4-70-68-66
+Email –metemamenhr@gmail.com, Metemamen Microfinance  S.C</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gMQ3deSSFm-junior-customer-service-officer</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:04 UTC</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>mFCgTH3vOp</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Senior Branch Coordination Officer</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>, work Experience, or other Evidence ) submitted during Employment/Registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Analytical skills; analytical skill;; Basic computer skills (MS Office, email).; Desired Skill; Analytical skills; Basic computer skills (MS Office, email).; Monitoring, Evaluation &amp; Learning</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can register through Ethijobs or send your application to cnplcvacancy@gmail.com  by clearly stating the job position and vacancy number in your email subject line. Please also attach the following documents: Updated CV and all supporting documents; work experience from non-government organisations must be supported by proof of employment tax payment; grade 8 completion certificate and "To whom it may concern letter from your current employer.
+Forgery liability: any falsified documents ( Education, work Experience, or other Evidence ) submitted during Employment/Registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/mFCgTH3vOp-senior-branch-coordination-officer</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:06 UTC</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>LluUvbtshk</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Risk Management &amp; Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>METEMAMEN MICRO FINANCING INSTITUTION S.C</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Interested &amp; qualified applicants can submit their letter of application with of CV and all educational Credentials within 5 working days from first day of announcement.
+Candidates are required to apply by scanning and submitting their educational documents by email. All scanned pages must be clear, complete, and arranged in order. Applications without scanned educational documents will not be considered.
+Our Address:-  Telephone 011-3-69-82-44/011-4-70-68-66
+Email –metemamenhr@gmail.com, Metemamen Microfinance  S.C</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/LluUvbtshk-risk-management-compliance-officer</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:09 UTC</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Tm5UcW37Wu</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ETHIO BIOPHARMA ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Proven experience in conducting similar policy reviews or legal assessments; Desired Skill; Civil Engineering, Construction Management, Architecture, Disaster Risk Managemen</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants are invited to submit their updated CV and cover letter and their Credentials in PDF format to ebpe@ethiobiopharma.et Please indicate "Senior Civil Engineer' in the subject line of your email.
+Only shortlisted candidates will be considered.
+Female Candidates are encouraged</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Tm5UcW37Wu-senior-civil-engineer</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:12 UTC</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>FZXvKOtPpA</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Request for Proposal (RFP): Technology Support Services: Ethiopia</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>FHI360</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Consultancy and Trainin...; Social Sciences and Com...; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Timetable and Address for Submission:
+All proposals should be submitted to ProcurementESAHub@fhi360.org
+Questions are due no later than September 29, 2026, by 5:00 PM EAT. Questions should be submitted via email to ProcurementESAHub@fhi360.org
+Proposals are due no later than October 7, 2026, by 5:00 PM EAT. Required documentation listed below must be e-mailed to ProcurementESAHub@fhi360.org
+Method of Submittal:
+Questions and Proposal responses should be submitted via e-mail to ProcurementESAHub@fhi360.org with the attached documents in MS Word / pdf / format. Pricing should be provided in Excel format unless otherwise specified.
+Offeror agrees to hold the prices in its offer firm for 45 days from the date specified for the receipt of offers, unless another time is specified in the addendum of the RFP.
+Contract Period of Performance:
+Estimated Late-September 2026 – Mid-December 2026
+Estimated Mid-October 2026 – Mid-April 2027</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/FZXvKOtPpA-request-for-proposal-rfp-technology-support-services-ethiopia</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:15 UTC</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>dKEgKEkJSQ</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SITE ENGINEER</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>ALTHEHET INDUSTRIAL PLC.</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Construction Management, Architecture, Disaster Risk Managemen</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates are invited to submit their updated CV and relevant credentials through the designated application channel. On Telegram: 0923262616. No phone calls are accepted or allowed; please abide by the instructions. Only candidates who meet the stated qualification and experience requirements will be considered.</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/dKEgKEkJSQ-site-engineer</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:18 UTC</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2m89oNtXRa</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Materials Assistant</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>CHINA COMMUNICATION CONSTRUCTION COMPANY</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Accounting and Finance; Management; Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Excellent communication and interpersonal abilities.; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to submit their application and relevant credentials according to the organization's recruitment
+Interested qualified candidate are invited to apply in person at: CCCC Bishoftu international Airport-Abusera contact person Hirpo
+Tona, HR manager phone 0916110401
+Email: hirposekete@yahoo.com
+Telegram 0916110401 Interested and qualified candidates are invited to apply.</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2m89oNtXRa-materials-assistant</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:21 UTC</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Is0An2XkPG</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>OFFICE ENGINEER</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ALTHEHET INDUSTRIAL PLC.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Civil Engineering, Construction Management, Architecture, Disaster Risk Managemen</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates are invited to submit their updated CV and relevant credentials through the designated application channel. On Telegram: 0923262616. No phone calls are accepted or allowed; please abide by the instructions given Only candidates who meet the stated qualification and experience requirements will be considered.</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Is0An2XkPG-office-engineer</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:23 UTC</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>V2E8KpSVj5</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Senior Information Security Officer</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>DIGAF &amp; MICRO-CREDIT PROVIDER SC</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Technology</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Attention to detail; security and safety; Analytical and problem-solving skills; Teamwork and collaboration; Confidentiality and accountability</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Interested candidates should send their resumes along with a cover letter to our HR department at hr.admin@digafcredit.com no later than 10 workdays. Please specify the position you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/V2E8KpSVj5-senior-information-security-officer</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:26 UTC</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>YeHickimhn</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Senior Fabrication &amp; Steel Structure Sales Person</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Automotive; Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/YeHickimhn-senior-fabrication-steel-structure-sales-person</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:29 UTC</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>3Q3066d8Rk</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Senior Sales Engineer Vehicles &amp; Automotive</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business Development</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3Q3066d8Rk-senior-sales-engineer-vehicles-automotive</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:32 UTC</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>GmOBuwIfhP</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Senior Warehouse Management Officer</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...; Management</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/GmOBuwIfhP-senior-warehouse-management-officer</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:35 UTC</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>zs8U8UU54S</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Digital Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>OSAKA STEEL PVT.LTD.CO</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit their CV and a short cover letter. Email: lakewbasha@gmail.com Phone: +251 953 239 257
+ Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zs8U8UU54S-digital-marketing-officer</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:38 UTC</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SgdZXo88Jm</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Personal Assistant to Head of Primary and Early Years School</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Education; Business and Administra...; Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Personal Assistant to Head of Primary and Early Years School- [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/SgdZXo88Jm-personal-assistant-to-head-of-primary-and-early-years-school</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:40 UTC</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>54vWOBXeMa</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Primary School Librarian</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Education</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Primary School Librarian- [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/54vWOBXeMa-primary-school-librarian</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:43 UTC</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>RDw50Kak2s</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Sports / Basketball Coordinator</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Social Sciences and Com...; Education</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>, Business, Hospitality, or a related field.</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Sports / Basketball Coordinator- [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/RDw50Kak2s-sports-basketball-coordinator</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:46 UTC</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>x6CSwe3xSV</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Reception / Customer Service Officer</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Customer Service; Hotel and Hospitality; Business and Administra...; Social Sciences and Com...; Education</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Jobs for Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Reception / Customer Service Officer- [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/x6CSwe3xSV-reception-customer-service-officer</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:50 UTC</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>eTxGF8LAMr</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Short-Term Consultancy Opportunity Digital Economy and ICT Skills Specialist</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>BCAD CONSULTING MANAGEMENT PLC</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Application Requirements
+Applicants should submit:
+An updated CV;
+Copies of relevant qualifications and professional certifications;
+Brief evidence of relevant assignments;
+A short statement identifying the digital fields they are qualified to cover;
+Confirmation of availability during the anticipated six-week assignment; and
+Proposed gross daily professional fee, subject to applicable statutory withholding tax.
+Important: Applicants who specialize only in one narrow area should clearly state their areas of competence.
+How to Apply
+Application deadline
+Monday, 28 September 2026 at 12:00 p.m.
+Email subject
+Application – Digital Economy and ICT Skills Specialist
+Email address
+hr.bcadconsulting@gmail.com
+Only shortlisted applicants will be contacted for a brief interview.</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/eTxGF8LAMr-short-term-consultancy-opportunity-digital-economy-and-ict-skills-specialist</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:53 UTC</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Y5SuNKcSXV</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Pool Technician – On Call</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...; Education</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Jobs for Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Pool Technician – On Call- [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Y5SuNKcSXV-pool-technician-on-call</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:56 UTC</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>XRLVtkQUvu</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...; Education</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Jobs for Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Lifeguard - [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XRLVtkQUvu-lifeguard</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:52:58 UTC</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>qJgh4sAveT</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Facilities / Maintenance Technician</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Facilities / Maintenance Technician - [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qJgh4sAveT-facilities-maintenance-technician</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:01 UTC</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>u1AKVZvbLR</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Program Development Manager (Re- Advert)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SAMARITAN'S PURSE</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Development and Project...; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Teamwork; High integrity and reliability; Desired Skill; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>All interested candidates are encouraged to apply for the position advertised by submitting their CV/Resume (maximum of 2 pages) and application letter (one Page only) no later than October 2, 2026. We only accept applications sent via our online-application form on https://mycareersethiopia.samaritan.org</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/u1AKVZvbLR-program-development-manager-re-advert</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:04 UTC</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>k0rRyb2qOm</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>TV Host</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SILVER SPRING PRODUCTION &amp; PROMOTION PLC</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Communications, Media a...</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified applicants should send their updated CV, portfolio and other credentials through the following e-mail address: silverspringhr@gmail.com with a subject line of TV Host.            
+Our Culture: Every employee is an influencer and culture keeper. We expect respectful communication (despite pressure), openness to feedback, an eagerness to learn, and an overall positive attitude!
+Silver Spring Production and Promotion P.L.C. is proud to be an Equal Opportunity Employer and Drug-Free Workplace!
+ </t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k0rRyb2qOm-tv-host</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:07 UTC</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2Wkkn7TKt6</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Follow-Up &amp; Student Progress Officer</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>NEW LIFE TRAINING AND EVENT CENTER</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.; Experience in a social service, psychology,</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified candidates should submit an updated CV, cover letter, and copies of relevant credentials/ certificates through one of the following methods. Only shortlisted applicants will be contacted for an interview.
+In Person: Bulgariya, near Saint Michael Church | newlifetecenter@gmail.com | Phone / Contact: 0970535455 / 0910733394
+ </t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2Wkkn7TKt6-follow-up-student-progress-officer</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:10 UTC</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Wu0GrDLNiJ</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN HUMAN RIGHTS COMMISSION (EHRC)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Afar</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Adaptability; Communication</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>Application link Registrar | HRIS</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Wu0GrDLNiJ-registrar</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:13 UTC</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>3oPclP8bS8</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Senior General Ledger Accountant</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>JR PETROLEUM PLC</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Interested applicants can apply by sending their CV and credentials via email with the subject line "Senior General Ledger Accountant" betelhem.mekonen@jrpetroleumplc.com</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3oPclP8bS8-senior-general-ledger-accountant</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:16 UTC</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ATILs92Zl8</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Trainer – Academic Performance &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>NEW LIFE TRAINING AND EVENT CENTER</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>, Sociology, Youth Development, Social Work, or a related field, Background or additional training in education, psychol</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.; Gender Studies, Social Work, Law</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified candidates should submit an updated CV, cover letter, and copies of relevant credentials/ certificates through one of the following methods. Only shortlisted applicants will be contacted for an interview.
+In Person: Bulgariya, near Saint Michael Church | newlifetecenter@gmail.com | Phone / Contact: 0970535455 / 0910733394
+ </t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ATILs92Zl8-front-desk-receptionist</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:19 UTC</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>sOuE9oRK2b</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Front Desk Receptionist</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>NEW LIFE TRAINING AND EVENT CENTER</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Business and Administra...; Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified candidates should submit an updated CV, cover letter, and copies of relevant credentials/ certificates through one of the following methods. Only shortlisted applicants will be contacted for an interview.
+In Person: Bulgariya, near Saint Michael Church | newlifetecenter@gmail.com | Phone / Contact: 0970535455 / 0910733394
+ </t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/sOuE9oRK2b-front-desk-receptionist</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:23 UTC</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>19KiLr1meB</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Finance Officer</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>NEW LIFE TRAINING AND EVENT CENTER</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified candidates should submit an updated CV, cover letter, and copies of relevant credentials/ certificates through one of the following methods. Only shortlisted applicants will be contacted for an interview.
+In Person: Bulgariya, near Saint Michael Church | newlifetecenter@gmail.com | Phone / Contact: 0970535455 / 0910733394
+ </t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/19KiLr1meB-finance-officer</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:26 UTC</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>oZeuBrWzWF</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Meal  officer</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>MOTHER AND CHILD DEVELOPMENT ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested candidates are invited to submit their CV and a cover letter outlining their suitability for the role
+to info@mcdo97.org.et, mcdohr6@gmail.com  staring date 24/9/2026 and end date 30/9/2026. Please include
+“Meal Officer Application” in the subject line. 
+We are an equal opportunity employer and strongly encourage applications from women, minorities, and individuals
+With disabilities. 
+ </t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oZeuBrWzWF-meal-officer</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:29 UTC</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>l8EVkcnW8n</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Senior Financial Planning &amp; Analysis (FP&amp;A) Analyst</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>JR PETROLEUM PLC</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>Interested applicants can apply by sending their CV and credentials via email with the subject line "Senior Financial Planning &amp; Analysis (FP&amp;A) Analyst" betelhem.mekonen@jrpetroleumplc.com</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/l8EVkcnW8n-senior-financial-planning-analysis-fpa-analyst</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:32 UTC</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>TQZuqrNnsk</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Senior Associate-Learning and Development</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>GRANT THORNTON ADVISORY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>, or a related field.</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Excellent facilitation, training, and community mobilization skills.; Training &amp; capacity building; Skills in organizing and facilitating training programs; Training &amp; Development Coordination</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>Fill the online application form by following the below link by inserting this vacancy code: GTE016/09/2026
+https://forms.office.com/r/Wfijv7sv10
+Only shortlisted applicants who filled online application form will be contacted.
+Female applicants are highly encouraged to apply.
+Grant Thornton Ethiopia is an equal opportunity employer. We value diversity and inclusion and welcome applications from all qualified candidates.</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/TQZuqrNnsk-senior-associate-learning-and-development</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:34 UTC</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>aqBurynz8H</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>MARKETING OFFICER (1 Position)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>PRIME CAPITAL INVESTMENT BANK</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Send your CV and cover letter to info@primecapitalsc.com  with the subject line "Marketing Officer" by October 5, 2026.</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/aqBurynz8H-marketing-officer-1-position</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:37 UTC</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>7NAmTcdAiX</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Business Development Officer</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>PRIME CAPITAL INVESTMENT BANK</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Send your CV &amp; cover letter to info@primecapitalsc.com with the subject line "BD Officer" until October 5, 2026.</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/7NAmTcdAiX-business-development-officer</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:40 UTC</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>DZJmHh668n</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Duty Manager / Theatre &amp; Events Lead</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Duty Manager / Theatre &amp; Events Lead - [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DZJmHh668n-duty-manager-theatre-events-lead</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:43 UTC</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>dBENABLs0Q</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>PRIME CAPITAL INVESTMENT BANK</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Business Development; Management</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Send your CV and cover letter to info@primecapitalsc.com with the subject line "BD Manager" until October 5, 2026.</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/dBENABLs0Q-business-development-manager</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:46 UTC</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2NknPq7HCL</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Driver I ለ ደቡብ ምዕራብ ቀጠና ጽ/ቤት (ቦንጋ)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>DASHEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>automotive</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://career55.sapsf.eu/sfcareer/jobreqcareer?jobId=2298&amp;company=dashenbank
+ለማንኛውም የድጋፍ ጥያቄና ማብራሪያ የሚከተለውን ስልክ ቁጥር ይጠቀሙ
+047-3-31-27-54
+ </t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2NknPq7HCL-driver-i</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:49 UTC</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>CJA0yzeWA2</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Centre Manager – Recreational Facilities</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Hotel and Hospitality; Management</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: Centre Manager – Recreational Facilities - [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/CJA0yzeWA2-recreational-facilities</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:52 UTC</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>rqzP7Z1TXU</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Cash Service Attendant For Branches Under Hawassa District</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>DASHEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Banking and Insurance</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Analytical skills; Desired Skill; analytical skill;</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In order to apply for this Job Positing, click the link below:
+https://career55.sapsf.eu/sfcareer/jobreqcareer?jobId=2297&amp;company=dashenbank
+Connect With Us For Updated News and Job Openings
+Career Site: Career Opportunities
+Telegram: https://t.me/DashenBankEthiopia
+LinkedIn: https://www.linkedin.com/company/dashen-bank-official-page
+Facebook: https://www.facebook.com/DashenBankOfficial
+ </t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/rqzP7Z1TXU-cash-service-attendant-for-branches-under-hawassa-district</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:55 UTC</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>eBA59RZD4k</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>AV / Technical Support Technician</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>CAMBRIDGE ACADEMY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above requirements are invited to submit their application package as a single PDF document containing: https://docs.google.com/document/d/1v4XP8fuCALbzRgUt4w9p4gHEOSL3IuOV/edit?usp=sharing&amp;ouid=108050534850595632006&amp;rtpof=true&amp;sd=true
+Comprehensive Curriculum Vitae (CV).
+Cover letter explaining suitability for the role.
+Copies of academic and professional credentials.
+Please email your application to: cae-careers@cambridgeethiopia.org
+Subject Line: Application: AV / Technical Support Technician - [Your Name]
+Important Notes:
+Cambridge Academy Ethiopia is committed to safeguarding and promoting the welfare of children and young people.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/eBA59RZD4k-av-technical-support-technician</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:53:58 UTC</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1qSaOHZ3BN</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Production Manager</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>MATHIOS MEBA COSMETICS MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.; Food Science, or Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to apply by email at etcareofficial@gmail.com  
+Application Period: Within 10 consecutive days from the date of this announcement.
+Applicants are encouraged to submit an updated CV and relevant educational and experience credentials along with their application.</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1qSaOHZ3BN-production-manager</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:01 UTC</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>UktrwwLAeR</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Night Housekeeper / Public Attendant</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>ALTERA LUXURY LIVING</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Interested and Qualified clients can apply through the email  below
+alteraluxuryliving@gmail.com Or In-person at Addis Ababa, Bole area.</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/UktrwwLAeR-night-housekeeper-public-attendant</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:03 UTC</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>LIWMqw4LC6</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Housekeeping / Public Attendant</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>ALTERA LUXURY LIVING</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Interested and Qualified clients can apply through the email  below
+alteraluxuryliving@gmail.com Or In-person at Addis Ababa, Bole area.</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/LIWMqw4LC6-housekeeping-public-attendant</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:06 UTC</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>0ATgS20IFl</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Female Security Guard</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>ALTERA LUXURY LIVING</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Interested and Qualified clients can apply through the email  below
+alteraluxuryliving@gmail.com Or In-person at Addis Ababa, Bole area.</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/0ATgS20IFl-female-security-guard</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:09 UTC</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>AlIltBbEpc</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Volunteer Community Monitor</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>CONSORTIUM OF CHRISTIAN RELIEF AND DEVELOPMENT ASSOCIATION (CCRDA )</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>September 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>How to Apply
+Interested applicants should complete the Community Monitor Application Form using the link below. The application form is available in English, Afaan Oromoo, and Amharic. To change the language, please select your preferred language option from the top-right corner of the application form.
+Application Link: https://ee.kobotoolbox.org/x/7dDBqC3b
+Number of Positions
+Three (3) Volunteer Community Monitors will be selected for each participating health facility.
+Women, youth, persons with disabilities, people living with HIV, TB-affected communities, malaria-affected communities, and other priority community groups are strongly encouraged to apply.</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/AlIltBbEpc-volunteer-community-monitor</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:12 UTC</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>8CP1xpOC2L</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Affairs/Liaison Officer</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>APEX CONFECTIONERY PLC</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>Application Instructions
+Applicants who meet the required qualifications, work experience, and skills for the positions listed above may apply within 10 (ten) working days from the date of publication of this announcement.
+Applications may be submitted in person or by email to:
+Email: hr@apexsweets.com
+Address:
+Akaki Kaliti Woreda 07, Industry Village
+For more information, please contact:
+0981849409 or 0932614646
+Apex Confectionery PLC</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/8CP1xpOC2L-affairsliaison-officer</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:15 UTC</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>BeRXxx550C</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Production Department Staff</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>APEX CONFECTIONERY PLC</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Application Instructions
+Applicants who meet the required qualifications, work experience, and skills for the positions listed above may apply within 10 (ten) working days from the date of publication of this announcement.
+Applications may be submitted in person or by email to:
+Email: hr@apexsweets.com
+Address:
+Akaki Kaliti Woreda 07, Industry Village
+For more information, please contact:
+0981849409 or 0932614646
+Apex Confectionery PLC</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BeRXxx550C-production-department-staff</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:18 UTC</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>NITvxT7JS8</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>TERMS OF REFERENCE Consultancy Services for Business Development Services (BDS) and Leadership/Managerial Skills Training</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>CENTER FOR ACCELERATED WOMEN'S ECONOMIC EMPOWERMENT (CAWEE)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Interested bidders must submit the following as part of their proposal:
+A technical proposal detailing the proposed methodology and work plan.
+A detailed work plan aligned with the assignment timeline indicated above (September 2026 – May 2027).
+Profiles/CVs of all proposed key personnel.
+A description of the tools, templates, and methodologies to be used.
+A financial proposal with a detailed budget breakdown.
+Evidence of previous similar assignments, including reports and/or client testimonials.
+11.  Submission Instructions
+Language / Format
+English
+Proposal Structure
+Technical and Financial proposals submitted as two separate files
+Authentication
+All submissions must bear the organization's official seal/stamp
+Submission Point
+Direct submission at CAWEE Office, HR and Admin Focal Person
+Submission Deadline
+September 28, 2026
+Late Submissions
+Will not be considered</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NITvxT7JS8-terms-of-reference-consultancy-services-for-business-development-services-bds-and-leadershipmanagerial-skills-training</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:21 UTC</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>gRUotHKqJh</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Import Export Officer</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SORETI INTERNATIONAL TRADING</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Sales and Marketing; Management; Economics; Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Attention to detail; Excellent communication and interpersonal abilities.; with an experience of Import, Export Company; MA/BA: Marketing Management, Business Administration, International Marketing</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Qualified job seekers who meet the requirements are invited to register by bringing their complete educational and work-experience documents to the company’s Head Office, located at Soreti Building, 3rd Floor, Summit Safari (commonly known as “Fiyel Bet”), Addis Ababa.
+Applications will be accepted within 10 consecutive working days from the date of this announcement.
+Email: hr@soretiinternational.com
+Website: www.soretiinternational.com/careers
+For further information, applicants may contact the company at:
+0994917982 | 0922363560</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gRUotHKqJh-import-export-officer</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:24 UTC</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>caGpoQC7Gd</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Monitoring Evaluations, Learning, Knowledge &amp; Sharing Officer (MELKS Officer )</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>CHILDREN BELIEVE FUND</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Application Process:
+If you believe you have that unique combination of a not-for-profit heart combined with the skills and interest for the “MELKS Officer” position, please use this link:-
+https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=cefdcbd8-57ee-4443-850b-74160ac06342&amp;ccId=19000101_000001&amp;jobId=555744&amp;lang=en_CA
+Applications are welcome from qualified applicants and will be received until October 7, 2026.
+Applications must be submitted in English.
+Applicants must be legally eligible to work in Ethiopia.
+Consistent with our Child Protection/Safe-Guarding Policy the successful candidate must receive clearance by a criminal record check.
+Children Believe is committed to diversity in the workplace and is an equal opportunity employer. Women applicants are highly encouraged to apply.
+We thank all applicants for applying, however, only candidates selected for an interview will be contacted.
+People &amp; Culture Team
+Children Believe</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/caGpoQC7Gd-monitoring-evaluations-learning-knowledge-sharing-officer-melks-officer</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:26 UTC</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>po09QG3Zoz</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Civil Engineer II</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Engineering; Architecture and Constr...</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>al Credentials and work experience documents</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> APPLICATION PROCEDURE
+Application Letter
+Updated CV
+Educational Credentials and work experience documents
+Applicants should submit documents in PDF format and clearly indicate the position for which they are applying.
+Application Link: https://rb.gy/3rtgvg
+Application Deadline: Within 7 days from the date of this announcement.
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/po09QG3Zoz-civil-engineer-ii</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:29 UTC</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>F080DJvHbC</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Customer Service Supervisor</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements can submit their application letter, updated CV, educational and work experience credentials in PDF format by clearly stating the position &amp; location that you are applying for through the application link within 7 days from the date of announcement.
+Application Link: https://forms.gle/Muqmf2ZrZCqzGuw58
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/F080DJvHbC-customer-service-supervisor</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:32 UTC</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>sUinyDgUOO</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Customs Clearance Officer / Transistor</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SORETI INTERNATIONAL TRADING</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Attention to detail; Excellent communication and interpersonal abilities.; with an experience of Import, Export Company</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Qualified job seekers who meet the requirements are invited to register by bringing their complete educational and work-experience documents to the company’s Head Office, located at Soreti Building, 3rd Floor, Summit Safari (commonly known as “Fiyel Bet”), Addis Ababa.
+Applications will be accepted within 10 consecutive working days from the date of this announcement.
+Email: hr@soretiinternational.com
+Website: www.soretiinternational.com/careers
+For further information, applicants may contact the company at:
+0994917982 | 0922363560</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/sUinyDgUOO-customs-clearance-officer-transistor</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:35 UTC</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>bEBk3pxbp0</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Project Engineer – Civil</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>REPI SOAP &amp; DETERGENT PLC</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Good project management knowledge.</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apply by Filling out the form - https://forms.gle/i4Hdg16TK829nr1B6 or  through Email - hana.seyum@et.wilmar-intl.com </t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/bEBk3pxbp0-project-engineer-civil</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:38 UTC</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>AUoKLFUHAI</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Graduate Piping Design Engineer (Trainee)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>CHINA RAIL TRANSIT ENGINEERING CONSULTANCY</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Engineering; Graduate and Management...; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>If You are a Passionate and Enthusiastic Engineering Graduate Looking for an Exciting Opportunity to Kick-Start Your Career, We Invite You to Submit Your Application. Please Include the Following Documents:
+Updated resume/CV; The file name for your resume/CV should be in the following format
+Full name
+Major
+Contact information (Phone Number or email)
+Temporary / Final Degree Certificate
+Copies of academic transcripts including student copy or semester slips indicating the grades they have achieved in each semester
+Any additional certifications or documents showcasing your skills (optional)
+Please send your application via email only to ethiopia.tmcoordinator@crtecsc.com or with the subject line: “Graduate Design Engineer (Trainee) - [Your Name and Engineering Discipline (E.g., Civil Engineer or ….) ]".
+Note: Only shortlisted candidates will be contacted for further evaluation and interviews. You are not expected to call so please No calls or texts or any in-person submissions.
+Application Deadline: [ 7 days after the announcement Date]
+Expect for an in-person Interview.
+Join our team and embark on a rewarding career in engineering with [China Rail Transit Engineering Consultancy - Ethiopia]. We look forward to reviewing your application and meeting talented individuals like you.</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/AUoKLFUHAI-graduate-piping-design-engineer-trainee</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:41 UTC</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>WbukNH1u33</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Lawyer</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>SHER ETHIOPIA PLC</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Proven experience in conducting similar policy reviews or legal assessments; Demonstrate a strong interest in legal aid and access to justice.</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit their full English CV and English application letter within 7 days to HR main office hrziway@sherethiopia.com</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/WbukNH1u33-lawyer</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:44 UTC</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Go5ZOtliFf</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Finance Intern</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>EMPOLO ADDIS TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Accounting,; Data Entry &amp; Record-Keeping</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates should submit their updated CV through the Ethiojobs application system.
+Application Deadline: September 30, 2026
+Please clearly indicate “Finance Intern” as the position applied for.
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Go5ZOtliFf-finance-intern</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:47 UTC</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>PGLglRLNPp</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Emergency Nutrition Officer (ENO) - NOA</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Nutrition, Public Health</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Emergency Nutrition Officer (ENO) - NOA ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+Application Deadline October 3, 2026</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/PGLglRLNPp-emergency-nutrition-officer-eno-noa</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:50 UTC</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>s3oEIKgciM</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>General Mechanics</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>KALITY FOODS S.C</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>• Creativity</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit their application letter, updated CV, and credentials within Ten (10) days from the date of this announcement, either in person or via email using the address provided below.
+Address:
+Kaliti Food S.C. around Kaliti St. Gebreal Church, on the way to Debrezeit (approximately 200 meters).     Email: D.hr_admin@cerealiabiscuits.com</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/s3oEIKgciM-general-mechanics</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:53 UTC</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>kNVrONn3DO</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>KALITY FOODS S.C</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>• Creativity; Desired Skill; • Creativity</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit their application letter, updated CV, and credentials within Ten (20) days from the date of this announcement, either in person or via email using the address provided below.
+Address:
+Kaliti Food S.C. around Kaliti St. Gebreal Church, on the way to Debrezeit (approximately 200 meters).     Email: D.hr_admin@cerealiabiscuits.com</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kNVrONn3DO-electrician</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:55 UTC</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>CIOKLCe3B4</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Senior Human Resources Officer</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>KALITY FOODS S.C</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>• Development-oriented; Desired Skill; • Development-oriented</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Interested  &amp; qualified applicants should submit their application letter, updated CV, and credentials within Ten (10) days from the date of this announcement, either in person or via email using the address provided below.
+Address:
+Kaliti Food S.C. around Kaliti St. Gebreal Church, on the way to Debrezeit (approximately 200 meters).     Email: D.hr_admin@cerealiabiscuits.com</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/CIOKLCe3B4-senior-human-resources-officer</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:54:58 UTC</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>lDKKfMHzNB</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Human Resources Officer</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>METROPOLITAN REAL ESTATE PLC</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Recruitment and Selection; Desired Skill; Recruitment and Selection</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can apply online through Ethiojobs.net or send your resume to Hr@metropolitanaddis.net.
+Use the subject line "Human Resource Officer" when applying via email.</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lDKKfMHzNB-human-resources-officer</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:01 UTC</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>g2VahVZmrr</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>TERMS OF REFERENCE Recruitment of a Trainer on Disability-Inclusive Project Planning and Implementation</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL SOLIDARITY FOUNDATION</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Legal</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.; Psychology, Social Work, Gender Studies, Law o</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guiding Principle
+The central expectation of the assignment is:
+Participants should not leave the training simply knowing more about disability inclusion. They should leave knowing what they need to change in their own projects, how to make those changes, and what they will do next.
+The successful trainer will therefore act as a facilitator, coach and technical resource person, supporting ISF staff and partners to translate disability inclusion principles into practical programme decisions.
+Timeline  
+The following timeline is proposed for the selection and engagement process:  
+Proposal submission deadline: 02.10.2026
+Consultant selection and notification: 09.10.2026
+Inception report: 15.10.2026
+Training delivery: 26-28.10.2026
+Note if you are not contacted during the above schedule, it means you are not selected.  
+Application submission:  
+Interested applicants should send their Proposals together with other supporting documents to the email isfethiopia@solidaarisuus.fi   with the subject head ‘ISF disability Inclusion’.  
+ </t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/g2VahVZmrr-terms-of-reference-recruitment-of-a-trainer-on-disability-inclusive-project-planning-and-implementation</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:04 UTC</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>g2qx2FAtVl</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Special Real Estate Sales Agent</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SUMMER REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Client Follow-up &amp; Communication; Excellent communication and interpersonal skills.</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>How to Apply
+Interested candidates are invited to submit their CV and relevant supporting documents to Summer Real Estate PLC via Telegram username "Abdulaziz Jafar"
+Application Deadline: Oct 5/ 2026 G.C</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/g2qx2FAtVl-senior-real-estate-sales-agent</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:07 UTC</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>F0962HRbfe</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Cash Service Attendant under Hawassa District</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>DASHEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Analytical skills</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>How To Apply
+In order to apply for this Job Positing, click the link below:
+https://career55.sapsf.eu/sfcareer/jobreqcareer?jobId=2297&amp;company=dashenbank
+For Any Enquiry or Support Request
+Connect With Us For Updated News and Job Openings
+Career Site: Career Opportunities
+Telegram: https://t.me/DashenBankEthiopia
+LinkedIn: https://www.linkedin.com/company/dashen-bank-official-page
+Facebook: https://www.facebook.com/DashenBankOfficial</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/F0962HRbfe-cash-service-attendant-under-hawassa-district</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:10 UTC</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>OhQSuXnU6e</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Individual Consultant / Consultancy Firm</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>EMPATHY FOR LIFE INTEGRATED DEVELOPMENT ASSOCIATION /ELIDA/</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>• Development-oriented; • Creativity; • Proven experience in working with CSOs, networks, or local initiatives and communities; • Strong coordination and networking skills; Ability to deliver quality work within deadlines; Desired Skill; • Creativity; • Proven experience in working with CSOs, networks, or local initiatives and communities; • Strong coordination and networking skills; Ability to deliver quality work within deadlines</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Application Procedure
+Interested applicants should submit the following documents to procurement@elidaethiopia.org Until 30 September 2026:
+Technical proposal addressing: understanding of the ToR, objectives, and methodology (including sampling); deliverables and timeline; risks and assumptions; teaming approach; previous experience ;and logistics and communication plan.
+Financial proposal detailing the financial/cost breakdown, including any applicable tax related to the assignment.
+Supporting documents: business registration, business license, TIN certificate, and VAT certificate (forconsultancy firms); ToT or similar tax-payment declaration (for individual applicants or sole proprietors);reference letter(s) from previous employers; and any other supporting documents relevant to the assesment</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/OhQSuXnU6e-individual-consultant-consultancy-firm</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:13 UTC</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29266,7 +38121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29310,6 +38165,19 @@
       </c>
       <c r="C3" t="n">
         <v>302</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:55:15 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U396"/>
+  <dimension ref="A1:U476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -38109,6 +38109,7562 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>c6xM9puB4e</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>IT Supervisor</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>HILTON ADDIS ABABA</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; IT, Computer Science an...; Technology</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Network administration; Hardware maintenance; • Creativity; Ability to work under pressure and meet targets; Desired Skill; Adaptability; Team work; Commitment to continuous learning and knowledge sharing</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Interested &amp; Qualified Candidates who is active and have a hands-on knowledge of Hotel Operation Software can apply through ADDHI_HRD@hilton.com or send 3-5 Pages CV to the Office of Director of Human Resources-Hilton Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/c6xM9puB4e-it-supervisor</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>14 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:42 UTC</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>oIT4pOS3EX</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Learning &amp; Development Officer (Training Officer)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>HILTON ADDIS ABABA</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...; Hotel and Hospitality; Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Basic knowledge of user interface communication; Training and Development; HRIS and Technology; • Strong coordination and networking skills; Desired Skill; Adaptability; • Creativity; • Strong coordination and networking skills; Ability to deliver quality work within deadlines</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Interested &amp; Qualified Candidates who are active and have hands on experience in Training Need Assessment, Training Impact Assessment and Training Delivery are invited to apply through ADDHI_HRD@hilton.com or can send their 3-5 pages CV to the Office of Director of Human Resources-Hilton Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oIT4pOS3EX-learning-development-officer-training-officer</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>40 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:45 UTC</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>gdQ8cHYDhJ</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Senior Digital and Fund Administration Officer</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>, work experience, or other evidence ) submitted during employment/registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Analytical skills; Basic computer skills (MS Office, email).; Desired Skill; Analytical skills; Basic computer skills (MS Office, email).; Monitoring, Evaluation &amp; Learning</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can register through Ethiojobs or by sending your application to cnplcvacancy@gmail.com  by Specifying Job Position and vacancy number clearly in the subject line of your email. Please also attach the following documents: Updated CV and all supporting documents, Work experience from non-Government organizations must be supported by proof of employment tax payment, grade 8 completion certificate and "To whom it may concern letter" from your current employer
+Forgery liability: any falsified documents (Education, work experience, or other evidence ) submitted during employment/registration will result in legal accountability
+Perks + Benefits
+Fuel
+Housing
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gdQ8cHYDhJ-senior-digital-and-fund-administration-officer</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:48 UTC</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>139afWIoVw</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ATM Service Technician</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>, work experience, or other evidence ) submitted during employment/registration will result in legal accountability</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Troubleshooting; Desired Skill; Troubleshooting; Hardware maintenance</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can register through Ethiojobs or by sending your application to cnplcvacancy@gmail.com  by Specifying Job Position and vacancy number clearly in the subject line of your email. Please also attached the following documents: Updated CV and all supporting documents, Work experience from non-Government organizations must be supported by proof of employment tax payment, grade 8 completion certificate and "To whom it may concern letter" from your current employer
+Forgery liability: any falsified documents (Education, work experience, or other evidence ) submitted during employment/registration will result in legal accountability
+Perks + Benefits
+Fuel
+Housing
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/139afWIoVw-atm-service-technician</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:51 UTC</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>70f4otEBYL</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Pizza Chef</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Customer Servce orienation; Strong knowledge of modern kitchen equipment and cooking techniques; Food Safety &amp; Hygiene; Desired Skill; Strong customer service orientation; Excellent customer service; Handle Customer Queries and Complaints; Good customer service, communications,</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio job attach your resume.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/70f4otEBYL-pizza-chef</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:54 UTC</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>R8oYxtzuMh</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Commis Chef II</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Sanitation; Ability to coordinate multiple tasks and work under pressure.; Food Safety &amp; Hygiene; Desired Skill; Team work</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio jobs attaching your resume.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/R8oYxtzuMh-commis-chef-ii</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:31:57 UTC</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Ii89wZMxOm</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Shift Fitter II - IS Machine</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>DEDE BOTTLE FACTORY</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Mechanical Troubleshooting</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to apply by submitting their application and updated CV through our website
+Application Link: https://dedebottle.com/careers/42
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Ii89wZMxOm-head-is-service</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:00 UTC</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>iIh63vjTbA</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>GENERAL SERVICE OFFICER</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>METROPOLITAN REAL ESTATE PLC</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Attention to detail; Computer skill and knowledge.; Driving Skills; Communication &amp; Negotiation; Ability to multitask and prioritize work; Administrative Support</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>October 27th, 2026</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can send your resume to Hr@metropolitanaddis.net or through Ethiojobs.
+Use the subject line “General Service Officer” when applying through email.</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iIh63vjTbA-general-service-officer</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:03 UTC</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>dC5146UISV</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Commis Chef I</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Product knowledge; Food Safety &amp; Hygiene; Desired Skill; Team work; Strong knowledge of modern kitchen equipment and cooking techniques</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio jobs attaching your resume.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/dC5146UISV-commis-chef-i</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:06 UTC</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>zLfJd3FEWY</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Product Sourcing, Production Coordination &amp; Planning Manager</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SACON CONSTRUCTION AND TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Agriculture; Logistics, Transport an...; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Attention to detail; Problem-solving, planning, and organizational skills.; Strong communication, negotiation, and interpersonal skills</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+Email: hayat@saconplc.com  
+with the subject line: “Application – Product sourcing and Production Planning ”
+Dead Line Oct -8-2026</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zLfJd3FEWY-product-sourcing-production-coordination-planning-manager</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:09 UTC</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>0wj1rhHWfp</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>IMPORT &amp; EXPORT HEAD</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>SACON CONSTRUCTION AND TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Economics; Business and Administra...; Warehouse, Supply Chain...</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Excellent communication, negotiation, and leadership skills.; Analytical and problem-solving skills; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,; Excellent verbal and written communication skills; with an experience of Import, Export Company</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+Email: hayat@saconplc.com  
+with the subject line: “Application – Import &amp; Export Head”
+Dead Line Oct -8-2026</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/0wj1rhHWfp-import-export-head</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:12 UTC</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>U3sH7FaoTB</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>FINANCE HEAD</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SACON CONSTRUCTION AND TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP; Analytical and problem-solving skills; • Strong coordination and networking skills; Strong knowledge of Ethiopian tax laws and regulations.</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+Email: hayat@saconplc.com  
+with the subject line: “Application – Finance Head”
+Dead Line Oct -8-2026</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/U3sH7FaoTB-finance-head</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:15 UTC</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>R93E4xLCGR</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Demi Chef De Partie</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Food Safety &amp; Hygiene; Desired Skill; Team work; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio job attaching your resume.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/R93E4xLCGR-demi-chef-de-partie</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:18 UTC</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>v5E6bg5ADM</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Truck Driver</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CARGO AND AVIATION SERVICE (ICAS)</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                          - 10th Grade complete and above</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              - One year and above relevant work experience</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Driving Skills</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the above requirements can apply for the position by submitting a cover letter, CV and non-returnable copies of educational, work experience and other relevant documents within Five consecutive working days from the date of this announcement from Monday to Friday during working hours in the Morning from 8:30AM to 12:30 noon and in the Afternoon from 1:30 PM to 5:00 PM to the following address: International Cargo &amp; Aviation Services Head office in front of Addis Ababa Stadium, next to Ghion Hotel, Nani Building Ground Floor.
+Note:-
+Please mention the title of the position ‘Truck Driver’ on the subject line of your application/cover letter.
+Incomplete application documents will not be considered.
+The vacancy may close before the dead line if sufficient number of applicants applied for the position.
+Only applicants meeting the minimum requirements will be shortlisted and contacted.</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/v5E6bg5ADM-truck-driver</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:21 UTC</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>xPCLTmJoEe</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Chef De Partie</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Product knowledge; Team work; Ability to work in a fast-paced environment and handle stressful situations calmly; Good communication and teamwork; Good communication and interpersonal skills; Food Safety &amp; Hygiene; Desired Skill; Teamwork and collaboration; Customer-oriented with a positive service mindset.; Strong leadership and team management skills; Staff supervision</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio jobs attaching your resumes.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xPCLTmJoEe-chef-de-partie</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:24 UTC</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>X2FqGmthbN</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Edible Sales Manager</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>GETASEW AYALEW IMPORT EXPORT</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business and Administra...; Economics; Management</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Communication; Leadership</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Application Date only 7 days /from 9/26/2026 to 10/2/2026
+Interested and qualified applicants who fulfill the minimum required specifications can send their updated CV online through the following email address hr@gie.com.e
+TEL.  0960 36 85 65 Addiss Ababa
+Or you can deliver physically. Addis Ababa Bole Tropical Mall 9th Floor In front of   Alem Cinema.</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/X2FqGmthbN-edible-sales-manager</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:27 UTC</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>k1CKooK3UL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Inventory management; Teamwork and collaboration; Leadership &amp; Team Management; Leadership &amp; Coaching; Coaching &amp; Mentoring; Food Safety &amp; Hygiene; Desired Skill; Customer Servce orienation; Customer Development; Strong customer service orientation; Excellent customer service; Handle Customer Queries and Complaints</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio-jobs attaching your resumes.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k1CKooK3UL-sous-chef</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:30 UTC</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>o2U3YJpJQK</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Regional Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>GETASEW AYALEW IMPORT EXPORT</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Economics; Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Negotiation; Communication</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Application Date only 7 days /from 9/26/2026 to 10/2/2026
+Interested and qualified applicants who fulfill the minimum required specifications can send their updated CV online through the following email address hr@gie.com.et
+               TEL.  0960 36 85 65 Addiss Ababa
+Or you can deliver physically. Addis Ababa Bole Tropical Mall 9th Floor In front of   Alem Cinema.</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/o2U3YJpJQK-regional-sales-supervisor</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:33 UTC</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>zgITWUzsoL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Head Chef</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>ROMINA PLC</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Customer-oriented with a positive service mindset.; Cost Control &amp; Budgeting; Strong training and mentoring skills;; Food Safety &amp; Hygiene; Desired Skill; Customer Servce orienation; Excellent customer service; Customer-oriented with a positive service mindset.; Handle Customer Queries and Complaints; Good customer service, communications,</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>You can apply via Ethio-Jobs attaching your resumes.
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zgITWUzsoL-head-chef</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:36 UTC</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>PbD8xOwf0h</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SENIOR HR OFFICER</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>HST CONSULTING PLC</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Communication; Leadership</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Applicants who fulfill the above qualification can register as a jobseeker and apply their application by this site HST Sira – AI Powered Recruitment ,
+URL: (https://sira.hst-et.com/en/job-seeker) or submit their application in person to the Human Resources Officer at Wollo Sefer, Mina Building, 5th Floor until 9 October 2026. Only shortlisted candidates will be contacted for next stage evaluation.</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/PbD8xOwf0h-senior-hr-officer</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>n7Cpem831T</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Assistant Registrar Head for TVET Program</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>HOPE ENTERPRISE’S UNIVERSITY COLLEGE</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>First  Degree in information technology, information science, information systems, information system management, Comput</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>SUBMISSION PARAMETERS &amp; APPLICATION GATEWAYS
+Application Timeline: Strictly, within 5 working days from the date of this official announcement.
+Documentation Needed: Formal application letter, updated CV, clear copies of all credentials, and names of 3 distinct professional references.
+When applying via email: applicants MUST state the exact job position title in the subject line of the email. Applications with blank or incorrect subject lines may not be considered.
+ Physical Submission: Human Resource Office, Lebu Campus, Addis Ababa, Ethiopia.
+Campus Landmarks: Lebu/Jemo-1 neighborhood, situated adjacent to Medihanalem Church.
+Digital Application Portal: Send an integrated PDF dossier to email: hr@heuc.edu.et</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/n7Cpem831T-assistant-registrar-head-for-tvet-program</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:41 UTC</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>VQVomIVmmC</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Financial Management Specialists</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP; Basic financial and business analysis</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Financial Management Specialist ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/VQVomIVmmC-financial-management-specialists</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:44 UTC</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>FQgyo8slXl</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Monitoring and Evaluation Specialists</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Monitoring, Evaluation &amp; Learning; Organization &amp; Time Management</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Monitoring and Evaluation Specialists ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted 
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/FQgyo8slXl-monitoring-and-evaluation-specialists</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:47 UTC</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>DVvDAwIHHX</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Procurement Specialists Biomedical Engineer</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Purchasing and Procurem...</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>ERP / SAP / Oracle procurement modules; Demonstrated experience in contract negotiation, litigation, and regulatory compliance; Experience in procurement and grants financing demonstrated technical knowledge</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Procurement Specialists Biomedical Engineer ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted 
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DVvDAwIHHX-procurement-specialists-biomedical-engineer</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:50 UTC</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Zp4xW2Up5n</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Senior Advisor for Diagnostic Incubation Center Development</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>laboratory technology or in Medical Laboratory Science</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Senior Advisor for Diagnostic Incubation Center Development ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+ Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Zp4xW2Up5n-senior-advisor-for-diagnostic-incubation-center-development</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:53 UTC</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>zAhqv27hzm</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Industry Development and Public Private Partnership Initiatives</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Strategic Management; Good project management knowledge.</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Pharmaceutical Industry Development and Public Private Partnership Initiatives ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zAhqv27hzm-pharmaceutical-industry-development-and-public-private-partnership-initiatives</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:32:57 UTC</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>k95OVnMWjt</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Senior Advisors for Pharmaceutical Regulatory Systems Strengthening</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Leadership and laboratory management abilities.; Excellent analytical, communication, and leadership skills.</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Senior Advisors for Pharmaceutical Regulatory Systems Strengthening ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k95OVnMWjt-senior-advisors-for-pharmaceutical-regulatory-systems-strengthening</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:00 UTC</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>RAcCRvLngN</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Corporate Sales &amp; Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>BEKELE ABSHIRO PLC</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Excellent communication, negotiation, and leadership skills.; sales excution &amp; negotiation; • Strong coordination and networking skills</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>We invite candidates meeting the required qualifications email their CV and application letter with a single pdf to admin@bekdesgroup.com before the closing date of this announcement i.e. within ten (10) days.
+Please mention “Corporate Sales and marketing Manager ” on the subject line of your email.
+CANDIDATES WHO DO NOT FOLLOW THESE INSTRUCTIONS WILL NOT BE CONSIDERED.</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/RAcCRvLngN-corporate-sales-marketing-manager</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>18 hours ago by</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:03 UTC</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>cudD5dmBUI</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>SQL (a must) and Hive (optional); PostgreSQL databases; Desired Skill; SQL (a must) and Hive (optional); PostgreSQL databases</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/cudD5dmBUI-senior-data-scientist</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>19 hours ago by</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:06 UTC</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>IB3DWQ5nWf</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Senior Bayesian Spatial Modeller and Small Area Estimation Expert</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Programming language (R, Python, Scala, Matlab); Desired Skill; Programming language (R, Python, Scala, Matlab)</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/IB3DWQ5nWf-senior-bayesian-spatial-modeller-and-small-area-estimation-expert</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>19 hours ago by</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:09 UTC</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>PAlh2pYMfL</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Senior Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Strong knowledge of engineering codes, standards, and best practices.; Desired Skill; Programming language (R, Python, Scala, Matlab)</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/PAlh2pYMfL-senior-artificial-intelligence-engineer</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>19 hours ago by</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:12 UTC</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>EW6FTijrCD</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Data Collection &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/EW6FTijrCD-supervisor</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>19 hours ago by</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:15 UTC</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>U3MEntx6TW</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Data Collectors</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Data Collection &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/U3MEntx6TW-data-collectors</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:18 UTC</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>nOuHnRUPId</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Data analysis; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/nOuHnRUPId-supervisor</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:21 UTC</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Gk7aG56fEw</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Head Chef / Executive Chef</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>EAST AFRICAN HOLDING S.C</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Event Management</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Hotel Management, Management and Tourism,; hotel service sector; Food Safety &amp; Hygiene</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Interested applicants are invited to submit their CV and cover letter to:
+recruit@eastafricanholding.com with the subject Line "Head Chef / Executive Chef – [Your Name]"</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Gk7aG56fEw-head-chef-executive-chef</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:24 UTC</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>6Id1dDFelY</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Data Collectors</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN PUBLIC HEALTH INSTITUTE</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Data Collection &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Note  Interested applicants can register in Online through only  ethiojobs.net   send their CVs and relevant documents at the address given below within 07 days from the first appearance of the announcement
+Remarks: Please attach copies of transcripts, academic degree, work experience  letters together with the application. If not attached the copies you may be not short listed.</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6Id1dDFelY-data-collectors</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:28 UTC</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>pepCfUYDjs</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Monitoring, Evaluation and Learning (MEL) Coordinator - Oromia Region</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>GLOBAL COMMUNITIES</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Development and Project...; Economics; Agriculture</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Communication; Leadership</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why Join Us? 
+Be part of a mission-driven team making a tangible difference in Ethiopia’s agricultural sector. 
+Collaborate with diverse stakeholders and contribute to innovative, evidence-based policy solutions. 
+Enjoy a dynamic and supportive work environment.  
+Global Communities is committed to being an equal opportunity employer- It is the policy of Global Communities to ensure equal employment opportunities for all individuals, without discrimination based on age, race, religion, color, national origin, sex, gender identity, sexual orientation, genetic information, political affiliation, marital status, veteran status, non-disqualifying physical or mental disability, membership or non-membership in an employee organization, personal favoritism, or any other non-merit factors, except where otherwise required or permitted by law. 
+Interested applicants who meet the qualifications should send their application letter and Curriculum Vitae through Ethiojobs The closing date for this application is 4th October 2026.  </t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/pepCfUYDjs-monitoring-evaluation-and-learning-mel-coordinator-oromia-region</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:30 UTC</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>CiSSKiKOE2</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Market System Analyst - Oromia Region</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>GLOBAL COMMUNITIES</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Agriculture; Veterinary Services</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Communication; Leadership</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the qualifications should send their application letter and Curriculum Vitae through Ethiojobs. The closing date for this application is 4th October</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/CiSSKiKOE2-market-system-analyst-oromia-region</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:33 UTC</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>gWytoiVm67</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Senior HR - Compensation &amp; Benefit</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>REPI SOAP &amp; DETERGENT PLC</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing; Human Resource and Recr...; Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Attention to detail; Ability to multitask and prioritize effectively.</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Apply Through Email:- hana.seyum@et.wilmar-intl.com or Fill out this form - https://forms.gle/E56H3Q39pMp6zB7E9</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gWytoiVm67-senior-hr-compensation-benefit</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:36 UTC</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>C57wcCa54y</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Storekeeper &amp; Inventory Controller</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/C57wcCa54y-storekeeper-inventory-controller</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:39 UTC</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>VK9FhIzPjJ</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Sales &amp; Counseling Operator</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/VK9FhIzPjJ-sales-counseling-operator</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:43 UTC</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>CghwHtOHe3</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Contact Center Representative</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>ROPE TECHNOLOGY PLC</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Customer Service; Social Sciences and Com...; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>We recommend answering these questions before applying
+Have you completed the following level of education: Diploma or Bachelor's Degree?
+Are you qualified to work in a remote setting?
+Are you comfortable commuting to this job's location?
+We must fill this position urgently. Can you start immediately?
+Send your CV to apply@ropetechet.com or telegram @ropetech1</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/CghwHtOHe3-contact-center-representative</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:45 UTC</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>zDyzBX22AS</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Vocational Guidance, Counselor &amp; Placement Specialist</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Psychology, Guidance/Counseling or HR</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zDyzBX22AS-vocational-guidance-counselor-placement-specialist</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:49 UTC</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>09wLdvRkMa</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Metal Work Instructor (MIG, TIG, ARC &amp; Painting)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Effective communication and sociability; Attention to detail; Team work; welding</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>September 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/09wLdvRkMa-metal-work-instructor-mig-tig-arc-painting</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:52 UTC</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>LUjpOc3dhw</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Business Development Trainer</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Business Administration,</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/LUjpOc3dhw-entrepreneurship-business-development-trainer</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>qDVAqezasJ</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Finishing &amp; Painting Work Instructor</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Architecture and Constr...; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Finishing/Construction</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qDVAqezasJ-finishing-painting-work-instructor</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:33:58 UTC</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>EGVlrOUvBZ</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Electrical Installation Instructor</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Commercial Electrical Installation Training</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/EGVlrOUvBZ-electrical-installation-instructor</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:01 UTC</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>uj5apfcZdk</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Construction Engineering Department Manager</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SHINING STONE INTERNATIONAL BUSINESS PLC</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Engineering</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>12 years</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Interested applicants, can apply who met the above criteria, submit their non-returnable application with CV, copies of testimonials &amp; other relevant documents with in 10(ten) consecutive working days from the first date of this announcement to the following address below.
+ Address: - Addis Ababa Bole Medhanealem, Medhanealem Mall 6th floor Office No.601A
+Email Address: shiningstonejob@gmail.com /Telegram Page only +251924333834</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/uj5apfcZdk-construction-engineering-department-manager</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:04 UTC</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>MnNQd6oDH2</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>INVITATION FOR BIDS (IFB) Procurement of Inputs for Communal Drying Facilities</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>HANNS R. NEUMANN STIFTUNG (HRNS)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>consultancy</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>All proposals (Technical and Financial) and the required material samples must be submitted no later than October 02, 2026, at 4:00 PM, to the HRNS-Ethiopia country office at the following address:
+HRNS-Ethiopia
+Bole Sub City, Woreda 06, House Number 289/12
+Gurd Shola, near Ethio Ceramic Building
+Addis Ababa, Ethiopia
+Delivery Location for Procured Goods:
+Upon award of the contract, all materials shall be delivered to: HRNS-Ethiopia, Bahir Dar Field Office
+7. Inquiries
+For any clarifications or inquiries regarding this bid, interested vendors may contact:
+Contact Person: Gelila Daniel
+Tel: 0994013526
+Email: ethiopia@hrnstiftung.org
+Reference: Please quote the IFB Reference No. in all correspondence.
+Evaluation Criteria
+Proposals will be evaluated based on the following criteria, with a strong emphasis on quality, compliance, and value for money:
+Criteria
+Weight / Consideration
+Compliance with eligibility criteria (Licensing, TIN/VAT)
+Pass/Fail
+Compliance with Technical Specifications (including sample evaluation)
+40%
+Relevant Experience and Quality of Client References
+30%
+Financial
+30%
+HRNS-Ethiopia
+Committed to Efficiency, Transparency, and Innovation</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/MnNQd6oDH2-invitation-for-bids-ifb-procurement-of-inputs-for-communal-drying-facilities</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:07 UTC</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>K1fhlIyQtk</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Aluminum &amp; Glass Fabrication Instructor</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Door &amp; Glass Fitting</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/K1fhlIyQtk-aluminum-glass-fabrication-instructor</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:10 UTC</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>kmZHLlMyYW</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Furniture Upholstery Instructor</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Effective communication and sociability; Attention to detail; Team work; wood work Technoogy</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>September 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kmZHLlMyYW-furniture-upholstery-instructor</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:13 UTC</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Rom4c6Tp1f</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Gypsum &amp; 3D Gypsum Instructor</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>EMD ELITE CONSTRUCTION FINISHING WORKS AND VOCATIONAL TRAINING CENTER PLC</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Effective communication and sociability; Attention to detail; Team work</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>September 28th, 2026</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document Via
+📱 Telegram Application:
+Please send your CV and supporting documents via Telegram to @Mikiyas_aaa.
+📍 In-Person Application:
+Applicants may apply in person at EMD Elite Institute of Vocational and Technical Training, located in Addis Ababa, Jemo Michael, in the institution's building next to the specified landmark.
+🕐 Application Hours:
+Applications can be submitted in person during working hours, from 8:30 AM to 5:30 PM.</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Rom4c6Tp1f-gypsum-3d-gypsum-instructor</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>20 hours ago by</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:16 UTC</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>k2b1JHS4fp</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Operations Coordinator _Re-Advertise</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>GREAT ABYSSINIA GROUP</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Ability to manage many requests at once.</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>We invite qualified and motivated candidates to apply for our open positions at Great Abyssinia Group. Interested applicants are requested to submit their Application Letter and CV as a single PDF document to corporate-hr@greatabyssinia.com. Please clearly indicate the position you are applying for in the subject line of your email.
+We sincerely appreciate your interest in joining Great Abyssinia Group. Due to the high volume of applications received, only shortlisted candidates will be contacted for the next stage of the recruitment process.
+Thank you for considering a career with Great Abyssinia Group. We look forward to reviewing your application.</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k2b1JHS4fp-operations-coordinator-re-advertise</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:19 UTC</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>qP5VROoHdD</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Senior Bio Analyst</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>LONADD CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Analytics &amp; reporting (Google Analytics, insights, dashboards); Data Analysis &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Interested applicants with the appropriate qualifications and experience should submit their most recent and detailed CV only, via email to recruitment@lonadd.com , by putting Application for ‘’ Senior Bio Analyst ‘’ in the subject box.
+Only Shortlisted Candidates will be contacted
+Application Deadline September 30, 2026</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qP5VROoHdD-senior-bio-analyst</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:22 UTC</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>tRudobl93N</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Sustainability Engineer</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>WATER FOR GOOD</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Candidates who fulfill all the requirements are invited to submit their CV, copies of relevant credentials and application letter to: ethiopia@waterforgood.org within 10 consecutive days of this announcement. The position is open for both internal and external applicants.</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tRudobl93N-sustainability-engineer</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:25 UTC</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Nh9skQTikj</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Junior Accountant (Only Femail Applicants)</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>ELEGANCE IMPORT AND EXPORT PLC (YANGO ELEGANCE )</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Accounting; Account management</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should submit only their updated CV until Oct.10,2026 via telegram username: @YANGOELEGNCEJOB1</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Nh9skQTikj-junior-accountant</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:28 UTC</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>4KfEn2orv3</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Livestock Productivity Specialist – Oromia Region</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>GLOBAL COMMUNITIES</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Agriculture; Veterinary Services</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Communication; Leadership</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why Join Us? 
+Make a Meaningful Impact: Be part of a mission-driven team creating tangible, lasting change in Ethiopia's livestock development sector. 
+Collaborate with Diverse Stakeholders: Work alongside community livestock groups, private sector partners, and government institutions to co-create innovative, evidence-based solutions. 
+Grow Professionally: Thrive in a dynamic, inclusive, and supportive work environment that values continuous learning and professional development. 
+Equal Opportunity Employer 
+Global Communities is committed to equal opportunity employment. It is the policy of Global Communities to ensure equal employment opportunities for all individuals without discrimination based on age, race, religion, color, national origin, sex, gender identity, sexual orientation, genetic information, political affiliation, marital status, veteran status, non-disqualifying physical or mental disability, membership or non-membership in an employee organization, personal favoritism, or any other non-merit factors, except where otherwise required or permitted by law. 
+Interested applicants who meet the qualifications should send their application letter and Curriculum Vitae through  Ethiojobs  The closing date for this application is 4th October 2026.  
+ </t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/4KfEn2orv3-livestock-productivity-specialist-oromia-region</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:31 UTC</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>XBqNDqRMD4</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Intern Physiotherapist</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>HUMANITY &amp; INCLUSION (BRAND NAME OF HANDICAP INTERNATIONAL)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Excellent communication and interpersonal abilities.</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>Interested candidates are invited to submit an updated and concise CV to the following email address: recruitment@ethiopia.hi.org
+Please send your application with the position name by writing only “Intern Physiotherapist” in the subject line. Failure to do so will disqualify your application.
+Please note: This position is open only to fresh graduates. Candidates who are not fresh graduates are kindly requested not to apply.
+We’re committed to safeguarding and promoting child protection and expect all staff and volunteers to share this commitment. This position involves working with beneficiaries and is subject to strict safer recruitment checks. The successful candidate will be required to complete a police check and sign a self-declaration form to help us verify your suitability to work with children, including checks with past employers.
+Humanity &amp; Inclusion is an equal opportunity employer and particularly welcomes women and persons with disabilities.
+All employment decisions are made based on organizational needs, job requirements, merit, and individual qualifications. Humanity and Inclusion is committed to providing an inclusive work environment free of sexual exploitation and abuse, all forms of discrimination, any kind of harassment, sexual harassment, and abuse of authority. Therefore, all selected candidates will undergo rigorous reference and background checks.</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XBqNDqRMD4-intern-physiotherapist</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:34 UTC</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>lXsgstgeJz</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Field Sales Agent</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>CRAFT TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Marketing,</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>👉 Apply here: https://forms.gle/otkzcPytMH6Xayi6A
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lXsgstgeJz-field-sales-agent</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:37 UTC</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>xv0mpKyTSb</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Call for Consultancy Service: Development of Organizational Cost Allocation Guide line.( urgent)</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>DEVELOPMENT FOR ALL (DFA)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Application Requirements
+Interested consultants should submit:
+Technical Proposal
+Understanding of the assignment.
+Proposed methodology and approach.
+Work plan and timeline.
+Relevant experience and examples of similar assignments.
+CV(s) of the consultant/team
+Financial Proposal
+Detailed consultancy fee and applicable costs/taxes.
+Submission
+Interested and qualified consultants with a valid and renewed business license, VAT registration certificate and the ability to issue the new QR-code receipt as required by ERCA, are invited to submit their applications
+Deadline: 02/10/2026 (as soon as possible)
+Subject: Application – Consultancy for Development of Organizational Cost Allocation Strategy
+Only shortlisted applicants will be contacted.
+All application documents should be submitted electronically to: dfaprocurement@developmentforall.org</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xv0mpKyTSb-call-for-consultancy-service-development-of-organizational-cost-allocation-guide-line-urgent</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:40 UTC</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>U6vd89OlXE</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>COMMUNITY EDUCATION AND ENGAGEMENT OFFICER</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>CAREEPILEPSY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Health Officer</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Send your CV and cover letter to admin@careepilepsyethiopia.org by [2nd October 2026].
+Submit your CV, educational certificates, work experience reference letter, and employment confirmation letter as a single PDF file.
+Duty station: Addis Ababa office and travel to program sites and regions when required
+Salary: Based on organization scale</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/U6vd89OlXE-community-education-and-engagement-officer</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:43 UTC</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>lfdPpFBPtk</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Admin Assistant</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>OLY TECHNOLOGIES AND ADDISFLY TRAVEL</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Attention to detail; Business Administration,; Excellent interpersonal and communication skills; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Application Process:
+Interested candidates can apply through OLY's careers page. 
+https://oly.et/jobs
+Please submit your application for consideration — shortlisted candidates will be contacted for interviews.</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lfdPpFBPtk-admin-assistant</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:46 UTC</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>g9d5RApBdw</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Senior Sales Person , Oil &amp; Lubricants</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/g9d5RApBdw-senior-sales-person-oil-lubricants</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:49 UTC</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>qiIwmTacLk</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Electric Vehicle Business Development &amp; Technical Lead</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qiIwmTacLk-electric-vehicle-business-development-technical-lead</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:52 UTC</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>kAOqYwVwxS</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Senior Project Accountant</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kAOqYwVwxS-senior-project-accountant</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:34:56 UTC</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>bXUzJBItG0</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Senior General Accountant</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>A Degree in Accounting, Accounting &amp; Finance, or in any related business field</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/bXUzJBItG0-senior-general-accountant</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:02 UTC</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>hnwUPSb9Qa</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Senior Cost Accountant</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/hnwUPSb9Qa-senior-cost-accountant</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:07 UTC</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>W38Gfcn6UE</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Senior Roasted Coffee Sales Person</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business Development</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/W38Gfcn6UE-senior-roasted-coffee-sales-person</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>jQkAb65pvZ</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Senior Roof Sheet Sales Person</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>AMG HOLDINGS</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Management; Economics</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Good communication and teamwork</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Qualified applicants who fulfill the above requirements can apply within10 working days from the date of this announcement
+using this link: https://forms.gle/khzy4iyk19dYiPvM7
+Application deadline: 10 working days from the date of this announcement.
+For further information please call: 0970-71-88-69
+Note: Our Company will cover transport expense for candidates who will be invited for written assessment and interview</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jQkAb65pvZ-senior-roof-sheet-sales-person</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:13 UTC</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>OJbLK13IaY</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Finance Business Partner: Commercial(Re-Advert)</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>DASHEN BREWERY SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>• Creativity</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who met the MINIMUM requirements should send their application and CV to the following address from September 25 - October 1,2026. Only shortlisted applicants shall be contacted.
+Dashen Brewery Share Company, 
+E-mail to: Jobs@dashenbeer.com
+Please mention the Title of the position you applied for on the subject line of your email. </t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/OJbLK13IaY-finance-business-partner-commercialre-advert</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:17 UTC</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>xlN60MxvKS</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Procurement Officer(Re-Advert)</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>DASHEN BREWERY SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Purchasing and Procurem...</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>• Development-oriented</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who met the MINIMUM requirements should send their application and CV to the following address from September 25 -October 1,2026. Only shortlisted applicants shall be contacted.
+Dashen Brewery Share Company, 
+E-mail to: Jobs@dashenbeer.com
+Please mention the Title of the position you applied for on the subject line of your email. </t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xlN60MxvKS-procurement-officerre-advert</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:20 UTC</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>vZdGSKeanx</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Sponsorship Manager</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>STAND BY ME</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...; Communications, Media a...</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Communication; • Creativity; the ability to work with children and adults from diverse backgrounds.</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Please visit www.standby.me/ethiopiajobs to obtain an application form and to see the full job description
+Please send the completed Application form, along with your CV and a cover letter (maximum 500 words outlining your suitability for the role) to: ethiopia@standby.me. Please include ‘Sponsorship Manager’ in the subject of your email.
+We welcome applicants from all backgrounds who share our passion for making a lasting difference in the lives of children. Female candidates are highly encouraged to apply. 
+For more information about Stand by Me visit: www.standby.me
+Perks + Benefits
+Transport Allowance</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vZdGSKeanx-sponsorship-manager</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:23 UTC</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>fGQGwqidfJ</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Project officer</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN WOMEN WITH DISABILITIES NATIONAL ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Project management</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>Closing Date: 5 working days from its announcement
+The Association reserves the right to close this vacancy before the stated deadline if a suitable candidate is identified.
+In your cover letter and email application please ,mention position and include the location you are applying for(Sekota town, Chifra town and Kilte Awulaelo)
+EWDNA is an equal opportunity employer offering employment without regard to disability, race, color, religion, sex, age, etc. Qualified women with disabilities are encouraged to apply!
+Applicants must submit their CV and copies of all supporting documents in person or through Wonde2323@gmail.com copy to bitsit12birhanu@gmail.com under subject: “Application for Vacancy”. Only shortlisted candidates will be contacted.
+Hand delivery Address: Hayahulet Golagoal behind Traffic Management office.</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fGQGwqidfJ-project-officer</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:26 UTC</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1VAB4KiZRU</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Project Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>MEDECINS SANS FRONTIERES-BELGIUM (MSF-BELGIUM)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>People management; Strong leadership and people management skills.; Supply Chain &amp; Logistics Oversight; Teamwork and collaboration; Problem-solving, planning, and organizational skills.; Teamwork and Interpersonal Skills; Ability to plan and coordinate; Desired Skill; Teamwork; Safety Protocols; Behavioral Flexibility; Teamwork and collaboration</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>October 1st, 2026</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Type of contract: Full Time 
+Work Location:  Korem  
+Terms of employment:  Fixed Term contract.
+Starting Monthly Gross Salary/month: 1,509.00 USD 
+Number of Position: One 
+Other Benefits: As per the Organization Policy 
+If you are interested, please complete the Application Form via the link below: 
+ Application Form Questionnaire 👉 LINK
+  Deadline:  October 01, 2026  
+Incomplete applications will not be accepted. 
+Only applications submitted via the Application Form will be accepted.  
+Only short-listed candidates will be contacted.
+If you are short-listed, you will be invited to a technical test.
+Only the candidates that will pass the technical test will be called for an interview
+Including reference checks and verification of professional history
+Qualified Female Applicant are highly encouraged to apply.
+MSF values diversity and is committed to creating an inclusive working environment. We welcome applications from all qualified candidates regardless of disability, gender, marital status, race, color, or ethnic and national origins, religion, or belief. The protection of your personal data is important to MSF. By submitting your application, you consent to MSF using your personal data. 
+MSF operates a zero-tolerance policy for sexual exploitation, abuse, harassment, abuse of power, and discrimination. Safe Recruitment procedures apply, including reference checks and verification of professional history. MSF is committed to fostering a safe, inclusive, and respectful workplace. Adherence to MSF Behavioural Commitments is required.</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1VAB4KiZRU-project-supply-chain-manager</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:29 UTC</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>71JKYug19d</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN WOMEN WITH DISABILITIES NATIONAL ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>, Gender Studies, psychology  or related fields.</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Project management</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Closing Date: 5 working days from its announcement
+The Association reserves the right to close this vacancy before the stated deadline if a suitable candidate is identified.
+In your cover letter and email application please ,mention position and include the location you are applying for (Sekota town, Chifra town and Kilte Awulaelo)
+EWDNA is an equal opportunity employer offering employment without regard to disability, race, color, religion, sex, age, etc. Qualified women with disabilities are encouraged to apply!
+Applicants have to submit their CV and copies of all supporting documents in person or through or email Wonde2323@gmail.com copy bitsit12birhanu@gmail.com under subject: “Application for Vacancy”. Only shortlisted candidates will be contacted.
+Hand delivery Address: Hayahulet Golagoal  behind Traffic Management office .</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/71JKYug19d-program-manager</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:32 UTC</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>rvU2tF58rB</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Truck Driver Recruiter</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>BLACK RIVER EXPRESS</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Customer Service; Human Resource and Recr...; Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Part time</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Send us your CV or contact our HR team on Telegram: @hr_dep_logistics
+We look forward to hearing from you!
+ </t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/rvU2tF58rB-truck-driver-recruiter</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:35 UTC</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2R1dNSxPeR</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Manager, Tech Talent</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>KIFIYA FINANCIAL TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- hr@kifiya.com</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2R1dNSxPeR-manager-tech-talent</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:38 UTC</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>8j0HSLANr9</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>CALL FOR EXPERTS – FIRMA CONSULTING TALENT POOL</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>FIRMA CONSULTING</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Research and Developmen...; Consultancy and Trainin...; Development and Project...; Environment and Natural...; Education; Social Sciences and Com...; Natural Sciences; Economics; Agriculture</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>&amp; Social Development</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Ability to deliver quality work within deadlines; Ability to coordinate multiple tasks and work under pressure.</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Interested applicants may submit their applications through either of the two links provided below, depending on the relevant category. Please upload one merged file containing all required experience documents and supporting materials.
+NOTE: Applications submitted outside the designated links will be automatically disqualified.
+For Technical Experts under the listed sectors, please use the link below:
+https://firma-consulting.com/jobs/call-for-experts-firma-consulting-talent-pool/
+For Data Collectors, please use the link below
+https://firma-consulting.com/jobs/call-for-data-collectors/</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/8j0HSLANr9-call-for-experts-firma-consulting-talent-pool</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:41 UTC</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>0q7zVBTd3T</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>HR MANAGER</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>ADDISPAY FINANCIAL TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...; Business and Administra...; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Effective problem-solving and decision-making skills,; Analytical and problem-solving skills; Familiarity with Ethiopian commercial law, labor law, and regulatory frameworks; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document
+1, Via Email: hr@addispay.et and
+2, Telegram of this phone number 0904456834 User Name : @yod8806
+With in 10 days starting from the posted date.</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/0q7zVBTd3T-hr-manager</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:44 UTC</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>xcRqZKCKkK</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Sales Representative – Merchant Onboarding</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>ADDISPAY FINANCIAL TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Accounting and Finance; Sales and Marketing; Economics</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>sales performance managment; Effective problem-solving and decision-making skills,; Increased sales volume and net revenue; Analytical and problem-solving skills; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their Document
+1, Via Email: hr@addispay.et and
+2, Telegram of this phone number 0904456834 User Name : @yod8806
+With in 10 days starting from the posted date.</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xcRqZKCKkK-sales-representative-merchant-onboarding</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:46 UTC</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38121,7 +45677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38178,6 +45734,19 @@
       </c>
       <c r="C4" t="n">
         <v>395</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:35:48 UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="n">
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U476"/>
+  <dimension ref="A1:U483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45665,6 +45665,625 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>oaGimTgmqK</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Project Health, Safety and Environment(HSE) Officer</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>TEMER PROPERTIES</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Attention to detail; Communication &amp; Negotiation; Teamwork and collaboration</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Interested candidates are invited to submit their CV: jobs@temerproperties.com. Please write “Project Health, Safety and Environment (HSE) Officer " in the subject line.</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oaGimTgmqK-project-health-safety-and-environmenthse-officer</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>19 hours ago by</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:36 UTC</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>wd8Mrtu0Om</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Junior Battery Swapper</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Customer Servce orienation; Excellent communication and interpersonal skills.; Organization &amp; Time Management</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>To Apply Use this Link</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/wd8Mrtu0Om-junior-battery-swapper</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:39 UTC</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>FRXDnJ8yKj</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Able to Properly Use Peachtree (Record, Post, close …Accounts); Knowledge of accounting principles; Strong skill in basic accounting and book keeping.; Accounts Payable &amp; Receivable</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>To Apply this Link</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/FRXDnJ8yKj-accountant</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:43 UTC</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>iEQfaUfbgN</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Junior Accountant</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Communication; Accounting; computer skill; accuracy</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>To Apply Use this Link</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iEQfaUfbgN-junior-accountant</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:46 UTC</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>WAhlweiNIf</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Junior Customer Experience Officer</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Active listening; problem solving skill; Communication &amp; Negotiation; Customer-oriented with a positive service mindset.</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>To Apply Use this Link</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/WAhlweiNIf-junior-customer-experience-officer</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:49 UTC</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>lhSLqpqXZO</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Assembly Technician</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Attention to detail; Technical proficiency; analytical, and problem-solving skills</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>To apply use this link</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lhSLqpqXZO-assembly-technician</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>S0kX4KyMd8</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>DODAI MANUFACTURING PLC.</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Customer Service; Logistics, Transport an...; Engineering</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>al Background Requirements</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Excellent analytical, problem-solving, and reporting skills.</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>To apply you this link</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/S0kX4KyMd8-intern</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:56 UTC</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45677,7 +46296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45747,6 +46366,19 @@
       </c>
       <c r="C5" t="n">
         <v>475</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:02:58 UTC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U483"/>
+  <dimension ref="A1:U541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -46284,6 +46284,5470 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>58Y61IqCYZ</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Corporate Loan Officer</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>DIGAF &amp; MICRO-CREDIT PROVIDER SC</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Banking and Insurance; Business and Administra...; Economics; Management</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>customer communication and understanding capabilities; Ability to work under pressure and meet targets; Communication &amp; Negotiation</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Interested candidates should send their resumes along with a cover letter to our HR department at hr.admin@digafcredit.com no later than 10 days. Please specify the position you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/58Y61IqCYZ-corporate-loan-officer</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>14 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:30 UTC</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>WDlBkgZDLR</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Operation Officer</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>DIGAF &amp; MICRO-CREDIT PROVIDER SC</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...; Banking and Insurance; Economics; Management</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Team building; analytical skill;; Digital Finance Transformation; Talent Acquisition &amp; Succession Planning; sales performance managment; Creative-Performance Alignment</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Interested candidates should send their resumes along with a cover letter to our HR department at hr.admin@digafcredit.com no later than 10 days. Please specify the position you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/WDlBkgZDLR-operation-officer</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>31 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:34 UTC</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>yjK0h9SfsH</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Messenger</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>GAFAT SECURITY &amp; HRS PLC</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Send your CV and application letter with PDF format to gafatsecure@gmail.com with the subject line "Accountant – [Your Name]", or submit your application directly to Ethiojobs site.   Please mention your salary expectation and notice Period at your application letter on this format. Position: Accountant (Salary Expectation Net-----birr, Notice Period----Days)
+For further information call 0908333377</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yjK0h9SfsH-messenger</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>31 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:37 UTC</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>d7asRXrryD</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>GAFAT SECURITY &amp; HRS PLC</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>Send your CV and application letter with PDF format to gafatsecure@gmail.com with the subject line "Accountant – [Your Name]", or submit your application directly to Ethiojobs site.   Please mention your salary expectation and notice Period at your application letter on this format. Position: Accountant (Salary Expectation Net-----birr, Notice Period----Days)
+For further information call 0908333377</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/d7asRXrryD-accountant</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>33 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:40 UTC</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>5yWyJfQcyO</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Senior Tax Accountant</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GAFAT SECURITY &amp; HRS PLC</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Send your CV and application letter with PDF format to gafatsecure@gmail.com with the subject line "Senior Tax Accountant – [Your Name]", or submit your application directly to Ethiojobs site.   Please mention your salary expectation and notice Period at your application letter on this format. Position: Senior Tax Accountant (Salary Expectation Net-----birr, Notice Period----Days)
+For further information call 0908333377</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5yWyJfQcyO-senior-tax-accountant</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>35 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:43 UTC</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>zCbFioltYa</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Nutrition Officer</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>DEGA GROUP TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Application Instructions
+ONLY APPLICANTS WHO APPLIED ACCORDING TO THE FOLLOWING INSTRUCTIONS ARE ELIGBLE FOR THE POSITION!
+Application letter which includes:
+Your FULL NAME
+POSITION for which you applied (Nutrition Officer)
+Your telephone number
+Attach all necessary educational testimonies with your application letter
+How to Apply
+Interested applicants can submit their CV &amp; other relevant documents via beza@degagrouptrading.com 5  days of this announcement.</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zCbFioltYa-nutrition-officer</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>40 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:46 UTC</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>nldHbutdIZ</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Security  Guard Lead</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>CURE INTERNATIONAL INC</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>security and safety</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates are welcome to submit their applications, along with their CV and other supporting documents, to the Human Resources department at Cure Hospital within 10 days of the announcement. Please note that Cure Hospital reserves the right to reject any application or pursue other options.
+For more information, please call 011-1-237767.
+Address: The Cure Hospital, near Hamle 19 Park, Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/nldHbutdIZ-security-guard-lead</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:48 UTC</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Y9LMcxkzOP</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>PROJECT COORDINATOR</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>HAKID ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Public-speaking; Superior command of written and spoken skills in English is mandatory; • Strong coordination and networking skills; Ability to deliver quality work within deadlines; Ability to coordinate multiple tasks and work under pressure.; ability to build strong working relationships; project management, budgeting, and reporting.; Youth development, Sport management, Physical education</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates who fulfill the above-stated criteria are warmly invited to submit their updated CV and a tailored Cover Letter detailing their relevant experience in the non-governmental sector.
+Applications must be submitted via email to our dedicated recruitment mailbox:
+📩 hakidetvacancy@gmail.com
+Important Note: Please clearly indicate the exact job title you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Y9LMcxkzOP-project-coordinator</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:51 UTC</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>BCztLX5rSa</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>SECRETARY AND OFFICE ADMINISTRATOR</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>HAKID ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Proficiency in MS Office (Word, Excel, PowerPoint); Ability to deliver quality work within deadlines; Basic Accounting Knowledge; Ability to coordinate multiple tasks and work under pressure.; Basic Data/Record-keeping.; Ability to plan and coordinate; Communication, coordination, networking and facilitation skills</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates who fulfill the above-stated criteria are warmly invited to submit their updated CV and a tailored Cover Letter detailing their relevant experience in the non-governmental sector.
+Applications must be submitted via email to our dedicated recruitment mailbox:
+📩 hakidetvacancy@gmail.com
+Important Note: Please clearly indicate the exact job title you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BCztLX5rSa-secretary-and-office-administrator</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:55 UTC</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>BDEbCXPMOd</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SICHEN PLASTIC PRODUCT MANUFACTURING PLC</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Strong knowledge of modern kitchen equipment and cooking techniques</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>ETB 10,000</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply through Ethiojobs</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BDEbCXPMOd-cook</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:23:58 UTC</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>un4VkC89Io</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>HR Officer</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>BEKELE ABSHIRO PLC</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>ERP / HRIS implementation experience; HR Policies &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>October 17th, 2026</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N.B: Experience in corporate company is preferable
+ Submit your CV via email: admin@bekdesgroup.com
+ Note: Use "Hr officer ” as the subject line of your email
+Please note that only short-listed candidates will be contacted
+ </t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/un4VkC89Io-hr-officer</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:00 UTC</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>FLT5heyg7X</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Graphics Designer</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>COMMERCIAL NOMINEES PLC</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Creative Arts</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Digital printing; Communication; Graphic User Interfaces (GUI); Adobe Photoshop, InDesign; Attention to detail; • Creativity; Desired Skill; Attention to detail; • Creativity</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Applicants who meet the minimum requirements mentioned above can registered in person at the Commercial Nominees Head Office, 7th floor, Human Resources Directorate, which is located behind Bole Shopping Center with the original proof of education, grade 8th and work experience or via cnhrvacancy@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/FLT5heyg7X-graphics-designer</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:03 UTC</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>QsgrpFRzDn</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Sanitary Forman/ Plumber</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>METROPOLITAN REAL ESTATE PLC</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Engineering; Environment and Natural...</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Engineering/COTM; Sanitation</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to send their updated CV and Cover letter outlining your relevant experience and achievements to Hr@metropolitanaddis.net.
+Please indicate “Sanitary Forman/ Plumber” in the subject line of your email.
+Applications will be reviewed on a rolling basis. Only shortlisted candidates will be contacted.
+Metropolitan Real Estate PLC (MRE) is an equal opportunity employer committed to attracting talented professionals who are passionate about marketing excellence and delivering business growth.</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/QsgrpFRzDn-sanitary-forman-plumber</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:07 UTC</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>UVcwBXeNLb</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>GO SUPER APP (BRIDGE COMMUNICATION PLC)</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management (CRM); Communication; Communication &amp; Negotiation; Additional automotive sales training is an advantage; Desired Skill; Presentation; Creative thinking; More Jobs by Go Super App (Bridge Communication PlC); Business Development Specialist; Office; September 30th, 2026; Head of Marketing &amp; Communications – Go Super App; Office; September 30th, 2026; Head of Human Resources</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>October 26th, 2026</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/UVcwBXeNLb-sales-representative</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:11 UTC</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>aG39sdxa9L</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Van Driver ለ ደቡብ ምዕራብ ቀጠና ጽ/ቤት (ቦንጋ ከተማ)</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>DASHEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>automotive</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>https://career55.sapsf.eu/sfcareer/jobreqcareer?jobId=2403&amp;company=dashenbank
+ጥያቄ ወይም ማብራሪያ ከፈለጉ 
+047-331-2754</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/aG39sdxa9L-van-driver</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:14 UTC</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>6h7QzYnAIH</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Consultancy Service – Local developer of Digital Market Intelligence System (DMIS)</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>GIZ SEQUA GGMBH</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Please send us a cover letter, your practical experience in designing and developing DMIS, relevant resumes &amp; company profile, and your daily fee expectation in ETB Birr. Please provide a clear description of achievements created for consulted BMOs/chambers/associations/companies in the past.
+Please send us your application by no later than October 15th, 2026, to vacancies.pss@sequa.de with the subject line "ETH-1148 Consultancy Service - DMIS development”.</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6h7QzYnAIH-consultancy-service-local-developer-of-digital-market-intelligence-system-dmis</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:17 UTC</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>JPLQ1MPxnW</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>IT and System Manager, Solar Installation Engineer, HR and Admin Assistant</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>GREEN SCENE ENERGY PLC</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Solar Enginering</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>For - IT and System Manager
+Apply online only through this link: https://form.jotform.com/262673740697066
+For - Solar Installation Engineer
+Apply online only through this link: https://form.jotform.com/262671833648063
+For - HR and Admin Assistant
+Apply online only through this link: https://form.jotform.com/262673846805064
+Perks + Benefits
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JPLQ1MPxnW-it-and-system-manager-solar-installation-engineer-hr-and-admin-assistant</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:21 UTC</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>lfdAOPZhMa</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Head of People &amp; Culture</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>GRANT THORNTON ADVISORY ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>HRIS and Technology; human resources Managment; Analytical thinking and problem-solving skills.; Good communication and interpersonal skills; HR Policies &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>Fill the online application form by following the below link by inserting this vacancy code: GTE017/09/2026
+https://forms.office.com/r/Wfijv7sv10
+Only shortlisted applicants who filled online application form will be contacted.
+Female applicants are highly encouraged to apply.
+Grant Thornton Ethiopia is an equal opportunity employer. We value diversity and inclusion and welcome applications from all qualified candidates.</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lfdAOPZhMa-head-of-people-culture</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:23 UTC</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>7qLwNLSeaw</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Senior Manager – Service &amp; Parts</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Warehouse, Supply Chain...; Business and Administra...; Automotive; Retail, Wholesale and D...</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>automotive; Automotive Service Shop; Automotive Shop Car; Performance Management (KPIs); Additional automotive sales training is an advantage; Business Management, Accounting,; Automotive Repair</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>Qualified candidates are invited to apply by submitting their updated CV along with relevant qualification documents.</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/7qLwNLSeaw-senior-manager-service-parts</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:27 UTC</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>JEvFcquEq4</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Senior Manager, Talent Management</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>KIFIYA FINANCIAL TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Human Resource and Recr...; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- hr@kifiya.com</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JEvFcquEq4-senior-manager-talent-management</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:30 UTC</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>jfn58BBrw6</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Area Sales Manager / Network Development Specialist – 2W &amp; 3W Vehicles (Petrol &amp; EV)</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Retail, Wholesale and D...; Automotive</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Sales reporting; Sales Leadership; sales excution &amp; negotiation; sales performance managment; Sales analytics and performance reporting; Increased sales volume and net revenue</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Qualified applicants can apply by attaching their updated CV and relevant qualification documents.</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jfn58BBrw6-area-sales-manager-network-development-specialist-2w-3w-vehicles-petrol-ev</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:33 UTC</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>vR0HvMmxDF</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Accountant – Harar Branch</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vR0HvMmxDF-accountant-harar-branch</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:36 UTC</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>bcGJQ0ZYBQ</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Store Keeper</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/bcGJQ0ZYBQ-store-keeper</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:39 UTC</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>NoVowyDcwn</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Resource and Asset Management (RAM) Senior Officer</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GSG MINING PLC</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>September 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Application
+Interested and qualified candidates are invited to submit their updated CV and application through the company’s designated recruitment channel. Please ensure that your application clearly demonstrates relevant experience and capability for the responsibilities of the position.
+Application Deadline: Sep 30, 2026
+Application Email: hr@allgsgroup.com; gm.gsgmining.et@allgsgroup.com; lh.gsg.et@allgsgroup.com
+Duty Station: Addis Ababa, Ethiopia and Frequent Site Visit in Project Sites, Ethiopia
+Only shortlisted candidates will be contacted.
+GSG MINING PLC</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NoVowyDcwn-resource-and-asset-management-ram-senior-officer</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:42 UTC</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>T2ZhZrUx3j</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Primay School Teachers</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>ETHIO EXCELLENCE ACADEMY</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Apply Now</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Microsoft Office (Excel, Word, PowerPoint); Excellent communication and interpersonal abilities.</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Interested applicants are kindly requested to submit their applications in person, accompanied by a non-returnable copy of their application documents, including a cover letter, curriculum vitae, educational credentials, work experience letter, and any other relevant documents.
+Address: Akaki Kality Sub city 
+Akaki Alembank Branch: Infront of Yeshi Total near the taxi station and beside Awash Bank
+Phone Number:  +251967112222 | +251966112222 | +251969842424 
+Email: director@eeaacademy.com
+www.eeaacademy.com
+Map: https://maps.app.goo.gl/ED1j3aaeRbjFMTtb9</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/T2ZhZrUx3j-primay-school-teachers</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:45 UTC</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>lIojuDvhe1</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>English Teacher</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>ETHIO EXCELLENCE ACADEMY</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Apply Now</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Oral and written communication; Creative thinking; Desired Skill; Teamwork; Technological &amp; digital literacy</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>Ethio Excellence Academy – Akaki Alembank Branch invites interested applicants to apply in person with a non-returnable copy of their CV at our campus.
+Alternatively, you may send your CV via email to: director@eeaacademy.com
+Address: Akaki Alembank Branch, Alembank Taxi Station, in front of Yeshi Total.
+Phone: +251 967 112 222 | +251 973 916 051</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lIojuDvhe1-english-teacher</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:48 UTC</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>oUFosBqsYP</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Senior Strategy and Change Management Officer II</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN CAPITAL MARKET AUTHORITY</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Economics; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Strategic thinking; problem solving skill; • Creativity; Development Studies, Project Management, Economics, Business Administration,; Desired Skill; • Creativity; Strategic Planning &amp; Execution; Supplier/vendor management</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Please submit your CV and application letter through Ethiojobs, and ensure you also complete the Online Application Form.
+All three components are mandatory; applications missing any of these will not be considered.
+Only shortlisted candidates will be contacted by ECMA.</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oUFosBqsYP-senior-strategy-and-change-management-officer-ii</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:51 UTC</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>xf2TLaFHj9</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Senior Pre Sales Engineer</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>MOTI ENGINEERING PLC</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Basic knowledge of user interface communication; Communication &amp; Negotiation; Problem solving Organizational Skill. Excellent written and verbal communication skills; Client Follow-up &amp; Communication</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>October 11th, 2026</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Only qualified &amp; interested candidates are encouraged to apply for this position: 
+1.    For online applicants, please attaché and send: 
+•  Your updated CV &amp; credentials copy, stating the position (Senior Presales Engineer) in the subject line; and mail to recruitment@motiengineering.com, making CC to “vacancy@motiengineering.com”
+o    Or 
+1.2.    physically drop:
+•    Your updated CV &amp; Copy of credentials at our office located at: “Africa Avenue, Mega House/building, 3rd floor, office No 309/ 307. For further Information, you can call /Contact on: - 0114702142/0114701635/0114702015
+ </t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xf2TLaFHj9-senior-pre-sales-engineer</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:54 UTC</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>tVBNL99Vob</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>French Teacher</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>FLIPPER INTERNATIONAL SCHOOL PLC</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Apply Now</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>• Strong coordination and networking skills; Desired Skill; Communication; Problem solving Organizational Skill. Excellent written and verbal communication skills; Excellent written and verbal communication skills.</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Interested candidates should send a CV, copies of certificates, and a cover letter to jobs@flipperschools.com. Shortlisted candidates will be invited for an interview, which will include an assessment of their French proficiency.
+Perks + Benefits
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tVBNL99Vob-french-teacher</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:24:57 UTC</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2mQ6hxb5sZ</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Kindergarten Teachers</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>ETHIO EXCELLENCE ACADEMY</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Apply Now</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Creative thinking; the ability to work with children and adults from diverse backgrounds.; social work, Sociology, Psychology, Child Development, Law, Public Health,; Desired Skill; Excellent communication, negotiation, and leadership skills.; • Creativity; Excellent interpersonal and communication skills; the ability to work with children and adults from diverse backgrounds.</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>Interested applicants are kindly requested to submit their applications in person, accompanied by a non-returnable copy of their application documents, including a cover letter, curriculum vitae, educational credentials, work experience letter, and any other relevant documents.
+Address: Akaki Kality Sub city 
+Akaki Alembank Branch: Infront of Yeshi Total near the taxi station and beside Awash Bank
+Phone Number:  +251967112222 | +251966112222 | +251969842424 
+Email: director@eeaacademy.com
+www.eeaacademy.com
+Map: https://maps.app.goo.gl/ED1j3aaeRbjFMTtb9
+Perks + Benefits
+Housing
+Transport Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2mQ6hxb5sZ-kindergarten-teachers</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:00 UTC</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>KzZy3pwFex</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>HR and Admin Manager</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Human Resource and Recr...; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/KzZy3pwFex-hr-and-admin-manager</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:03 UTC</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>t4L8bmorE1</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Executive Secretary</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ELEGANCE IMPORT AND EXPORT PLC (YANGO ELEGANCE )</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Secretarial Science, Management, Business Administratio</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should submit only their Updated CV until Oct.10,2026 via this link:
+https://docs.google.com/forms/d/e/1FAIpQLSeKvY4UBfQYrORn_-eaF475n77J8XF-JF_pmyCykxB948iJIQ/viewform?usp=dialog</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/t4L8bmorE1-executive-secretary</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:06 UTC</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>izS5Pqww0s</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Machine Operator</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>TVET Level II or above in Mechanical, Industrial Operations, or a related technical field.</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/izS5Pqww0s-machine-operator</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:09 UTC</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>u8c3fZdWPd</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Senior Electrician</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Engineering</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/u8c3fZdWPd-senior-electrician</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:12 UTC</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>0Lkn9aSpQF</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Maintenance Manager</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/0Lkn9aSpQF-maintenance-manager</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:15 UTC</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>ysahzu3Ht3</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Horizontal Baler Operator</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ysahzu3Ht3-horizontal-baler-operator</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:18 UTC</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>hkAYgAxETU</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Grapple Machine Operator</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/hkAYgAxETU-grapple-machine-operator</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:21 UTC</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>SgHlWPVJ0v</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Mechanical Technician/Mechanic</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/SgHlWPVJ0v-mechanical-technicianmechanic</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:24 UTC</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>yzDPqQLVsG</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Polysheet Machine Jr. Operator</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>ABBAHAWA TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the requirements for the position can submit their applications via E-mail address  recruitment@abbahawa.com OR in person having their necessary documents along with CV within 5 days from the date of the announcement to HR Division-Zaki or ONE JUICE AND SNACK MANUFACTURING /Daleti/ OR Abbahawa Head Office Around Lebu along the ring road from Garment to Mebrat Square.
+Application date Sept-28-Oct 10-2026
+Contact Address  ……….0114-199629/0114-197928</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yzDPqQLVsG-polysheet-machine-jr-operator</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:27 UTC</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>vboqKfUuha</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Operator, Bottle Preform</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>ABBAHAWA TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the requirements for the position can submit their applications via E-mail address  recruitment@abbahawa.com OR in person having their necessary documents along with CV within 5 days from the date of the announcement to HR Division-Zaki or ONE JUICE AND SNACK MANUFACTURING /Daleti/ OR Abbahawa Head Office Around Lebu along the ring road from Garment to Mebrat Square.
+Application date Sept-28-Oct 10-2026
+Contact Address  ……….0114-199629/0114-197928</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vboqKfUuha-operator-bottle-preform</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:30 UTC</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>0lHedlZ3Yw</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Call for Applications: Research Consultant - Climate-Related Urban Migration, Djibouti</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>LIFE &amp; PEACE INSTITUTE (LPI)</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Research &amp; Analysis; Desired Skill; Research &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>How to apply
+Interested applicants should submit a CV, three writing samples, and a 1 page cover letter that
+addresses with details of: research experience, experience leading data collection teams, reasons for interest in this project, and the consultant's daily rate. The application package should be submitted to procurement.addisababa@life-peace.org by 06 October 2026. Any questions not covered in this ToR should be directed to Caroline Katuma at caroline.katuma@life-peace.org.</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/0lHedlZ3Yw-call-for-applications-research-consultant-climate-related-urban-migration-djibouti</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:33 UTC</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>BW7WL7AWXn</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Call for Applications: Research Consultant - Climate-Related Urban Migration, Djibouti</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>LIFE &amp; PEACE INSTITUTE (LPI)</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Research &amp; Analysis; Desired Skill; Research &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>How to apply
+Interested applicants should submit a CV, three writing samples, and a 1 page cover letter that
+addresses with details of: research experience, experience leading data collection teams, reasons for interest in this project, and the consultant's daily rate. The application package should be submitted to procurement.addisababa@life-peace.org by 06 October 2026. Any questions not covered in this ToR should be directed to Caroline Katuma at caroline.katuma@life-peace.org.</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BW7WL7AWXn-call-for-applications-research-consultant-climate-related-urban-migration-djibouti</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:37 UTC</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>ISJcTCHkTr</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Production Manager</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ISJcTCHkTr-production-manager</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:40 UTC</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>dmblr5TITF</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Sr. Operator, Bottle Preform</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>ABBAHAWA TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Environment and Natural...; Natural Sciences; Health Care</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the requirements for the position can submit their applications via E-mail address  recruitment@abbahawa.com OR in person having their necessary documents along with CV within 5 days from the date of the announcement to HR Division-Zaki or ONE JUICE AND SNACK MANUFACTURING /Daleti/ OR Abbahawa Head Office Around Lebu along the ring road from Garment to Mebrat Square.
+Application date Sept-28-Oct 10-2026
+Contact Address  ……….0114-199629/0114-197928</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/dmblr5TITF-sr-operator-bottle-preform</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:43 UTC</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>HpPETSUyAk</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Call for Applications: Research Consultant – Climate-Related Urban Migration, Dire Dawa, Ethiopia</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>LIFE &amp; PEACE INSTITUTE (LPI)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Research skills</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>How to apply
+Interested applicants should submit a CV, three writing samples, and a 1 page cover letter that
+addresses with details of: research experience, experience leading data collection teams, reasons for interest in this project, and the consultant's daily rate. The application package should be submitted to procurement.addisababa@life-peace.org by 06 October 2026. Any questions not covered in this ToR should be directed to Caroline Katuma at caroline.katuma@life-peace.org.</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/HpPETSUyAk-call-for-applications-research-consultant-climate-related-urban-migration-dire-dawa-ethiopia</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:25:52 UTC</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>OjUBFPmJZr</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>RDF Production Line Operator</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>KUBIK ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>TVET Level II or above in a relevant technical field, preferably Mechanical, Electrical, Industrial Operations, or relat</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through :- HR@buildkubik.com</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/OjUBFPmJZr-rdf-production-line-operator</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:07 UTC</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>tOuPwpjhbb</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Re-Advertise Digital Payment Officer I (For definite period of one year)</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>ETHSWITCH S.C.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>al Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Attention to detail; Strong teamwork and willingness to learn.; Excellent communication and interpersonal skills.</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>Qualified candidates are invited to submit their application with non-returnable CV, educational qualifications and work experience to hr@ethswitch.com, stating the title of the position clearly on the subject line. Qualified female applicants are highly encouraged.
+*Please be aware that it is mandatory to attach your credentials (educational qualifications and work experience) along with your CV. Submitting only your CV is not sufficient.
+*Please be advised that all applicants’ Educational Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tOuPwpjhbb-re-advertise-digital-payment-officer-i-for-definite-period-of-one-year</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:18 UTC</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>3bawDOJEo4</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Senior Accountant</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>DESTA PLC</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP; Accounts Payable &amp; Receivable</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>We invite candidates meeting the required qualifications email their CV and application letter with a single pdf to admin@bekdesgroup.com before the closing date of this announcement i.e. within ten (10) days.
+Please mention “Senior Accountant” on the subject line of your email.
+CANDIDATES WHO DO NOT FOLLOW THESE INSTRUCTIONS WILL NOT BE CONSIDERED</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3bawDOJEo4-senior-accountant</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:28 UTC</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>DgA940C8G0</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Translation of the Foundational Helping Skills Training Manual and REACHNow Training Manual into Amharic</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>SOS CHILDREN'S VILLAGES IN ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>Interested vendors should submit a complete proposal comprising:
+Technical Proposal
+Company profile and relevant experience.
+Methodology and implementation approach.
+Detailed work plan and timeline.
+Proposed team and their qualifications.
+Financial Proposal
+Detailed cost breakdown (license fees, customization, training, support, etc.).
+Separate indication of taxes and optional/recurring costs
+Validity of the financial offer.
+ Annexes
+List of similar projects with three contactable client references.
+CVs of proposed team members.
+Any certifications, partnerships, or proof of compliance
+Submission Details
+Proposals must be submitted electronically to:
+Subject line: “Translation of the Foundational Helping Skills Training Manual and REACHNow Training Manual into Amharic”
+E-Mail: procurement@sos-ethiopia.org</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DgA940C8G0-translation-of-the-foundational-helping-skills-training-manual-and-reachnow-training-manual-into-amharic</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:32 UTC</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>HV0EFN0NkJ</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Executive I – Accounts (Maternity Cover)</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>KADISCO PAINT AND ADHESIVE INDUSTRY S.C</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract Details
+Position: Executive I – Accounts
+Contract Type: Fixed-Term – 4 Months (Maternity Cover)
+Experience: 0–2 Years
+Joining: Immediate
+Interested candidates who meet the above requirements are invited to submit their updated CV for consideration through open.vacancy@kadiscopaint.com Please mention the job title “Executive I – Accounts” in the subject line of the email.
+ </t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/HV0EFN0NkJ-executive-i-accounts-maternity-cover</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:35 UTC</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>yhMsnLzbZx</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Executive Secretary</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>YES EXPRESS PLC</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; analytical skill;; Microsoft Office (Excel, Word, PowerPoint)</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to submit their updated CV through our Telegram channel:
+YESEHRD – https://t.me/YESEHRD
+Only shortlisted candidates will be contacted.
+Phone number; 0998000002/0998000011</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/yhMsnLzbZx-secretary</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:38 UTC</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>6VJA7GcTAR</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Cost and Tender Engineer</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>ASER CONSTRUCTION PLC</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Engineering; Architecture and Constr...; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the above requirements can submit their application   via  hr@aserplc.com
+ Please clearly specify job positions you apply in the subject line and all your documents has to be compiled in one PDF format, or submit in person with non-returnable Copies of supporting documents.
+Address: - (Gergi Emperial, Besides Mega Painting Factory).
+for further information please use Tel No - 011-662-03-57 / 0116-39-20-64 Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6VJA7GcTAR-cost-and-tender-engineer</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:41 UTC</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>x4ztO8maHd</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>ASER CONSTRUCTION PLC</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Engineering; Architecture and Constr...; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Interested applicants who fulfill the above requirements can submit their application   via  hr@aserplc.com
+ Please clearly specify job positions you apply in the subject line and all your documents has to be compiled in one PDF format, or submit in person with non-returnable Copies of supporting documents.
+Address: - (Gergi Emperial, Besides Mega Painting Factory).
+for further information please use Tel No - 011-662-03-57 / 0116-39-20-64 Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/x4ztO8maHd-contract-engineer</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:44 UTC</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>6SolRSVWF1</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Customer Care / Receptionist (Female Applicants Only )</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>DESTINY LINE TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>; Grade 10 and above</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Time management; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>October 27th, 2026</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>Address
+Summit Condominium, Ber 3
+Around Sunshine Philanthropy / Aregawuyan Merja Derejet or Ashara
+To Apply / Contact
+Temesgen — 0929 106 345
+Interested and qualified candidates are encouraged to contact us for more information and application.</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6SolRSVWF1-customer-care-receptionist-female-applicants-only</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:47 UTC</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>zeOdIIGbHB</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Injection Molding Machine Technical Expert</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>KROMOTO MANUFACTURING PLC</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Dire Dawa</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Six years and above</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Oral and written communication; Team work</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Applicants are requested to submit their original and non-returnable photocopies of their documents to the organization's administrative office within 10 consecutive working days from the date of publication of this announcement, or to register online at myzemaye@gmail.com
+Note:
+Our address is Dire Dawa Industrial Village. For more information, you can call 025-411-15-25.
+The organization (Kromoto Manufacturing PLC)</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zeOdIIGbHB-injection-molding-machine-technical-expert</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:50 UTC</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>BLvSamDa9N</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>DESTA PLC</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Attention to detail; Advanced Accounting Knowledge; Basic Accounting Knowledge</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N.B: Experience in manufacturing company is preferable
+Submit your CV via email: admin@bekdesgroup.com
+ Note: Use "Accountant” as the subject line of your email
+Please note that only short-listed candidates will be contacted
+ </t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BLvSamDa9N-accountant</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>7 hours ago by</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:52 UTC</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>vTcqQjGyCb</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>IEC/SBCC Graphic Designer and Illustrator</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>PATH MINISTRIES INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Adobe Photoshop, InDesign; • Creativity; Ability to coordinate multiple tasks and work under pressure.; ability to build strong working relationships; Desired Skill; ability to build strong working relationships</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>65,000</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Required Application Documents
+Interested applicants must submit the following:
+Updated Curriculum Vitae
+The CV should clearly indicate:
+Educational background.
+Professional experience.
+Relevant consultancy assignments.
+Technical skills.
+Software proficiency.
+Language skills.
+Contact information.
+B. Professional Portfolio
+Applicants must submit a portfolio demonstrating relevant previous work.
+The portfolio should preferably include:
+Original illustrations.
+IEC materials.
+BCC/SBCC materials.
+Child-friendly educational materials.
+Training-material illustrations.
+Posters and brochures.
+Booklets and manuals.
+Infographics.
+Community communication materials.
+Multilingual designs.
+NGO or development-sector communication materials.
+Project visibility materials.
+Applicants should clearly identify which works were personally designed or illustrated by them.
+C. Previous Organizations and Client Experience
+Applicants must provide information on organizations, institutions, companies, or projects for which they have previously provided similar services.
+For each relevant assignment, applicants should provide:
+Name of organization/client.
+Type of organization.
+Assignment or project title.
+Nature of work performed.
+Main deliverables produced.
+Period of assignment.
+Contact person.
+Contact telephone number and/or email address.
+PATH Ethiopia may contact previous clients to verify experience, performance, and quality of work.
+D. Letters of Acknowledgement or Recommendation
+Applicants should submit relevant:
+Letters of acknowledgement.
+Recommendation letters.
+These should preferably relate to graphic design, illustration, IEC/SBCC, training-material development, communication, or similar assignments.
+E. Technical Proposal
+Applicants should submit a brief technical proposal explaining:
+Their understanding of the assignment.
+Their proposed approach to developing IEC/SBCC materials.
+Their approach to technical review and revisions.
+Their approach to culturally appropriate illustration.
+Their availability for weekly and monthly meetings.
+Their availability for field visits when required.
+Applicants should combine their application documents into clearly named files and submit them by email to:
+pathinternational.jobs@gmail.com
+The email subject line should be: pathinternational.jobs@gmail.com
+Application – IEC/SBCC Graphic Designer and Illustrator</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vTcqQjGyCb-iecsbcc-graphic-designer-and-illustrator</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>8 hours ago by</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:26:58 UTC</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2ZkipcEn1A</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Research Admin Assistant Officer I</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>ARMAUER HANSEN RESEARCH INISTITUTE(AHRI)</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Understanding of Clerical and Secretarial Principles</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>How to Apply: Submit your application letter (detailing your motivation and suitability), CV (maximum of three pages with a clear indication of your educational background and experience), and copies of your documents and certificates as one PDF file.</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2ZkipcEn1A-research-admin-assistant-officer-i</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>13 hours ago by</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:27:01 UTC</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -46296,7 +51760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46379,6 +51843,19 @@
       </c>
       <c r="C6" t="n">
         <v>482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:27:02 UTC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>58</v>
+      </c>
+      <c r="C7" t="n">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U541"/>
+  <dimension ref="A1:U569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -51748,6 +51748,2629 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>3bUtqNg9OI</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>IT Auditor</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>AMHARA BANK S.C.</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Telecommunications</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Auditing skills; Audit &amp; Compliance Management; Audit Coordination; Audit Documentation; Audit Reporting</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>NB:
+Female applicants highly encouraged
+Only shortlisted candidates will be communicated
+Hard copy or physical applications will not be accepted
+The Bank has the right to cancel the post advertised
+Interested applicants fulfilling the above requirements are invited to apply within five (5) Consecutive days from September 28, 2026to October 02, 2026.
+https://vacancy.amharabank.com.et/.</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3bUtqNg9OI-it-auditor</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>10 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:33 UTC</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>lVcLdxQAGQ</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Senior IT Auditor (Re-advertised)</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>AMHARA BANK S.C.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Customer Service; IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Auditing skills; Audit &amp; Compliance Management; Audit Coordination; Audit Documentation; Audit Reporting</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>NB:
+Female applicants highly encouraged
+Only shortlisted candidates will be communicated
+Hard copy or physical applications will not be accepted
+The Bank has the right to cancel the post advertised
+Interested applicants fulfilling the above requirements are invited to apply within five (5) Consecutive days from September 28, 2026to October 02, 2026.
+https://vacancy.amharabank.com.et/.</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lVcLdxQAGQ-senior-it-auditor-re-advertised</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>20 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:36 UTC</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>YdnWUnjVPz</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Senior Service Quality Assurance Officer</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>AMHARA BANK S.C.</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Banking and Insurance; Business and Administra...; Economics</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Quality control; Quality assurance; Quality assurance and compliance focus</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>October 2nd, 2026</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>NB:
+Female applicants highly encouraged
+Only shortlisted candidates will be communicated
+Hard copy or physical applications will not be accepted
+The Bank has the right to cancel the post advertised
+Interested applicants fulfilling the above requirements are invited to apply within five (5) Consecutive days from September 28, 2026to October 02, 2026.
+https://vacancy.amharabank.com.et/.</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/YdnWUnjVPz-senior-service-quality-assurance-officer</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>20 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:39 UTC</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>1zXFys9G3H</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Financial Management Systems Expert</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>NATIONAL ELECTION BOARD OF ETHIOPIA(NEBE)</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Financial planning; Accounting; xperience and knowledge of IFMIS, IFRIS is required</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>INTERESTED APPLICANTS ARE INVITED TO SEND NON-RETURNABLE:
+Application letter that explains why you fit for the post and updated CV, and Three work related referees;
+Application letter &amp; resume should be saved by full name of Applicants.
+Only short-listed candidates will be contacted for further screening.
+Those who are interested can only apply through the attached link               
+https://nebe-election.org/apply  within 10 days from this announcement.
+Female candidates are encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1zXFys9G3H-financial-management-systems-expert</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:42 UTC</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>JkNAt5FtQR</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Junior Budget Expert I</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>NATIONAL ELECTION BOARD OF ETHIOPIA(NEBE)</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Budgeting</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      INTERESTED APPLICANTS ARE INVITED TO SEND NON-RETURNABLE:
+Application letter that explains why you fit for the post and updated CV, and Three work related referees;
+Application letter &amp; resume should be saved by full name of Applicants.
+Only short-listed candidates will be contacted for further screening.
+Those who are interested can only apply through the attached link               
+https://nebe-election.org/apply within 10 days from this announcement.
+Female candidates are encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JkNAt5FtQR-junior-budget-expert-i</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:45 UTC</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>XBIqNMTnRU</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Graduate in Training (GIT) - Sales</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>HABESHA BREWERIES SC.</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Continuous learning; Result Driven; customer communication and understanding capabilities; Teamwork and collaboration; action driven</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above criteria should submit their updated CV and academic transcripts by October 10, 2028.
+Application Tip: While not a strict requirement, candidates are highly encouraged to detail any extracurricular achievements, club roles, or volunteer experience in their CV or cover letter to maximize their chances.
+Habesha Breweries is an Equal Opportunity Employer. Only shortlisted candidates will be contacted for the assessment phase.</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XBIqNMTnRU-graduate-in-training-git-sales</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:48 UTC</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Ddyortlph0</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Technology Product Manager</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>AMERICAN COLLEGE OF TECHNOLOGY (ACT)</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Technology; Development and Project...</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Good knowledge of manufacturing systems, ERP tools (SAP), and digital production platforms.; Ability to support Resident Engineer in technical and administrative tasks; Computer Science, Information System, Information Technology, Computer Engineering; Computer Science, Software Engineering, Information Technology; Desired Skill; Product knowledge; Good knowledge of manufacturing systems, ERP tools (SAP), and digital production platforms.; Computer Science, Information System, Information Technology, Computer Engineering; Computer Science, Software Engineering, Information Technology</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>October 17th, 2026</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should submit their CV, cover letter, and copies of academic credentials via website actjobs</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Ddyortlph0-technology-product-manager</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:51 UTC</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>TEA3tPEr88</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Senior Finance Expert</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>NATIONAL ELECTION BOARD OF ETHIOPIA(NEBE)</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>7 years</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP; xperience and knowledge of IFMIS, IFRIS is required; Accounts Payable &amp; Receivable</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      INTERESTED APPLICANTS ARE INVITED TO SEND NON-RETURNABLE:
+Application letter that explains why you fit for the post and updated CV, and Three work related referees;
+Application letter &amp; resume should be saved by full name of Applicants.
+Only short-listed candidates will be contacted for further screening.
+Those who are interested can only apply through the attached link
+https://nebe-election.org/apply  Within 10 days from this announcement.
+Female candidates are encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/TEA3tPEr88-senior-finance-expert</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:54 UTC</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>NXN8XMleIi</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Head of Student Affairs</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>AMERICAN COLLEGE OF TECHNOLOGY (ACT)</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Conflict Resolution; A genuine passion for education and student development.; Youth development, Sport management, Physical education; Desired Skill; Analytical thinking and problem-solving skills.; analytical, and problem-solving skills; Analytical and problem-solving skills; Analytical: strong problem-solving and analytical abilities.</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>October 17th, 2026</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should submit their CV, cover letter, and copies of academic credentials via website actjobs</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NXN8XMleIi-head-of-student-affairs</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:31:57 UTC</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ZN8rd4UfEs</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Finance Expert</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>NATIONAL ELECTION BOARD OF ETHIOPIA(NEBE)</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP; xperience and knowledge of IFMIS, IFRIS is required</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      INTERESTED APPLICANTS ARE INVITED TO SEND NON-RETURNABLE:
+Application letter that explains why you fit for the post and updated CV, and Three work related referees;
+Application letter &amp; resume should be saved by full name of Applicants.
+Only short-listed candidates will be contacted for further screening.
+Those who are interested can only apply through the attached link
+https://nebe-election.org/apply  Within 10 days from this announcement.
+Female candidates are encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ZN8rd4UfEs-finance-expert</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:00 UTC</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>TU2FZxc1NN</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SENIOR ACCOUNTANT</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>SAM BUSINESS GROUP</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Adaptability; Accounting; Desired Skill; Communication</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>All candidates can apply through telegram or WhatsApp
++251 91 151 6723
+@Eyouel_S</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/TU2FZxc1NN-senior-accountant</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:03 UTC</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>zY3zAQ03Jp</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Electro-Mechanical Technician</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>SCEPTO IMPORT</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Engineering; Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to submit your CV and relevant credentials to:
+SCEPTO IMPORT PLC
+📧 Email: Jobs@scepto.net</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/zY3zAQ03Jp-electro-mechanical-technician</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:06 UTC</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>EXyWvvhJ7Y</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Senior Officer, Core Systems</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>ZEMEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Banking and Insurance</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>Digital security; Communication; Network administration</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates can apply through www.ethiojobs.net. Please attach your updated CV and credentials in PDF format.
+NB; In person applications are not Acceptable.</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/EXyWvvhJ7Y-senior-officer-core-systems</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:09 UTC</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>HfmOr4zC4u</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Administrative Officer</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>ETHIOCHICKEN</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Ability to coordinate multiple tasks and work under pressure.; Ability to work under pressure and meet deadlines; Desired Skill; Documentation; Excellent communication and interpersonal abilities.</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>APPLICATION INSTRUCTIONS 
+Please title your application with the subject line: - "Administrative Officer”
+Only candidates meeting the required qualifications are invited to send their applications (Cover Letter) including a detailed CV to 
+careers@ethiochicken.com 
+Women are highly encouraged to apply</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/HfmOr4zC4u-administrative-officer</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:12 UTC</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>o7oIUnAxb5</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Officer, Network Support (Re-Advert)</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>ZEMEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Banking and Insurance</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Cloud networking and file sharing</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates can apply through www.ethiojobs.net. Please attach your updated CV and credentials in PDF format.
+NB; In person applications are not Acceptable.</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/o7oIUnAxb5-officer-network-support-re-advert</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:15 UTC</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>43dTsNxsou</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>CSO III – Accounts (For Ambo &amp; Nekemte Banking Center)</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>ZEMEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Banking and Insurance</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/43dTsNxsou-cso-iii-accounts-for-ambo-banking-center</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:32:46 UTC</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>UYwV987S7G</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Section Head, ATM Services</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>ZEMEN BANK S.C</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Banking and Insurance</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/UYwV987S7G-section-head-atm-services</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:18 UTC</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>6XUHJDQax4</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Junior Finance Expert II</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>NATIONAL ELECTION BOARD OF ETHIOPIA(NEBE)</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP; xperience and knowledge of IFMIS, IFRIS is required</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      INTERESTED APPLICANTS ARE INVITED TO SEND NON-RETURNABLE:
+Application letter that explains why you fit for the post and updated CV, and Three work related referees;
+Application letter &amp; resume should be saved by full name of Applicants.
+Only short-listed candidates will be contacted for further screening.
+Those who are interested can only apply through the attached link
+https://nebe-election.org/apply  Within 10 days from this announcement.
+Female candidates are encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6XUHJDQax4-junior-finance-expert-ii</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:22 UTC</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>iLsLUngnyh</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Ticketing Officer</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>NOLAWI TOUR &amp; TRAVEL</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Travel and Tourism</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>October 20th, 2026</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>Interested candidates may apply either in person or by email . • In Person: Submit your CV and required documents, along with a non-returnable photocopy, at the office located behind Haya Hulet Debre Damo Hotel, below Arsho Laboratory . • By Email: Send your CV and required documents to theod.visionary@gmail.com For more Information +251977933333/+251968454647</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iLsLUngnyh-ticketing-officer</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:25 UTC</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>tl8JsjEQCH</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Senior, District Digital Officer</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>HIJRA BANK S.C</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Banking and Insurance; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Technological &amp; digital literacy; Digital Finance Transformation</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply within ten (10) consecutive calendar days from the date of this announcement through: https://forms.gle/PbNZrXVogg2ky7sd6
+Perks + Benefits
+Fuel
+Housing
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tl8JsjEQCH-senior-district-digital-officer</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:28 UTC</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>5z4gvaz1aB</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Graduate Internship Program (GIP)</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>EAST AFRICA BOTTLING SHARE COMPANY - COCA COLA</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Graduate and Management...; Human Resource and Recr...; Sales and Marketing; Engineering</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Analytical skills</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates who meet the above requirements are invited to submit their applications through the following link: Application link
+Please note:
+Due to the high volume of applications, we may not be able to respond to all applicants individually.
+Applicants are required to follow our official Telegram channel for updates on their application status, shortlisting results, assessment schedules, and other important recruitment announcements using the link below.
+It is the responsibility of each applicant to regularly check the Telegram channel throughout the recruitment process.
+Official Telegram Channel: CCBAETHIOPIA</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5z4gvaz1aB-graduate-internship-program-gip</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:31 UTC</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>coyWJwZ3KK</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Branch Manager I</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>HIJRA BANK S.C</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Banking and Insurance; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Market research; Excellent customer service; Leadership &amp; Team Management; Financial control &amp; reporting Treasury &amp; cash management</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply within ten (10) consecutive calendar days from the date of this announcement through: https://forms.gle/PbNZrXVogg2ky7sd6
+Perks + Benefits
+Fuel
+Housing
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/coyWJwZ3KK-branch-manager-i</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:34 UTC</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>3FFXWb2EYA</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Personal &amp; General Service Officer I</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>WAGWAGO BUSINESS GROUP</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Teamwork; Problem solving; Communication &amp; Negotiation; • Strong coordination and networking skills; Ability to work under pressure and meet deadlines; Ability to multitask and prioritize work</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>Candidates who fulfill the above requirements can submit their application through the Company ATS link:
+https://erp.wagwagoelectric.com/jobs/personal-general-service-officer-1096</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3FFXWb2EYA-personal-general-service-officer-i</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:40 UTC</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>xpZ3NtZwqA</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Branch Operation Supervisor</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>HIJRA BANK S.C</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Banking and Insurance; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Account management; Excellent customer service; Audit &amp; Compliance Management; Financial control &amp; reporting Treasury &amp; cash management</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply within ten (10) consecutive calendar days from the date of this announcement through: https://forms.gle/PbNZrXVogg2ky7sd6
+Perks + Benefits
+Fuel
+Housing
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xpZ3NtZwqA-branch-operation-supervisor</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:43 UTC</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>COCIxGX0qY</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Senior Customer Service Officer</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>HIJRA BANK S.C</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Banking and Insurance; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Marketing management, Business Management; Excellent customer service; Financial control &amp; reporting Treasury &amp; cash management</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply within ten (10) consecutive calendar days from the date of this announcement through: https://forms.gle/PbNZrXVogg2ky7sd6
+Perks + Benefits
+Fuel
+Housing
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/COCIxGX0qY-senior-customer-service-officer</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:46 UTC</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>9nsNnDhxRZ</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Techinichal and Oprational Manager (Pharmacy sector)</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>ANNAM MARKETING SOLUTION PLC</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Pharmaceutical; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>Interested applicant shall submit CV, copy of academic documents, copy of testimonials, application letters in person at Bole Friendship Building, Office No. 804/3. Phone No.: 0911551022
+Application date: 10 Days as of the vacancy announcement.</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/9nsNnDhxRZ-techinichal-and-oprational-manager-pharmacy-sector</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:49 UTC</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>WpYm5vEGeL</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>FINANCE AND HR ADMINISTRATION OFFICER</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>ZEWDITU GETACHEW FOUNDATION</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>October 29th, 2026</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>Contact Address: Zewditu Getachew Foundation, Kirkos Sub-City, Woreda 01, Bambis, Afework Building, Office -205, tsigegm@zewditugetachew.org, Tel: +252911242095</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/WpYm5vEGeL-finance-and-hr-administration-officer</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:52 UTC</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>xcSAOWy1mE</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Customer Service Officer II</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>HIJRA BANK S.C</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Banking and Insurance; Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Attention to detail; Excellent customer service</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should apply within ten (10) consecutive calendar days from the date of this announcement through:
+Perks + Benefits
+Fuel
+Housing
+Loan
+Medical Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xcSAOWy1mE-customer-service-officer-ii</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -51760,7 +54383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51856,6 +54479,19 @@
       </c>
       <c r="C7" t="n">
         <v>540</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:33:57 UTC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C8" t="n">
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -54383,7 +54383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54491,6 +54491,19 @@
         <v>28</v>
       </c>
       <c r="C8" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:08:06 UTC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
         <v>568</v>
       </c>
     </row>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U569"/>
+  <dimension ref="A1:U627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54371,6 +54371,5512 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>V3Z7MiCE3a</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Treasury &amp; Cash Management Senior Accountant</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>DAYE BENSA BUSINESS PLC</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Accounting Principles (GAAP), IFRS and ERP</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>Application Deadline
+Interested applicants should submit their CV and cover letter within7 working days of this announcement via the under‑mentioned application link: https://forms.gle/aouipNvXHvtwDD5d9</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/V3Z7MiCE3a-treasury-cash-management-senior-accountant</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>4 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:49:38 UTC</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>AlWwrhqCGm</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Senior Office Engineer Head</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>BMK GEOINFORMATIC ENGINEERING</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>12 years</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Adaptability; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants should submit: 
+Application Letter
+Updated CV in English
+Contact details (phone number and email address)
+Copies of academic and professional credentials
+At least three professional references Applications should be sent to:
+Email: bmkengineering19@gmail.com 
+Telegram / WhatsApp: +251 912 163 675 
+Or submit in person at:
+BMK Geoinformatics Engineering PLC Tsion Building, 5th Floor, Office No. 508 Summit, Fiyel Bet Area
+Addis Ababa, Ethiopia 
+Important Notes
+Please clearly indicate the position title "Senior Office Engineer Head" in the subject line of your email application.
+BMK Geoinformatics Engineering PLC is an equal opportunity employer. Female candidates are strongly encouraged to apply.
+Applications will be reviewed on a rolling basis; therefore, early application is encouraged.
+The vacancy may close before the stated deadline once a suitable candidate is identified.
+Only shortlisted candidates will be contacted.
+Integrity screening will form part of the recruitment process.
+Submitted applications will not be returned.
+ Join BMK Geoinformatics Engineering PLC and contribute to the successful delivery of Ethiopia's major infrastructure development projects.</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/AlWwrhqCGm-senior-office-engineer-head</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>14 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:49:48 UTC</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>FMewjPE6rs</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Sales Executive (Jimma)</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>UNITED BEVERAGES SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing; Sales and Marketing; Retail, Wholesale and D...</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Sales; Effective communication and sociability; sales excution &amp; negotiation</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the required qualifications are invited to apply through ethiojobs.</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/FMewjPE6rs-sales-executive-jimma</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>14 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:49:56 UTC</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>foyYBFhgIB</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Tender Manager</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>ZE-EL TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Pharmaceutical; Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: marketing@zeeltradingplc.com
+CC: tadeteferi@zeeltradingplc.com
+Subject Line: Tender Manager
+Note: Only shortlisted candidates will be contacted. Female applicants are encouraged to apply.</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/foyYBFhgIB-tender-manager</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>26 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:50:00 UTC</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>HNuG09lxF0</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Senior Internal Audit Officer</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>MEBA MICROFINANCE INSTITUTION SC</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Management</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Attention to detail; Good communication and interpersonal skills; Internal audit &amp; controls</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Interested applicants should send soft copy of their C.V., scanned copy of testimonials, application letter outlining / specify the position you will apply for on subject line, how their experience and education fit this vacancy in the email address within 5 Consecutive days by the following Link : https://forms.gle/aK8ULRmnRVGEeeen6 or in person at Meba Microfinance Institution Share Company</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/HNuG09lxF0-senior-internal-audit-officer</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>37 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:50:19 UTC</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>1SnlsyebTE</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Senior Occupational Health and Safety</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>GOLD BOTTLED WATER AND NONALCOHOLIC BEVERAGE FACTORY</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Degree in Environmental Science, Environmental Health, or a related field.</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; Problem solving</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Application Process
+Interested applicants who meet the above requirements can submit their application letter, updated CV, and copies of their educational and work experience documents.
+In-Person Application:
+Feda Wak PLC Factory Premises, OR
+Head Office: Meskel Flower Road, Jema'a Building 3rd Floor (next to Dreamliner Hotel).
+Email: hrm@gold-purifiedwater.com
+Telegram: +251 99 422 1843
+Contact Information
+Phone: +251 99 422 1843
+Website: www.gold-purifiedwater.com</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1SnlsyebTE-senior-occupational-health-and-safety</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>39 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:50:37 UTC</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>k5Sq09uvkD</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Senior Chemist</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>GOLD BOTTLED WATER AND NONALCOHOLIC BEVERAGE FACTORY</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Application Process
+Interested applicants who meet the above requirements can submit their application letter, updated CV, and copies of their educational and work experience documents.
+In-Person Application:
+Feda Wak PLC Factory Premises, OR
+Head Office: Meskel Flower Road, Jema'a Building 3rd Floor (next to Dreamliner Hotel).
+Email: hrm@gold-purifiedwater.com
+Telegram: +251 99 422 1843
+Contact Information
+Phone: +251 99 422 1843
+Website: www.gold-purifiedwater.com</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/k5Sq09uvkD-senior-chemist</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>41 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:50:56 UTC</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>DdlkMQnuWc</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Microbiological</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>GOLD BOTTLED WATER AND NONALCOHOLIC BEVERAGE FACTORY</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; problem solving skill</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Application Process
+Interested applicants who meet the above requirements can submit their application letter, updated CV, and copies of their educational and work experience documents.
+In-Person Application:
+Feda Wak PLC Factory Premises, OR
+Head Office: Meskel Flower Road, Jema'a Building 3rd Floor (next to Dreamliner Hotel).
+Email: hrm@gold-purifiedwater.com
+Telegram: +251 99 422 1843
+Contact Information
+Phone: +251 99 422 1843
+Website: www.gold-purifiedwater.com</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DdlkMQnuWc-microbiological</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>43 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:00 UTC</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>soGl6BnuKK</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Junior Shift Chemist (Injection and Polysheet)</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>GOLD BOTTLED WATER AND NONALCOHOLIC BEVERAGE FACTORY</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Engineering</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Degree in Applied Chemistry, Industrial Chemistry, Chemical Engineering, or a related field.</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; problem solving skill</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Application Process
+Interested applicants who meet the above requirements can submit their application letter, updated CV, and copies of their educational and work experience documents.
+In-Person Application:
+Feda Wak PLC Factory Premises, OR
+Head Office: Meskel Flower Road, Jema'a Building 3rd Floor (next to Dreamliner Hotel).
+Email: hrm@gold-purifiedwater.com
+Telegram: +251 99 422 1843
+Contact Information
+Phone: +251 99 422 1843
+Website: www.gold-purifiedwater.com</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/soGl6BnuKK-junior-shift-chemist-injection-and-polysheet</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:11 UTC</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>kF91b8GuS7</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Food Safety and Quality Assurance Supervisor</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>GOLD BOTTLED WATER AND NONALCOHOLIC BEVERAGE FACTORY</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Applied Chemistry, Industrial Chemistry, Chemical Engineering, Applied Biology, or related</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Application Process
+Interested applicants who meet the above requirements can submit their application letter, updated CV, and copies of their educational and work experience documents.
+In-Person Application:
+Feda Wak PLC Factory Premises, OR
+Head Office: Meskel Flower Road, Jema'a Building 3rd Floor (next to Dreamliner Hotel).
+Email: hrm@gold-purifiedwater.com
+Telegram: +251 99 422 1843
+Contact Information
+Phone: +251 99 422 1843
+Website: www.gold-purifiedwater.com</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kF91b8GuS7-food-safety-and-quality-assurance-supervisor</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:17 UTC</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>iRTdRcECNL</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Room Attendant</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>HILTON ADDIS ABABA</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Health Care; Travel and Tourism</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Attention to detail</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Interested &amp; Qualified applicants can send their 3-4 pages application (CV) through email or directly drop CV at the Office of Director of Human Resources, Hilton Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iRTdRcECNL-room-attendant</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:27 UTC</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>8EqX62QjVd</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Waiter/Waitress</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>HILTON ADDIS ABABA</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Travel and Tourism</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Custmer Relationship</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates can send their 3-4 pages CV through email ADDHI_HRD@hilton.com or Drop it to the Office of Director of Human Resources, Hilton Addis Ababa</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/8EqX62QjVd-waiterwaitress</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:30 UTC</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ndbyD5DseR</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Operation Intern</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>MEDICAL TEAMS INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Admin, Secretarial, and...; Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Benishangul Gumuz</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can apply through the following link
+Operations Intern - Assosa  – Fill out form</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ndbyD5DseR-operation-intern</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:33 UTC</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ysjDVRETcJ</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>TRANSSION MANUFACTURING PLC</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Creative Arts</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Content creation; Digital Marketing,; • Creativity; Digital marketing certification</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Send your CV, portfolio, and relevant documents to: transsionmanufacturing@gmail.com Subject line: Digital Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ysjDVRETcJ-digital-marketing-specialist</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:36 UTC</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>shb7TWXCyJ</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Event Organizer</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>PROJECT HOPE THE POEPLE TO PEOPLE HEALTH FOUNDATION INC.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Communications, Media a...</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Part time</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Communication; Fluent in both written and spoken English and Amharic; additional languages are a plus.; Excellent analytical, communication, and leadership skills.</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Interested candidates must review the Terms of Reference above and submit: 
+Technical proposal,
+Financial proposal,
+Valid business license, and
+Taxpayer registration certificate in a sealed envelope to the Project
+All documents must be submitted in a sealed envelope addressed to Project HOPE Ethiopia.
+Applicants are expected to submit their Expression of Interest (EoI), including detailed technical and financial proposals in accordance with the scope of work outlined in the ToR, no later than October 8, 2026, at 5:00 PM to the following address:
+Any questions or requests for clarification regarding these Terms of Reference should be directed to Wegayehu Madebo, Senior Logistics &amp; Operations Coordinator.
+Project HOPE Ethiopia Office Location:
+Google Maps Location: Project HOPE Ethiopia Office on Google Maps
+Submissions should be delivered in person to:
+Project HOPE Ethiopia Country Office
+Minaye PLC Building
+Kirkos Sub-city, Woreda 9,
+10th Floor, Addis Ababa, Ethiopia
+Tel: +251 11 662 2123</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/shb7TWXCyJ-event-organizer</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:39 UTC</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>tCj9RtV4qN</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Construction and Engineering Business Development Associate</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION SOLUTIONS PLC</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Architecture and Constr...; Engineering</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Construction Technology and Management (CoTM)</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 
+Interested applicants who meet the requirements are invited to submit an application letter, CV and supporting credentials within fifteen (15) consecutive days from the date of announcement to consoljobs2026@gmail.com
+or
+Submit in person to Construction Solutions PLC, Located at Meskel Flower to Wollo Sefer Street (Ethio China Road), Martereza Building 3rd Floor, Office Number 301.
+Specify “Construction and Engineering Business Development Associate” in the subject line of your email or application letter.
+For further information, call +251 11 4 70 04 52 during office hours. Please use only the telephone numbers listed in this announcement.
+Construction Solutions plc
+addis ababa, ethiopia</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tCj9RtV4qN-construction-and-engineering-business-development-associate</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:42 UTC</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>jqdbyFcKsq</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Accounting Manager</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>HOLLAND DAIRY P.L.C</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP; Accounts Payable &amp; Receivable</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Click HERE to apply.</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jqdbyFcKsq-accounting-manager</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>6W2fKKIbsw</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>PLANET COLORS IMPORT PLC</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Application Procedure
+Applicants who meet the above requirements are invited to apply in person, starting from the date this announcement is published. Applicants should bring their original educational and work-experience documents along with non-returnable photocopies.
+ Address: Mexico, below Keker Building, around Landmark Hospital, the building where YANGO is located, Ground Floor.
+ Phone: 0944-99-33-00 / 0901-00-33-33</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6W2fKKIbsw-accountant</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:47 UTC</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>usoC9xAvce</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Junior Accountant</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>TEN SENSES PERENNIAL CROPS PRODUCTION P.L.C</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Accounting; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates are invited to submit their CV, educational credentials, and relevant work experience documents to : hrtseplc@gmail.com Within eight (8) consecutive days starting from October 02, 2026.
+Application Period: October 02, 2026 – October 09, 2026
+Application Deadline: October 09, 2026, at 5:00 PM (Applications received after this time will not be accepted)
+Office Address: AA Bole Sub City, Woreda 03, In front of Alem Cinema
+Contact Phone: 0911721295 (Jarso)</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/usoC9xAvce-junior-accountant</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:51 UTC</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>5idmnFUTww</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>PLANET COLORS IMPORT PLC</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>al Qualification:</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>10 years</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>Application Procedure
+Applicants who meet the above requirements are invited to apply in person, starting from the date this announcement is published. Applicants should bring their original educational and work-experience documents along with non-returnable photocopies.
+ Address: Mexico, below Keker Building, around Landmark Hospital, the building where YANGO is located, Ground Floor.
+ Phone: 0944-99-33-00 / 0901-00-33-33</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5idmnFUTww-driver</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:54 UTC</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>GtifjfXShm</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Counseling Program Coordinator</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>HOPE WALKS INC.</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Active listening; • Strong coordination and networking skills; Ability to plan and coordinate; ability to build strong working relationships</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Interested applicants are invited to apply only through this Link by submitting an updated CV and an application letter.
+The organization reserves the right to close this job advert early based on the number of applications received.
+Hope Walks reserves the right to cancel or amend this vacancy. Only shortlisted candidates will be contacted. We are an equal opportunity employer and do not charge any recruitment fees.</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/GtifjfXShm-counseling-program-coordinator</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:57 UTC</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>gq9ENy0nNn</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Lead Researcher - (Governance, Civic Participation, public accountability &amp; Social Cohesion)</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>SOPHOS AFRICA</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.; Developmnet Studies</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants shall submit their non-returnable CV; copy of their credentials for educational qualification, professional work experience, skills training; along with motivation/cover letter to sophosafrica21@gmail.com  with the subject line “application for LEAD RESEARCHER”. Applicants can submit their application in person to SOPHOS AFRICA Ethiopia Office at the Ethiopian Bible Society building, 2nd floor, located in the Bole area, 300 meters from Millennium Hall, below Ambassador Hotel. Only shortlisted applicants will be contacted. For any additional information, please contact us at 0902-45-00-45
+Application Deadline: October 8th / 2026, 5:00 PM</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gq9ENy0nNn-lead-researcher-governance-civic-participation-public-accountability-social-cohesion</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:51:59 UTC</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>s8Os24QkIS</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Utility Operator</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>REPI SOAP &amp; DETERGENT PLC</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Good knowledge of manufacturing systems, ERP tools (SAP), and digital production platforms.; Mechanical Engineering, Electrical Engineering,; Desired Skill; Ability to manage multiple projects and meet deadlines</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>Apply through Ethiojobs - Utility Operator or fill out the form: - https://forms.gle/oeahWGxEzyEFSvQi8or through Email. lidiya.tamirat@et.wilmar-intl.com/ bethlehem.gobena@et.wilmar-intl.com</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/s8Os24QkIS-utility-operator</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:02 UTC</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>KIjdZIAFZP</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Secretary</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>TSEDEY BANK EMPLOYEE ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving; Microsoft Office (Excel, Word, PowerPoint); Highly proficient in Microsoft Office suite.</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>Registration: Register only via Tsedey Bank Employee Association
+‘Female applicants are strongly encouraged to apply’</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/KIjdZIAFZP-secretary</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:05 UTC</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>KDsALXWeaZ</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Junior Occupational Therapist – Pediatric Rehabilitation</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ADDIS GUZO</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>HEALCARE; Clinical Nursing, Public Health, Psychology; Physiotherapy, Occupational Therapy, Rehabilitation Sciences, Community-Based Rehabilitation</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>October 3rd, 2026</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>Applicants should submit:
+CV with photo
+Motivation letter explaining their interest in pediatric rehabilitation and what they hope to learn during the six-month internship at Addis Guzo
+Application Deadline
+Saturday, October 3, 2026
+Early applications are encouraged, as the internship is planned to start as soon as possible.
+How to Apply
+Please submit your CV and motivation letter by email to: martina.oberli@addisguzo.com Subject line: OT Internship 2026 – [Your Name]</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/KDsALXWeaZ-junior-occupational-therapist-pediatric-rehabilitation</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:08 UTC</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>JRTjaZID3a</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Project Management Assistant</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>BOLDKORE CONSULT PLC</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Economics; Agriculture</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Economics, Agricultural Economics, Rural Development, Development Management, Development Studies</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit:
+Updated CV (PDF file only)
+Brief cover letter (PDF file only)
+Applications should be sent to: careers@boldkore.com 
+Email Subject: Application for Project Management Assistant
+Application Deadline: October 12, 2026
+Only shortlisted candidates will be contacted.
+Female candidates are encouraged to apply.</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JRTjaZID3a-project-management-assistant</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:10 UTC</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>fkl0EgyEg4</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Plant Manager-TDT</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Engineering; Architecture and Constr...; Management</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Quality control; Preventive Maintenance; Production Management; Leadership &amp; Team Management; Heavy Equipment Maintenance; Plant Operations Management; Crusher Plant Operations; Crushing &amp; Screening; Quarry Operations; Health, Safety &amp; Environment; Desired Skill; Environmental Management; Laboratory testing and equipment troubleshooting.; Excellent computer skills, including knowledge of Microsoft Office applications such as Outlook,; Aggregate Production</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates should submit their updated CV to deborah.eshetu@ethiojobs.net. With a subject line of Plant Manager-TDT.</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fkl0EgyEg4-plant-manager-tdt</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:13 UTC</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>gqWUYPeBtP</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Skills Development and Employment Linkage Specialist</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION SOLUTIONS PLC</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Education; Social Sciences and Com...; Management</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>	</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>management, economics, marketing communication, management, social studies,</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the relevant requirements are invited to submit an application letter, detailed CV and supporting academic, training, COC (where applicable) and work-experience credentials within fifteen (15) consecutive days from the date of announcement to consoljobs2026@gmail.com
+oR 
+Submit in person to Construction Solutions PLC, Located at Meskel Flower to Wollo Sefer Street (Ethio China Road), Martereza Building 3rd Floor, Office Number 301.
+Specify “Skills Development and Employment Linkage Specialist” in the subject line of your email or application letter. Shortlisted applicants will be contacted for interview.
+For further information, call +251 11 4 70 04 52 during office hours. Please use only the telephone numbers listed in this announcement.
+Construction Solutions plc
+Addis Ababa, Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gqWUYPeBtP-skills-development-and-employment-linkage-specialist</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:16 UTC</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>qjytnXXKgf</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Regional Trade Marketing Supervisor</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>KOMARI BEVERAGE</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Dire Dawa</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Sales; Data Analysis &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Those who meet the above requirements can submit their CV to the following link 
+Kindly note that only short-listed candidates will be contacted. Link
+Female applicants are highly encouraged to apply  </t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qjytnXXKgf-regional-trade-marketing-supervisor</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:19 UTC</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>9F161GDi8f</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Front Desk and Business Support Coordinator</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION SOLUTIONS PLC</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Management; Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Management, Business Administration, Marketing</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the requirements are invited to submit an application letter, CV and supporting credentials within fifteen (15) consecutive days from the date of announcement to consoljobs2026@gmail.com
+or
+Submit in person to Construction Solutions PLC, located at Meskel Flower to Wollo Sefer Street (Ethio China Road), Martereza Building 3rd Floor, Office Number 301.
+Specify “Front Desk and Business Support Coordinator” in the subject line of your email or application letter.
+For further information, call +251 11 4 70 04 52 during office hours. Please use only the telephone numbers listed in this announcement. 
+Construction Solutions plc
+addis ababa, ethiopia</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/9F161GDi8f-front-desk-and-business-support-coordinator</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:22 UTC</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>ZJkkgQRObC</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Messenger</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION SOLUTIONS PLC</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Customer Service</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>	</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Communication, coordination, networking and facilitation skills</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the requirements are invited to submit an application letter, CV and supporting credentials within fifteen (15) consecutive days from the date of announcement to consoljobs2026@gmail.com
+or 
+Submit in person to Construction Solutions PLC, located at Meskel Flower to Wollo Sefer Street (Ethio China Road), Martereza Building 3rd Floor, Office Number 301.
+Specify “Messenger” in the subject line of your email or application letter.
+For further information, call +251 11 4 70 04 52 during office hours. Please use only the telephone numbers listed in this announcement. 
+Construction Solutions plc
+addis ababa, ethiopia
+ </t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ZJkkgQRObC-messenger</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:25 UTC</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>oWWcmBO7IU</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Business Development and Consultancy Specialist</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION SOLUTIONS PLC</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Business Development</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>	</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Business Administration,; Business Administration, Management, Entrepreneurship,</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the requirements are invited to submit an application letter, CV and supporting credentials within fifteen (15) consecutive days from the date of announcement to consoljobs2026@gmail.com
+or 
+Submit in person to Construction Solutions PLC, located at Meskel Flower to Wollo Sefer Street (Ethio China Road), Martereza Building 3rd Floor, Office Number 301.
+Specify “Business Development and Consultancy Specialist” in the subject line of your email or application letter.
+For further information, call +251 11 4 70 04 52 during office hours. Please use only the telephone numbers listed in this announcement. 
+Construction Solutions plc
+addis ababa, ethiopia</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oWWcmBO7IU-business-development-and-consultancy-specialist</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:27 UTC</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>j3zrcAozuK</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Head, Hatchery Section</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ELFORA AGRO INDUSTRY PLC</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Veterinary Services; Agriculture</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Communication; Problem solving</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements should Apply through Ethio jobs Elfora online application plate form within 7 working days from the date of this vacancy announcement.
+OR
+Interested applicant who meets the above requirements should submit their application with relevant documents and CV within 7 working days from the date of this vacancy announcement to ELFORA Main Office, Admin &amp; Human Resource Dep’t at 4th floor (You can apply at your current Operation)
+N.B the Company has the right to cancel the post advertised.
+N.B Selected candidates must have their educational credentials authenticated by the issuing institution and submit the verification within six months.
+Address: Tele Phone 251-16732069/67</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/j3zrcAozuK-head-hatchery-section</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:30 UTC</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>IvU1T0HKOA</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Veterinarian</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>ELFORA AGRO INDUSTRY PLC</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Veterinary Services; Agriculture</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Communication; Problem solving</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements should Apply through Ethio jobs Elfora online application plate form within 7 working days from the date of this vacancy announcement.
+OR
+Interested applicant who meets the above requirements should submit their application with relevant documents and CV within 7 working days from the date of this vacancy announcement to ELFORA Main Office, Admin &amp; Human Resource Dep’t at 4th floor (You can apply at your current Operation)
+N.B the Company has the right to cancel the post advertised.
+N.B Selected candidates must have their educational credentials authenticated by the issuing institution and submit the verification within six months.
+Address: Tele Phone 251-16732069/67</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/IvU1T0HKOA-veterinarian</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:33 UTC</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>GTDjgzCaA4</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Cost, Budget &amp; Financial Analysis Accountant</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ELFORA AGRO INDUSTRY PLC</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Communication; Problem solving</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements should Apply through Ethio jobs Elfora online application plate form within 7 working days from the date of this vacancy announcement.
+OR
+Interested applicant who meets the above requirements should submit their application with relevant documents and CV within 7 working days from the date of this vacancy announcement to ELFORA Main Office, Admin &amp; Human Resource Dep’t at 4th floor (You can apply at your current Operation)
+N.B the Company has the right to cancel the post advertised.
+N.B Selected candidates must have their educational credentials authenticated by the issuing institution and submit the verification within six months.
+Address: Tele Phone 251-16732069/67</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/GTDjgzCaA4-cost-budget-financial-analysis-accountant</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:36 UTC</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>ieL2USTo59</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Food &amp; Beverage Manager</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>THE FIRST GROUP HOSPITALITY</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>al Qualification and</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; Problem solving</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>How to Apply
+Interested and qualified candidates who meet the above requirements are invited to register and apply through Ethio Jobs starting from September 27, 2026.
+Only candidates who meet the stated minimum requirements will be considered for further assessment and selection.
+Human Resources Department
+JIMMA PALACE HOTEL PLC
+Jimma, Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ieL2USTo59-food-beverage-manager</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:39 UTC</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>DLpB1JDDi0</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Call Center Agent</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>AFROREACH TECHNOLOGY PLC</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Negotiation; Analytical skills</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>How to Apply: Send us your CV, education credentials, and an example of something you’ve built or worked on.
+eshetu@afromessage.com</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DLpB1JDDi0-call-center-agent</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:42 UTC</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>tvZRCLnQ2Q</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Reservation Agent</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tvZRCLnQ2Q-reservation-agent</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:45 UTC</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>D3ZGsyIHd4</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Chief Steward</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/D3ZGsyIHd4-chief-steward</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:48 UTC</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>tyy1Q2yFYB</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Midwifery Nurse – MHNT</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>SAVE THE CHILDREN</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Scrub Nurse (OR Nurse)</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>Please attach a copy of your CV and cover letter with your application and include details of your current remuneration and salary expectations. 
+Use the below link to apply:  
+https://hcri.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1
+We need to keep children safe so our selection process, which includes rigorous background checks, reflects our commitment to the protection of children from abuse.
+All employees are expected to carry out their duties in accordance with our global anti-harassment policy. Qualified female candidates are highly encouraged to apply</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tyy1Q2yFYB-midwifery-nurse-mhnt</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:52:51 UTC</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>1VrjwZdZea</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/1VrjwZdZea-bartender</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:03 UTC</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>fNBFIDjXOD</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fNBFIDjXOD-sales-executive</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:15 UTC</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>24jg6OPcab</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/24jg6OPcab-sous-chef</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:22 UTC</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2CrgHHlntV</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Roving Restoring Family Links Field officer</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN RED CROSS SOCIETY- OROMIA BRANCH</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Management; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>Interested applicants should send a non-returnable complete application letter together with copies of other testimonial within Ten days of this vacancy announcement to the following address through postal service.
+No need of telephone communication except short listed.
+How To Apply interested applicants who met the minimum requirements should send and apply   
+ERCS Oromia Region
+P. Box. No 122637</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/2CrgHHlntV-roving-restoring-family-links-field-officer</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:30 UTC</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>VI6TTECX1Q</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Housekeeping Attendant</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/VI6TTECX1Q-housekeeping-attendant</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:37 UTC</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>RRy6x449t5</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Senior Procurement Officer</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>PRIME PACKAGING PLC</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Purchasing and Procurem...; Retail, Wholesale and D...; Warehouse, Supply Chain...</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Attention to detail; Quality control; Inventory software; Inventory management; Desired Skill; Adaptability; Team work; Chartered Accountant/CIA; risk management certifications</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>HOW TO APPLY
+Interested candidates should submit a CV and cover letter outlining relevant experience to talent@primepackaging.net
+Please indicate "Senior Procurement Officer" in the subject line.
+Prime Packaging PLC is an equal opportunity employer.
+Perks + Benefits
+Medical Allowance
+Transport Allowance</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/RRy6x449t5-senior-procurement-officer</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:52 UTC</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>69rv8SPPJZ</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/69rv8SPPJZ-technician</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:05 UTC</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>tSbgXnKURo</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Ethiopian Traditional Food Cook</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tSbgXnKURo-ethiopian-traditional-food-cook</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:17 UTC</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>p00rMBOjtY</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/p00rMBOjtY-driver</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:27 UTC</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>7yvPCyjxBJ</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Front Office Team Member/Receptionist</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/7yvPCyjxBJ-front-office-team-memberreceptionist</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:42 UTC</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>urOIIwEWGn</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Health &amp; Nutrition Officer – MHNT</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>SAVE THE CHILDREN</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>nutrition</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>Please attach a copy of your CV and cover letter with your application and include details of your current remuneration and salary expectations. 
+Use the below link to apply:  
+https://hcri.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1
+We need to keep children safe so our selection process, which includes rigorous background checks, reflects our commitment to the protection of children from abuse.
+All employees are expected to carry out their duties in accordance with our global anti-harassment policy.
+Qualified female candidates are highly encouraged to apply</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/urOIIwEWGn-health-nutrition-officer-mhnt</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:57 UTC</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>xVfSWxBi1n</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Chef De Partie</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/xVfSWxBi1n-chef-de-partie</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:15 UTC</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>WWhRHxZx1f</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Waiter/Waitress</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/WWhRHxZx1f-waiterwaitress</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:23 UTC</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>YIV4FGebp9</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Training Manager</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>RADISSON BLU</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Hotel and Hospitality; Business and Administra...; Management</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>Application Instruction: 
+Only candidates meeting the required qualifications are invited to send their applications including a detailed CV and related supporting documents by email through HR.addisababa@radissonblu.com
+Application Dead Line: - October 05th, 2026
+Note:- Only short listed candidates will be contacted</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/YIV4FGebp9-training-manager</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:32 UTC</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>6xPY59vYqL</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Human Resource Officer</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>PRIME PACKAGING PLC</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Data analysis; Basic knowledge of user interface communication; Training and Development; Recruitment and Selection; HRIS and Technology; Desired Skill; Conflict Resolution; Adaptability</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>HOW TO APPLY
+Interested candidates should submit a CV and cover letter outlining relevant experience to talent@primepackaging.net.
+Please indicate "Human Resource Officer" in the subject line.
+Prime Packaging PLC is an equal opportunity employer.
+Perks + Benefits
+Medical Allowance
+Transport Allowance</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6xPY59vYqL-human-resource-officer</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:36 UTC</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>41FbZcxFcI</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Credit Control Officer</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>DIGAF &amp; MICRO-CREDIT PROVIDER SC</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Economics; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Communication &amp; Negotiation; Ability to handle high volumes of alerts with structured prioritization; Ability to multitask and prioritize effectively.; Ability to work under pressure and meet deadlines</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants are invited to submit their CV and application letter via EthioJobs or send directly to: hr.admin@digafcredit.com Please mention the position title in the email subject line</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/41FbZcxFcI-credit-control-officer</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:41 UTC</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>vjbdxzOISS</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Bid Cancellation Announcement</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>THREE ROOTS INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; More Jobs by Three Roots International; Bid Cancellation Announcement; Office; October 30th, 2026; Search Similar Jobs in Bid Cancellation Announcement; Jobs in Logistics, Transport and Supply Chain; Jobs for Mid Level(3-5 years); Jobs in Oromia; FAQ; How to register; How to apply for a job?; How do I reset my password?; How do I edit my CV on Ethiojobs?</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vjbdxzOISS-bid-cancellation-announcement</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:47 UTC</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Ii5M1L3jqH</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Senior Project Officer II – Livestock Value Chain Development</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN AGRICULTURAL TRANSFORMATION AGENCY (ATA)</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Benishangul Gumuz</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Strong organizational and time-management skills.; Organization &amp; Time Management</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>APPLICATION INSTRUCTIONS
+We invite all candidates meeting the required qualifications to submit (i) a cover letter and (ii) a CV (maximum 5 pages) to https://apply.ati.gov.et. It is mandatory to mention the position title in both the subject line of your cover letter and the Outlook email subject line. Please DO NOT submit scans of certificates with your application.
+Women are highly encouraged to apply
+NB. Only short-listed candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Ii5M1L3jqH-senior-project-officer-ii-livestock-value-chain-development</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:50 UTC</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -54383,7 +59889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54505,6 +60011,19 @@
       </c>
       <c r="C9" t="n">
         <v>568</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:55:52 UTC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>58</v>
+      </c>
+      <c r="C10" t="n">
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/ethiojobs_tracker.xlsx
+++ b/ethiojobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U627"/>
+  <dimension ref="A1:U723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -59877,6 +59877,9039 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>3b8PitSCAh</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>MEAL Officer – ECHO-RISE Project</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>GENEVA GLOBAL</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Economics; Management; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>Interested applicants can submit their application letter and updated CV to ethiojobs</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3b8PitSCAh-meal-officer-echo-rise-project</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>8 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:14 UTC</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>O9lat04KkE</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Content Creator &amp; Copywriter</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>TADESSE DESTA IMPORT EXPORT</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Communications, Media a...</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>All interested and qualified applicants who fulfill the above requirement can submit or send their application letter with CV and non- returnable copies of academic &amp; work experience testimonial documents within seven consecutive working days from the first publication date via Email address hr@tadessedesta.com by mentioning the Job Title on the subject line of your email or apply in person, at its head office, Afework building, 9th floor.
+For More Information: - Tel +251115226002</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/O9lat04KkE-content-creator-copywriter</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>26 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:17 UTC</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>vYeqM7UYjg</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Autoclave Machine Operator</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>TEKLEHAIMANOT GENERAL HOSPITAL</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Machine operating; Desired Skill; Machine operating</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>October 14th, 2026</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates are invited to submit their CV (PDF format) along with copies of relevant documents to the HR Department.
+Location: Office No. 502, 5th Floor, Somale Tera
+Telephone: +251 11 1 56 04 92
+Mobile: +251 9 96 – 97 98 38
+Email: hr@teklehaimanothospital.com
+Perks + Benefits
+Medical Allowance</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vYeqM7UYjg-autoclave-machine-operator</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>27 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:20 UTC</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Xd08K4GlQJ</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Trade Marketing Assistance</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>ETHIO-ASIAN INDUSTRIES S.C</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business and Administra...; Social Sciences and Com...; Management</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>B2B Marketing; Communication; Data analysis and market trend interpretation; Commercial insight and market analysis; Desired Skill; Data analysis and market trend interpretation; Commercial insight and market analysis; Digital marketing &amp; E-Commerce.</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates can apply through email andarge.k@ethioasian.com</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Xd08K4GlQJ-trade-marketing-manager</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>27 minutes ago by</t>
+        </is>
+      </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:23 UTC</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>agF556RIhe</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Sales Representative (Outdoor Sales)</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>BREAKTHROUGH TRADING S.C</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>customer communication and understanding capabilities; Good customer service, communications,</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>ethiojobs.net
+hr@alphagenuine.com</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/agF556RIhe-sales-representative-outdoor-sales</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>an hour ago by</t>
+        </is>
+      </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:26 UTC</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>5qolvtKeRO</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>National Solar Power Design and Installation Expert (Freelance Consultant)</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>GITEC IGIP GMBH</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>consultancy</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>Please send your applications comprising CV, degree certificate(s), other certificates, reference letters, illustrative track record of similar works, and fee expectations by way of email communication and email attachments to Ms Helen Bayu, BioDiv Office Manager, c/o Ethiopian Wildlife Conservation Authority helen.bayu@projectgic.com
+Receipt of all applications will be confirmed in writing. Note, only up to five selected experts will be invited for an interview.</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5qolvtKeRO-national-solar-power-design-and-installation-expert-freelance-consultant</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>P4olm4gOGz</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Engineering; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/P4olm4gOGz-electrician</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:32 UTC</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>9CY3P3grST</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Finished Goods Store Keeper</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Management; Economics; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/9CY3P3grST-finished-goods-store-keeper</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:35 UTC</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Q5sFIFUjbW</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Main Chef (Foods Preparation ) Supervisor</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...; Hotel and Hospitality</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Q5sFIFUjbW-main-chef-foods-preparation-supervisor</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:38 UTC</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>D1HAIs7TZW</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Senior Food Assurance &amp; Quality Control</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Environment and Natural...; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/D1HAIs7TZW-senior-food-assurance-quality-control</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:41 UTC</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>BFdA6ItfZl</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Junior Sales &amp; Marketing Officer (Social Medea Manager)</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/BFdA6ItfZl-junior-sales-marketing-officer-social-medea-manager</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:44 UTC</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>LgiRqs0SHV</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Senior Sales &amp; Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/LgiRqs0SHV-senior-sales-marketing-officer</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:47 UTC</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>aX0EvHUi7p</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Environment and Natural...; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/aX0EvHUi7p-production-supervisor</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:50 UTC</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>evJHelqnAQ</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Senior Cost Accountant</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/evJHelqnAQ-senior-cost-accountant</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:53 UTC</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>P2XegviNZs</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Internal Control Officer</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>MAJET FOODS TRADING ONE MEMBER PLC</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Applicants Who Fulfill the above mentioned criteria could submit detailed curriculum vitea   along with supporting documents / credentials accompanied by Email Address majetfoodstrading@gmail.com within 10 Working days.
+Note :-  Only Short Listed Candidates will be contacted and People who live in Akaki Kality  Worda  7 and nearby areas are given priority</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/P2XegviNZs-internal-control-officer</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>2 hours ago by</t>
+        </is>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:56 UTC</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>fPEStHZuS8</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Monitoring, Evalaution and Learning (MEL) Specialist</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Business Development; Economics</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>• Development-oriented; • Creativity; Ability to deliver quality work within deadlines; Ability to manage multiple projects and meet deadlines; Desired Skill; Monitoring, Evaluation &amp; Learning</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Attached Link: Monitoring Evaluation and Learning Specialist(Jijiga)
+                                    Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS:12 October 2026/ 12:00 PM</t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fPEStHZuS8-monitoring-evalaution-and-learning-mel-specialist</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:36:59 UTC</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>ziYzfeaAZ4</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Senior - Reward and Benefits Officer (Re-Adverts)</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ETHSWITCH S.C.</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Business Development</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>al Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Qualified candidates are invited to submit their application with non-returnable CV, educational qualifications and work experience to hr@ethswitch.com, stating the title of the position clearly on the subject line. Qualified female applicants are highly encouraged.
+*Please be aware that it is mandatory to attach your credentials (educational qualifications and work experience) along with your CV. Submitting only your CV is not sufficient.
+*Please be advised that all applicants’ Educational Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ziYzfeaAZ4-senior-reward-and-benefits-officer-re-adverts</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:06 UTC</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>dGtwJ6J2AA</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Junior Accountant</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ETHIOPIAN CATHOLIC CHURCH DAUGHTERS OF CHARITY DEVELOPMENT COORDINATING OFFICE</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Accounting; Analytical thinking and problem-solving skills.; Microsoft Office (Excel, Word, PowerPoint)</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Female applicants are encouraged to apply and only shortlisted candidates will be contacted.
+HOW TO APPLY
+Interested and qualified candidates are required to complete and submit their profile through the following link:
+https://ee.kobotoolbox.org/single/QJO1N0CE
+In addition to completing the form using the link, applicants are required to submit the following documents:
+Updated CV
+Copies of relevant educational and professional supporting documents
+The CV and supporting documents should be sent by email to tesfaenye@gmail.com or docdcoethiopia@gmail.com no later than October 10, 2026.
+Submission of the link application form is a mandatory requirement. Applications submitted without completing the link form will not be considered.
+Only shortlisted candidates will be contacted for the subsequent stages of the recruitment process.</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/dGtwJ6J2AA-junior-accountant</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:10 UTC</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>RN02Whrvg0</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Consultancy Services for Digitally Enabled, Women-Led Food Delivery Aggregation (Micro Franchise) Model Re-Bid Number (027/26/SNV)</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>SNV</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Senior Executive(C Level)</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Team work</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Submission Guidelines and Application Submission Date: 
+Both the Technical and Financial proposals should be sent separately, only through ettenders@snv.org
+Therefore, SNV will expect two submission emails that are for the technical and financial offers. Both email subjects must contain the name of the assignment and proposal type. If the consultants miss the submission procedure, they will be automatically rejected.
+Title of the specific assignment: Digitally enabled, Women-led Food Delivery aggregation (Micro franchise) Model
+SNV will be rejected for proposals submitted without indicating the title of the assignment “Digitally enabled, Women-led Food Delivery aggregation (Micro franchise) Model” in the subject of the email.
+For any clarification or questions, use the following email: Samson Gizaw sgizaw@snv.org
+Proposals must be received by SNV no later than October 15, 2026, 17:00 PM, (5:00 PM), close of business.
+SNV Ethiopia, Roosevelt St. on the way from AU to Mexico Square, telephone: +251 (0)11 616 6232, P.O. Box 40675, Addis Ababa | Ethiopia
+SNV Ethiopia reserves the right to accept or reject any or all bids.</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/RN02Whrvg0-consultancy-services-for-digitally-enabled-women-led-food-delivery-aggregation-micro-franchise-model-re-bid-number-02726snv</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:13 UTC</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>I5GdiKaIXh</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>ETHSWITCH S.C.</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>al Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Analytical: strong problem-solving and analytical abilities.; Computer Science, Software Engineering, Information Technology</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Qualified candidates are invited to submit their application with non-returnable CV, educational qualifications and work experience to hr@ethswitch.com, stating the title of the position clearly on the subject line. Qualified female applicants are highly encouraged.
+Please be aware that it is mandatory to attach your credentials (educational qualifications and work experience) along with your CV. Submitting only your CV is not sufficient.
+Please be advised that all applicants’ Educational Credentials will be verified with the respective higher institutions.</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/I5GdiKaIXh-senior-software-engineer</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:16 UTC</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Ir1Yc7uJcD</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>MARVELOUS REAL ESTATE S.C</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Engineering; Architecture and Constr...; Management</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>10 years</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Excellent communication, negotiation, and leadership skills.; Effective problem-solving and decision-making skills,; Structural Engineering, Civil Engineering, Construction Management; Strong project management and organizational skills. Excellent communication,</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Application Deadline and Submission
+Interested candidates are invited to submit their educational and work experience documents within five (5) consecutive working days from the date of this announcement.
+Applications may be submitted by email to marvelousrealest4@gmail.com or in person at the Human Resources Management Office of Marvelous Real Estate, located in the Haile Garment intersection area.
+Tel: +251 980-242-526 / +251 980-272-829</t>
+        </is>
+      </c>
+      <c r="Q648" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Ir1Yc7uJcD-project-manager</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:19 UTC</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>sSDKuTxwDP</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Senior Site Engineer</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>MARVELOUS REAL ESTATE S.C</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>AutoCAD or Civil 3D; Excellent communication and interpersonal abilities.; Basic understanding of BIM concepts and civil engineering software; Strong time management skills</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Interested candidates are invited to submit their educational and work experience documents within five (5) consecutive working days from the date of this announcement.
+Applications may be submitted by Email to marvelousrealest4@gmail.com or in person at the Human Resources Management Office of Marvelous Real Estate, located in the Haile Garment intersection area.
+Tel: +251 980-242-526 / +251 980-272-829</t>
+        </is>
+      </c>
+      <c r="Q649" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/sSDKuTxwDP-senior-site-engineer</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>3 hours ago by</t>
+        </is>
+      </c>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:22 UTC</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>gxwDRVW7oh</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Coffee Industry Professional</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>GREAT COFFEE ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates who meet the requirements for the above positions are invited to apply by submitting their updated CV and proof of relevant work experience.
+Job Location: Coffee sites located in Jimma Zone, Setema Woreda
+Application Location: Addis Ababa
+Phone: 0946 778 899
+Email: greatcoffeehrdep@gmail.com
+Important Notice
+Candidates with practical and relevant work experience in the coffee industry will be given priority during the recruitment process.</t>
+        </is>
+      </c>
+      <c r="Q650" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gxwDRVW7oh-coffee-industry-professional</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:24 UTC</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>3qaBdfkjkL</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Coffee Site Cashier / Site Finance Officer</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>GREAT COFFEE ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates who meet the requirements for the above positions are invited to apply by submitting their updated CV and proof of relevant work experience.
+Job Location: Coffee sites located in Jimma Zone, Setema Woreda
+Application Location: Addis Ababa
+Phone: 0946 778 899
+Email: greatcoffeehrdep@gmail.com
+Important Notice
+Candidates with practical and relevant work experience in the coffee industry will be given priority during the recruitment process.</t>
+        </is>
+      </c>
+      <c r="Q651" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3qaBdfkjkL-coffee-site-cashier-site-finance-officer</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:27 UTC</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>6XhjwWYgdT</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Coffee Kilo Supervisor / Coffee Weighing &amp; Store/Warehouse Supervisor</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>GREAT COFFEE ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>October 5th, 2026</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>Qualified and interested candidates who meet the requirements for the above positions are invited to apply by submitting their updated CV and proof of relevant work experience.
+Job Location: Coffee sites located in Jimma Zone, Setema Woreda
+Application Location: Addis Ababa
+Phone: 0946 778 899
+Email: greatcoffeehrdep@gmail.com
+Important Notice
+Candidates with practical and relevant work experience in the coffee industry will be given priority during the recruitment process.</t>
+        </is>
+      </c>
+      <c r="Q652" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6XhjwWYgdT-coffee-kilo-supervisor-coffee-weighing-storewarehouse-supervisor</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:30 UTC</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>R1bIRyI3VR</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Advisor, AYSRH Programs</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>POPULATION SERVICES INTERNATIONAL (PSI)</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>Knowledge of Ethiopia's health, population, and NGO regulatory context.; Public Health, Nursing, Midwifery, Health Officer,; Reproductive Health, Nursing, Gender, WASH, education</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>October 11th, 2026</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Are you intrigued? Apply!
+By following our 3 steps application process:
+Fill out the application form using the following link: Online Application Form. It will only take 5 to 10 minutes.
+Send your CV and application letter to recruitment@psiet.org and clearly mark “Advisor-SRH Programs” in the subject line.
+Check your email and make sure you receive an automatic response acknowledging receipt of your application that means your application was successful. If you don’t receive the automatic response, check again your subject line and if needed, re-submit your CV and application letter with the correct subject.
+PSI is an Equal Opportunity Employer and encourages applications from qualified individuals regardless of race, religion, national origin, sexual orientation or disability.
+ </t>
+        </is>
+      </c>
+      <c r="Q653" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/R1bIRyI3VR-advisor-aysrh-programs</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:34 UTC</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>pU84dIV1d1</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Purchase Executive- Contract</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Purchasing and Procurem...; Warehouse, Supply Chain...</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>Procurement; ERP / SAP / Oracle procurement modules; Demonstrated experience in contract negotiation, litigation, and regulatory compliance; Contract Coordination; commercial contracts; Good understanding of contract management; Procurement and Supply Chain Management,; Strong knowledge of Ethiopian Labor Law, Commercial Law, and Contract Law.</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>Interested and qualified candidates should submit their updated CV to deborah.eshetu@ethiojobs.net. With a subject line of Purchase Executive- Contracts.</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/pU84dIV1d1-purchase-executive-contract</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:37 UTC</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>hvpQbnsugG</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Clinical Officer</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>PHARO FOUNDATION</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Benishangul Gumuz</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>health; Health Officer; Clinical Nursing, Public Health, Psychology</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Apply Now
+Use the link below to submit your application:
+👉 [Click Here]
+What to Submit:
+Your resume
+A short application letter
+No need to include educational credentials or work certificates at this stage.
+We’re excited to hear from you—keep it simple and let your experience speak for itself!
+Why Apply Now?
+Rolling Review Process: We review applications as they come in, so don’t wait! Apply early to ensure your application is considered.
+Only Shortlisted Candidates: Only those selected for further consideration will be contacted. Thank you for your understanding.
+We can't wait to learn more about you and how you can contribute to our mission of fostering a self-reliant Africa. Join us and help make an impact!</t>
+        </is>
+      </c>
+      <c r="Q655" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/hvpQbnsugG-clinical-officer</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>4 hours ago by</t>
+        </is>
+      </c>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:40 UTC</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>4ARhMjlLpM</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Logistics Assistant</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Logistics, Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 08 October 2026/ 4:00 PM
+Logistics Assistant BSP | Yabelo</t>
+        </is>
+      </c>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/4ARhMjlLpM-logistics-assistant</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:43 UTC</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>5lHT7qZsAX</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Logistics Assistant</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Human Resource Management, Management, Business Administration,; Logistics, Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 08 October 2026/ 4:00 PM
+Logistics Assistant BSP | Bahir Dar</t>
+        </is>
+      </c>
+      <c r="Q657" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5lHT7qZsAX-logistics-assistant</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:46 UTC</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>KWm3X3zhpd</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Secretary</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>REALITY SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Problem solving; Microsoft Office (Excel, Word, PowerPoint)</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Submit your application via email to: realityhrgs@gmail.com
+Or apply in person at:
+Reality Plaza Building, 6th Floor
+HRGS Department Office
+Near Bole Brass, close to You Go City Church
+Addis Ababa
+For Further Information
+Telephone: 011 666 3336 / 0950 253 532</t>
+        </is>
+      </c>
+      <c r="Q658" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/KWm3X3zhpd-secretary</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:50 UTC</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Ad2DZrkcYy</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>MR Care Companions</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>MERRYRIGHT TRADING PLC,</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Part time</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Patience; Patient care and assistance; Strong empathy and survivor-centered attitude</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can apply through this email address merryright.et@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Ad2DZrkcYy-mr-care-companions</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:53 UTC</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Rfw66Kooyn</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Area Coordinator</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Strong leadership and people management skills.; trong leadership and people-management skills Excellent planning, budgeting, and reporting skills</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 08 October 2026/ 4:00 PM
+Area Coordinator BSP | Bahir Dar</t>
+        </is>
+      </c>
+      <c r="Q660" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Rfw66Kooyn-area-coordinator</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:56 UTC</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>IWdmMiGxnD</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Finished Good Storekeeper</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>HOLLAND DAIRY P.L.C</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Attention to detail</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Interested and Qualified candidates can send their updated resume to hr@holland-dairy.com</t>
+        </is>
+      </c>
+      <c r="Q661" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/IWdmMiGxnD-finished-good-storekeeper</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:37:59 UTC</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>tDpwHytxVv</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Production Manager</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>DUGDA CONSTRUCTION PLC</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>al Qualification</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>9 Year</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Construction, Civil Engineering, or related field.Technical trainin</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Interested applicants can apply within 05 Consecutive working days from September-30, 2026, by the following
+address: - Get As international Building, 3rd Floor, near to Ministry of Innovation &amp; Technology or Wudasse
+Diagnostic Center, Tel +251011156-41-18/0111-56-64-42/0929918362/0919403688 or Using Our email address; E-Mail hr@dugdacon.com Telegram : @dugdacons</t>
+        </is>
+      </c>
+      <c r="Q662" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tDpwHytxVv-production-manager</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:02 UTC</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>lAESCRKMFF</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Supply Chain and Procurement Officer</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>SEGON-MARILL INTERNATIONAL MOVERS PLC</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Social Sciences and Com...; Logistics, Transport an...</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Qualified Candidates Apply Through this link is https://forms.gle/GhSZxiVXPdDKxKSP6</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lAESCRKMFF-supply-chain-and-procurement-officer</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:05 UTC</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>969wn0oAkS</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Area Coordinator</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Development and Project...</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Account management; Strong leadership and people management skills.; • Strong coordination and networking skills</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 08 October 2026/ 4:00 PM
+Area Coordinator BSP | Yabelo</t>
+        </is>
+      </c>
+      <c r="Q664" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/969wn0oAkS-area-coordinator</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:08 UTC</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>tXshfADe9k</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Anesthesia Professional</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>DREAM LIYANA HEALTHCARE PLC</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above qualifications are encouraged to submit within 7 consecutive days a resume/CV, educational, Document and cover letter to https://t.me/dream_admin_hr please include “Anesthesia Professional" in the subject line.
+Deadline for Application: (Oct, 07/2026 G.C)
+At Dream Orthopedics, Trauma and Spine Center we are committed to providing exceptional patient care and fostering a supportive and collaborative work environment. Join our team and make a difference in the lives of our patients and community.
+Tell:  +251-115-50-00-26</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tXshfADe9k-anesthesia-professional</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:11 UTC</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>GVwTZYvVg1</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Finance And Subaward Specialist</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>MERCY CORPS ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Donor Reporting; Fundraising &amp; donor engagement; Compliance Management,</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All qualified individuals are invited to apply for the advertised position. All applications, including a CV, three references, and all applicable official papers, must be sent electronically.
+Only candidates that are short-listed will be acknowledged and called for interviews.
+“Mercy Corps is an equal opportunity employer promoting gender, equity and    diversity. Qualified female and young candidates are strongly encouraged to apply. We are committed to empower women and youth.”
+DEADLINE FOR ALL APPLICATIONS: 08 October 2026/ 4:00 PM
+Finance And Subaward Specialist BSP | Addis Ababa  </t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/GVwTZYvVg1-finance-and-subaward-specialist</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:15 UTC</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>GzMuAa6jxh</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>DREAM LIYANA HEALTHCARE PLC</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above qualifications are encouraged to submit within 7 consecutive days a resume/CV, educational, Document and cover letter to https://t.me/dream_admin_hr please include “Nurse" in the subject line.
+Deadline for Application: (Oct, 07/2026 G.C)
+At Dream Orthopedics, Trauma and Spine Center we are committed to providing exceptional patient care and fostering a supportive and collaborative work environment. Join our team and make a difference in the lives of our patients and community.
+Tell:  +251-115-50-00-26</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/GzMuAa6jxh-nurse</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:22 UTC</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>kDhnGUWsbe</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Head Nurse</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>DREAM LIYANA HEALTHCARE PLC</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above qualifications are encouraged to submit within 7 consecutive days a resume/CV, educational, Document and cover letter to https://t.me/dream_admin_hr please include “Head Nurse" in the subject line.
+Deadline for Application: (Oct, 07/2026 G.C)
+At Dream Orthopedics, Trauma and Spine Center we are committed to providing exceptional patient care and fostering a supportive and collaborative work environment. Join our team and make a difference in the lives of our patients and community.
+Tell:  +251-115-50-00-26</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kDhnGUWsbe-head-nurse</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:30 UTC</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>DWjV6eeLW1</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Quality Officer</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>DREAM LIYANA HEALTHCARE PLC</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Health Care; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above qualifications are encouraged to submit within 7 consecutive days a resume/CV, educational, Document and cover letter to https://t.me/dream_admin_hr please include “Quality Officer" in the subject line.
+Deadline for Application: (Oct, 07/2026 G.C)
+At Dream Orthopedics, Trauma and Spine Center we are committed to providing exceptional patient care and fostering a supportive and collaborative work environment. Join our team and make a difference in the lives of our patients and community.
+Tell:  +251-115-50-00-26</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/DWjV6eeLW1-quality-office</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:37 UTC</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>5ejuLVpwET</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Senior Accountant</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>DREAM LIYANA HEALTHCARE PLC</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Interested candidates who meet the above qualifications are encouraged to submit within 7 consecutive days a resume/CV, educational, Document and cover letter to https://t.me/dream_admin_hr please include “Senior Account Application" in the subject line.
+Deadline for Application: (Oct, 07/2026 G.C)
+At Dream Orthopedics, Trauma and Spine Center we are committed to providing exceptional patient care and fostering a supportive and collaborative work environment. Join our team and make a difference in the lives of our patients and community.
+Tell:  +251-115-50-00-26</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/5ejuLVpwET-senior-accountant</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>5 hours ago by</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:40 UTC</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>P4wR3ONZJm</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Senior Financial Accountant</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>ETHIO-NIPPON TECHNICAL SC</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>Applicants are expected to submit/mail their applications letter, updated CV, and necessary documents via vacancies@ethio-nippon.com or 
+in person Human Resource and Administration Department located in front of the African Union, Mexico across Genet Hotel on or before October 7, 2026.
+Don’t forget to mention the position you’re applying for in the subject line of your email.
+Tel. 011-5-51-46-61</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/P4wR3ONZJm-senior-financial-accountant</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:43 UTC</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>13XEVM8D5z</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Financing Appraisal Officer II (Re-advertised)</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Banking and Insurance; Social Sciences and Com...; Accounting and Finance; Economics</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements can submit their application letter, updated CV, educational and work experience credentials in PDF format by clearly stating the position &amp; location that you are applying for through the application link within 7 days from the date of announcement.
+Application Link: https://forms.gle/Muqmf2ZrZCqzGuw58
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/13XEVM8D5z-financing-appraisal-officer-ii-re-advertised</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:46 UTC</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>onDjnNiuIh</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Banking Business Officer I</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Banking and Insurance; Social Sciences and Com...; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements can submit their application letter, updated CV, educational and work experience credentials in PDF format by clearly stating the position &amp; location that you are applying for through the application link within 7 days from the date of announcement.
+Application Link: https://forms.gle/Muqmf2ZrZCqzGuw58
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/onDjnNiuIh-banking-business-officer-i</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:50 UTC</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>SQYhMmOFXK</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Senior Banking Business Officer</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Banking and Insurance; Social Sciences and Com...; Management</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements can submit their application letter, updated CV, educational and work experience credentials in PDF format by clearly stating the position &amp; location that you are applying for through the application link within 7 days from the date of announcement.
+Application Link: https://forms.gle/Muqmf2ZrZCqzGuw58
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/SQYhMmOFXK-senior-banking-business-officer</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:53 UTC</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>fcA6SahXnF</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Branch Manager I</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>ZAMZAM BANK</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...; Banking and Insurance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>October 7th, 2026</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Interested applicants who meet the above requirements can submit their application letter, updated CV, educational and work experience credentials in PDF format by clearly stating the position &amp; location that you are applying for through the application link within 7 days from the date of announcement.
+Application Link: https://forms.gle/Muqmf2ZrZCqzGuw58
+IMPORTANT NOTICE
+Only candidates who meet the stated minimum requirements will be considered.
+Only shortlisted candidates will be contacted.
+ZamZam Bank reserves the right to use appropriate assessment methods as part of the recruitment process.
+Applicants are expected to provide accurate and verifiable information.
+A NAME WITH HERITAGE.  A BANK WITH PURPOSE.  A CAREER WITH IMPACT.
+JOIN US.
+PROFESSIONAL GROWTH + LEGITIMATE EARNING + PURPOSE + IMPACT
+ZAMZAM BANK S.C. | The First Full-Fledged Interest-Free Bank in Ethiopia</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fcA6SahXnF-branch-manager-i</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:56 UTC</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>CPBR9D52ew</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Deputy CEO</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>ZIAD MOHAMMED IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Management; Business and Administra...; Economics</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Adaptability; Leadership &amp; Team Management</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>October 31st, 2026</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employees who want to work with our company and who meet the requirements Can apply With the company email address zmiemanagingdirector@gmail.com within 5 working days after the announcement of this vacant position applicants Must mention the position that applying for in their application.
+ </t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/CPBR9D52ew-deputy-ceo</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:38:59 UTC</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>bJqihDltlA</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Officer — Medical Supplies &amp; Devices</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>ZE-EL TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Pharmaceutical; Engineering; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV, and copies of credentials within 10 working days of this announcement to:
+Email: tadeteferi@zeeltradingplc.com
+CC: ytebekaw@gmail.com
+Subject Line: Medical Supplies &amp; Devices
+Note: Only shortlisted candidates will be contacted. Female applicants are encouraged to apply.</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/bJqihDltlA-marketing-sales-officer-medical-supplies-devices</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>6 hours ago by</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:02 UTC</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>vQYGThVlkO</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Technical Lead – Agriculture and Rural Development</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>FRONTIERI CONSULT P.L.C</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Agriculture; Research and Developmen...; Development and Project...; Consultancy and Trainin...</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Research and Data analysis; Quantitative and Qualitative research; Research &amp; Analytical Skills; impact measurement, research methodology, and rural development relevant</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>Interested candidates are invited to complete the online application form using the link below and submit their application on or before October 10, 2026.
+Apply here: https://forms.gle/M48nwG23imxc2DoY8
+Application Deadline: October 10, 2026
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/vQYGThVlkO-technical-lead-agriculture-and-rural-development</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>9 hours ago by</t>
+        </is>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:05 UTC</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>cRw4ZQUpHr</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Consultancy Service – Quality management expert for organic soybean production and processing</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>GIZ SEQUA GGMBH</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Agriculture; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>Please send us a cover letter, your CV in the EuropeAid format, relevant resumes, and your daily fee expectation in Ethiopian birr (ETB) If you apply as a firm, please send your company profile and financial proposal. Please provide a clear description of achievements created for consulted companies in the past.
+The CV template can be downloaded from our website.
+Please send us your application by no later than October 15, 2026, to vacancies.pss@sequa.de with the subject line ‘ETH-1148 Consultation Service- Nutritionist Expert’.</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/cRw4ZQUpHr-consultancy-service-quality-management-expert-for-organic-soybean-production-and-processing</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:08 UTC</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>hTsvH1hIt1</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Consultancy Service – Quality management expert for organic soybean production and processing</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>GIZ SEQUA GGMBH</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Consultancy and Trainin...; Agriculture; Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>consulting</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Please send us a cover letter, your CV in the EuropeAid format, relevant resumes, and your daily fee expectation in ETB[LL2] . If you apply as a firm, please send your company profile and financial proposal. Please provide a clear description of achievements created for consulted companies in the past.
+The CV template can be downloaded from our website.
+Please send us your application by no later than October 15, 2026, to vacancies.pss@sequa.de with the subject line ‘ETH-1148 Consultation Service- Quality Management/Organic Farming Expert’.</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/hTsvH1hIt1-consultancy-service-quality-management-expert-for-organic-soybean-production-and-processing</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>16 hours ago by</t>
+        </is>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:11 UTC</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>SqvV4wAUUo</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>SECRETARY Ethio Korebta Real Estate SC</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Admin, Secretarial, and...; Customer Service</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Understanding of Clerical and Secretarial Principles; Secretarial Science, Management, Business Administratio</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can apply by attaching their cv</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/SqvV4wAUUo-secretary-ethio-korebta-real-estate-sc</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:15 UTC</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>6PiUcTaKQX</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>PART-TIME ACCOUNTANT Ethio Korebta Real Estate SC</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>TALENT SEARCH - ETHIOJOBS</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Business and Administra...</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Part time</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>Accounting; Accounting Principles (GAAP), IFRS and ERP; Advanced Accounting Knowledge; Construction cost accounting; ERP / Accounting Software</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants can apply by attaching your updated CV</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/6PiUcTaKQX-part-time-accountant-ethio-korebta-real-estate-sc</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:19 UTC</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>iQplF5TpUt</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Account Executive - Paid Internship</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>NATIONAL MARKETERS PLC</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Customer Service; IT, Computer Science an...</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Presentation; Customer Relationship Management (CRM); Sales reporting; sales excution &amp; negotiation; Good communication skills in teamwork, team mobilizations, and partnership management; Excellent communication and interpersonal skills.; Good customer service, communications,</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Interested applicants are encouraged to apply through the application form below:
+[ https://forms.gle/cdqv2bhvjGXamV3BA]
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/iQplF5TpUt-account-executive-paid-internship</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:22 UTC</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>e92KZVAK3m</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Ethiopia Senior Tree Expansion Research Officer (Fixed-Term)</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>ONE ACRE FUND</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Research and Data analysis</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Apply here: https://grnh.se/y8fgebkk1us</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/e92KZVAK3m-ethiopia-senior-tree-expansion-research-officer-fixed-term</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:25 UTC</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>QpbW7W2WvP</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Graduate Trainee for Production Controller</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>HUDI TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Management; Engineering; Accounting and Finance; Economics</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>No prior work experience required.</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTICE
+Women are highly encouraged for all positions!
+Applicants who meet the stated requirements may apply within ten (10) consecutive working days from the date of publication of this vacancy announcement.
+Applicants should prepare complete copies of their cv, educational and work-experience documents in PDF format and submit their applications through one of the following options:
+Application Options
+In Person Visit the company at: Meri Family Mall, 3rd Floor, Addis Ababa
+By Email: Taema2277@gmail.com
+By Telegram @BusiManager
+Google forms: https://forms.gle/cUwcVgvoQouueJru9
+For More Information
+Please call: 0988111000 / 0913098181</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/QpbW7W2WvP-graduate-trainee-for-production-controller</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:28 UTC</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>aOFK1Un9Bu</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Cost Accountant</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>HUDI TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Economics</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTICE
+Women are highly encouraged for all positions!
+Applicants who meet the stated requirements may apply within ten (10) consecutive working days from the date of publication of this vacancy announcement.
+Applicants should prepare complete copies of their cv, educational and work-experience documents in PDF format and submit their applications through one of the following options:
+Application Options
+In Person Visit the company at: Meri Family Mall, 3rd Floor, Addis Ababa
+By Email: Taema2277@gmail.com
+By Telegram @BusiManager
+Google forms: https://forms.gle/cUwcVgvoQouueJru9
+For More Information
+Please call: 0988111000 / 0913098181</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/aOFK1Un9Bu-cost-accountant</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>21 hours ago by</t>
+        </is>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:31 UTC</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>JxLENhxf9L</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>HUDI TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTICE
+Women are highly encouraged for all positions!
+Applicants who meet the stated requirements may apply within ten (10) consecutive working days from the date of publication of this vacancy announcement.
+Applicants should prepare complete copies of their cv, educational and work-experience documents in PDF format and submit their applications through one of the following options:
+Application Options
+In Person Visit the company at: Meri Family Mall, 3rd Floor, Addis Ababa
+By Email: Taema2277@gmail.com
+By Telegram @BusiManager
+Google forms: https://forms.gle/cUwcVgvoQouueJru9
+For More Information
+Please call: 0988111000 / 0913098181</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JxLENhxf9L-electrician</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:34 UTC</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>kMY1hByf4z</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>HUDI TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Engineering; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTICE
+Women are highly encouraged for all positions!
+Applicants who meet the stated requirements may apply within ten (10) consecutive working days from the date of publication of this vacancy announcement.
+Applicants should prepare complete copies of their cv, educational and work-experience documents in PDF format and submit their applications through one of the following options:
+Application Options
+In Person Visit the company at: Meri Family Mall, 3rd Floor, Addis Ababa
+By Email: Taema2277@gmail.com
+By Telegram @BusiManager
+Google forms: https://forms.gle/cUwcVgvoQouueJru9
+For More Information
+Please call: 0988111000 / 0913098181</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kMY1hByf4z-mechanic</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:37 UTC</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>JlpFBuVSmk</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Female Business Development Manager Re Advertised</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>BROTHERS TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Business and Administra...; Sales and Marketing; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Executive(VP, Director)</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>8-12 years</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Microsoft Office Pack: Word, Excel, Access, Publisher, Outlook, Powerpoint; Communication; Attention to detail; Problem solving</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>How to Apply: Interested candidates are invited to submit their applications through brotherstradingplc0@gmail.com /info@brotherstradingplc.com/ Within 10 working days from the date of this announcement.</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/JlpFBuVSmk-female-business-development-manager-re-advertised</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:39 UTC</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>NY6GW7D4EU</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Outdoor Sales Representative</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>ETHAL ALUMINUM MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Sales; Communication</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Application Deadline
+Interested applicants who meet the above requirements are invited to send their CV and supporting documents within 7 working days from the date of this announcement.
+Email: mamaru.tadele@ethal.net</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/NY6GW7D4EU-outdoor-sales-representative</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:42 UTC</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>jWQmMFSzlD</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Store Department Head</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>HUDI TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...; Warehouse, Supply Chain...; Purchasing and Procurem...</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>October 10th, 2026</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTICE
+Women are highly encouraged for all positions!
+Applicants who meet the stated requirements may apply within ten (10) consecutive working days from the date of publication of this vacancy announcement.
+Applicants should prepare complete copies of their cv, educational and work-experience documents in PDF format and submit their applications through one of the following options:
+Application Options
+1. In Person Visit the company at: Meri Family Mall, 3rd Floor, Addis Ababa
+2. By Email: Taema2277@gmail.com
+3. By Telegram @BusiManager
+4. Google forms: https://forms.gle/cUwcVgvoQouueJru9
+For More Information
+Please call: 0988111000 / 0913098181</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/jWQmMFSzlD-store-department-head</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:45 UTC</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>fUJO7SeFVP</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>E-Commerce Officer</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>ETHAL ALUMINUM MANUFACTURING</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Sales and Marketing; Business and Administra...; IT, Computer Science an...; Management</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; problem solving skill</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>How to Apply
+Interested and qualified applicants are invited to send their CV, cover letter, and supporting credentials to:
+Email: mamaru.tadele@ethal.net
+Application Deadline: Within 7 (seven) working days from the date of this announcement.
+Ethal Aluminium Manufacturing PLC is an equal opportunity employer and encourages qualified candidates to apply.</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fUJO7SeFVP-e-commerce-officer</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:48 UTC</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>EWe8d57mlI</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Junior Electrician</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>THREE Y FLEXIBLE PACKAGING PLC</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Entry Level (Fresh Graduate)</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>- Basic electrical troubleshooting skills; - Good teamwork and communication skills; - Willingness to learn and develop technical skills; -Ability to follow instructions and safety procedures; -Ability to work under supervision and in a manufacturing environment; Requirement Skill; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>All applicant should send their application to threey.packaging@yahoo.com</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/EWe8d57mlI-junior-electrician</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:51 UTC</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>kHm1YIsFtt</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Quality Inspector</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>THREE Y FLEXIBLE PACKAGING PLC</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Quality Assurance; Engineering</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Good analytical and problem-solving skills; Good communication and teamwork skills; Computer literacy, including Microsoft Office; Requirement Skill; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>All applicant should send their application to threey.packaging@yahoo.com</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/kHm1YIsFtt-quality-assurance-manager</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:55 UTC</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>XZsoDBr5jA</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Marketing Administration &amp; Reporting Assistant</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>OVID REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Basic financial and business analysis; • Strong coordination and networking skills; Ability to work under pressure and meet deadlines</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>October 15th, 2026</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants are required to submit the following documents:
+A Cover Letter
+An Updated Curriculum Vitae (CV)
+Clear scanned copies of supporting documents
+All documents must be enclosed into a single PDF file.  
+Please ensure that the title of the position is clearly written in the Subject Line of your application email as: Subject: Marketing Administration &amp; Reporting Assistant
+Applicants may apply through Ethiojobs or via the company email: hr@ovid-realestates.com</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XZsoDBr5jA-marketing-administration-reporting-assistant</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:39:59 UTC</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Wu2lvULCIi</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Manager-Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>NFA BUSINESS PLC</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Logistics, Transport an...; Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Microsoft Office Pack: Word, Excel, Access, Publisher, Outlook, Powerpoint; Communication; Attention to detail; Problem solving; Accounting</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Interested applicants who meet the above requirements are invited to submit their CV along with copies of educational and work experience documents with   Email: hrnfa63@gmail.com within 7 (seven) working days.
+Address:  A.A Bole Bulbula, Mariam Mazoriya, next to Huda Tower, 1st Floor, HR Department Tel. 0116292398 /0983932996
+ </t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Wu2lvULCIi-finance-manager</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:01 UTC</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>fokd0DuFry</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Quality Assurance Manager</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>THREE Y FLEXIBLE PACKAGING PLC</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Engineering; Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>-Good analytical, leadership, communication, and problem-solving skills; -Good computer skills, including MS Office; -ISO 9001 Lead Auditor certification is an advantage; -Leadership and team management; -Problem-solving and root-cause analysis; -Data analysis and reporting; Requirement Skill; Communication; Attention to detail</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>All applicant should send their application to threey.packaging@yahoo.com</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fokd0DuFry-quality-assurance-manager</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:05 UTC</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>wQ43Klx0Of</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Parts &amp; Service Sales Representative (PSSR) – Mining (Readvertised)</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>RIES ENGINEERING SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Engineering</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Communication; Attention to detail; Analytical thinking and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested and qualified applicants are invited to submit their application letter, updated CV, and relevant supporting documents within 5 (five) working days from the date of this announcement via:
+Email: jobs@riesethiopia.com
+Applicants should clearly indicate “Parts &amp; Service Sales Representative (PSSR) – Mining” in the subject line of their application. Only shortlisted candidates will be contacted.
+ </t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/wQ43Klx0Of-parts-service-sales-representative-pssr-mining-readvertised</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:08 UTC</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>3nsSPLyP7W</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>FP &amp; A Analyst</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>HOLLAND DAIRY P.L.C</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>Excellent analytical, problem-solving, and reporting skills.</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>October 12th, 2026</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Click HERE to apply.</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/3nsSPLyP7W-fp-a-analyst</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:11 UTC</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>awqBWYvCVC</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES OFFICER, NOC</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>UNITED NATIONS ECONOMIC COMMISSION FOR AFRICA (UNECA)</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Human Resource Management, Management, Business Administration,; Desired Skill; Data Analysis &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>To get information on how to apply, please visit careers.un.org
+Job openings advertised on the Careers Portal will be removed at 11:59 p.m. (New York time) on the deadline date.</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/awqBWYvCVC-human-resources-officer-noc</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:14 UTC</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>x5W010t1bC</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Public Information Officer (Publishing Officer), NOC</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>UNITED NATIONS ECONOMIC COMMISSION FOR AFRICA (UNECA)</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>Graphic design</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>October 16th, 2026</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>To get information on how to apply, please visit careers.un.org
+Job openings advertised on the Careers Portal will be removed at 11:59 p.m. (New York time) on the deadline date.</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/x5W010t1bC-public-information-officer-publishing-officer-noc</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:17 UTC</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>y1vb82PmN6</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Branch Loan Officer</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>DIGAF &amp; MICRO-CREDIT PROVIDER SC</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Banking and Insurance; Business and Administra...; Economics</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>Ability to work under pressure and meet targets; Communication &amp; Negotiation</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Interested candidates should send their resumes along with a cover letter to our HR department at hr.admin@digafcredit.com no later than 10 days. Please specify the position and location you are applying for in the subject line of your email.</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/y1vb82PmN6-branch-laon-officer</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:20 UTC</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>gcWcykSWir</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Monitoring, Evaluation, Learning and Accountability (MEAL) Officer</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>GENEVA GLOBAL</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Economics; Management; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Three (3) to five (5) years of progressively responsible exp</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>October 6th, 2026</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Interested applicants can submit their application letter and updated CV to ethiojobs</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gcWcykSWir-monitoring-evaluation-learning-and-accountability-meal-officer</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:23 UTC</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>PmvwRlIqno</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Jr. Coffee Cupper</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>BNT INDUSTRY AND TRADING PLC</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>Horticulture/plant science</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>October 25th, 2026</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Candidates should apply by sending an updated Curriculum Vitae and application letter including scanned educational documents.
+If you believe that your credentials meet the outlined profile, we invite you to apply by emailing your application to bnt.hr@bntbeverages.com
+Ensure to attach all requested documents for consideration.
+Clearly indicate the title of the position being applied for as follows “Application for Jr. Coffee Cupper Position” in the title of your Email. Only short-listed applicants will be contacted.
+You can also apply in person at Mexico road, Mezid Plaza behind Addis Ababa University School of Commerce 8th floor office number 808 
+For more information call with 011 5581168/011 558 0002
+CALLING TO OTHER NUMBERS IS PROHIBITED</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/PmvwRlIqno-jr-coffee-cupper</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:26 UTC</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>H2VX1tFIRk</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Qualitative Research Facilitator/Interviewer</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>PROJECT HOPE THE POEPLE TO PEOPLE HEALTH FOUNDATION INC.</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Health Care; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Quantitative and Qualitative research</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>October 4th, 2026</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Interested applicants should submit the following:
+Cover letter clearly indicating the preferred region/city administration, relevant language proficiency, and summary of relevant qualitative research experience.
+Updated CV outlining academic qualifications, relevant professional experience and three references.
+Academic credentials and testimonials/certificates demonstrating experience in at least five previous qualitative health or health-related research projects/studies.
+Contact details for at least three professional references who can provide testimonials regarding the applicant’s qualitative research experience and performance.
+Interested applicants can send their CV and cover letter through ethiojobs ONLY no later than October 4, 2026, at 5:00 PM.
+Qualified female applicants are highly encouraged to apply.
+Due to the large number of inquiries, we receive, only candidates who have met the required experience &amp; qualifications for this position will be considered. No phone calls please.
+However, since we are active around the world in the field of public health, we may wish to retain your CV in our database for other/future opportunities, unless you direct us otherwise.
+Thank you very much for your interest in Project HOPE</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/H2VX1tFIRk-qualitative-research-facilitatorinterviewer</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:29 UTC</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>oizHoo2apk</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Project Accountant</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>IMAGINE1DAY INTERNATIONAL ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>South West Ethiopia People's Region</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>Communication; • Creativity; • Strong coordination and networking skills; Ability to manage many requests at once.</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Click here to Apply </t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oizHoo2apk-project-accountant</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:32 UTC</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Jxq0e4A0Y0</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Finance Assistant</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>GENEVA GLOBAL</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Accounting and Finance; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>Time management; Microsoft Office Pack: Word, Excel, Access, Publisher, Outlook, PowerPoint; Communication; Attention to detail; Financial reporting; Accounting; Requirement Skill; Communication</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Interested applicants can submit their application letter and updated CV to ethiojobs</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/Jxq0e4A0Y0-finance-assistant</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:35 UTC</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>VcO4C4ZflL</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>HR and Admin Officer</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>SHOBOLE ELECTROMECHANICAL</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>Human Resource Management, Management, Business Administration,</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>October 20th, 2026</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Interested and qualified applicants are invited to submit their CV and cover letter via email their applications directly to hayat@shobole.com with the subject line "Application for HR and Admin Officer Position".</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/VcO4C4ZflL-hr-and-admin-officer</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:38 UTC</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>ecq3Qvqzh1</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>HR Officer</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>JEMAL SEID ADEM IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Human Resource and Recr...</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Human Resource Management, Management, Business Administration,</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: Jemalseidexporter35@gemail.com</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/ecq3Qvqzh1-hr-officer</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:41 UTC</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>UIqfquUZ0c</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Request for Proposal (RFP)</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL FERTILIZER DEVELOPMENT CENTER (IFDC)</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Social Sciences and Com...</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>Excellent interpersonal and communication skills</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>October 8th, 2026</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposal Submission:
+Technical proposals shall be submitted electronically in both Word and PDF formats to procurementethiopia@ifdc.org: and financial proposals shall be submitted in hardcopy only in sealed envelope to IFDC office in Addis Ababa, located near St. Urael Church Axum building, 2nd floor. The deadline for submission of both technical and financial proposals shall be October 8, 2026. It is the responsibility of the bidder to ensure that proposals are submitted in the method and format within the stated period as prescribed herein. Late submissions will not be considered under any circumstances.
+ Evaluation Methodology:
+All proposals will be evaluated based on technical capacity, relevant experience in software development and digital platforms, methodology, implementation approach, personnel qualifications, and financial competitiveness. IFDC reserves the right to accept or reject any or all proposals, wholly or partially, without incurring any obligation to provide justification for its decision.
+ </t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/UIqfquUZ0c-request-for-proposal-rfp</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:50 UTC</t>
+        </is>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>u37VCoo5pQ</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Quality Control and Assurance Supervisor</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>JEMAL SEID ADEM IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>quality-management systems and laboratory testing methods</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: Jemalseidexporter35@gemail.com</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/u37VCoo5pQ-quality-control-and-assurance-supervisor</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:54 UTC</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>gv5sbvjF5C</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Account Responsible</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>HUAWEI TECHNOLOGIES ETHIOPIA PLC</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>IT, Computer Science an...; Accounting and Finance; Telecommunications</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>Excellent communication, interpersonal and organizational skills; Commercial insight and market analysis</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>All interested and qualified candidates are invited to submit their applications through www.ethiojobs.net Applicants are kindly requested to specify the position they are applying for.
+If you do not meet the required educational and professional qualifications, or if your degree is in an unrelated field, we kindly ask that you refrain from submitting an application.</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gv5sbvjF5C-account-responsible</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:40:57 UTC</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>fjLMv2LzJp</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Electrical and Automation Technician</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>JEMAL SEID ADEM IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>planning and asset-management skills</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: Jemalseidexporter35@gemail.com</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/fjLMv2LzJp-electrical-and-automation-technician</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:00 UTC</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>tiIjFGtA4K</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Assistant Store head</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>HILINA ENRICHED FOODS PLC</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>FMCG and Manufacturing; Warehouse, Supply Chain...</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Ability to manage many requests at once.; Desired Skill; • Creativity</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>We invite all candidates meeting the required qualifications to send (i) a cover letter, (ii) CV (maximum 3 pages) via ethiojobs Or apply in person to the following address: 
+Hilina Enriched Foods PLC
+T: +251 116 679041/42
+F: +251 116 675019
+P.O.Box: 1648 CODE 1110
+Legetafo
+Oromia, Ethiopia
+Email: jobs@hilinafoodseth.com
+Web: www.hilinafoodesth.com
+Perks + Benefits
+Medical Allowance
+Meal
+Transport Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/tiIjFGtA4K-assistant-store-head</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:03 UTC</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>qpUrQvP29O</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Engineering Supervisor</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>JEMAL SEID ADEM IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>planning and asset-management skills</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: Jemalseidexporter35@gemail.com</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/qpUrQvP29O-engineering-supervisor</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:06 UTC</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>XrGyp0Um1g</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>JEMAL SEID ADEM IMPORT AND EXPORT</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>Chemical Engineering, Food Engineering, Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>October 13th, 2026</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>Qualified applicants should send an application letter, CV and copies of credentials within 10 working days of this announcement to:
+Email: Jemalseidexporter35@gemail.com</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/XrGyp0Um1g-production-supervisor</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:09 UTC</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>aEyN9kpK9W</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Store controller</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>HILINA ENRICHED FOODS PLC</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Warehouse, Supply Chain...; FMCG and Manufacturing</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Ability to work under pressure and meet deadlines; Desired Skill; analytical, and problem-solving skills</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>October 9th, 2026</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>We invite all candidates meeting the required qualifications to send (i) a cover letter, (ii) CV (maximum 3 pages) via ethiojobs Or apply in person to the following address: 
+Hilina Enriched Foods PLC
+T: +251 116 679041/42
+F: +251 116 675019
+P.O.Box: 1648 CODE 1110
+Legetafo
+Oromia, Ethiopia
+Email: jobs@hilinafoodseth.com
+Web: www.hilinafoodesth.com
+Perks + Benefits
+Medical Allowance
+Meal
+Transport Allowance
+Training Opportunities</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/aEyN9kpK9W-store-controller</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:11 UTC</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>j4Bief2YkP</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Architects (Intermediate Level)</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>AT-CON ENGINEERING &amp; ARCHITECTURE CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>Architecture.; Civil Engineering, Construction Management, Architecture, Disaster Risk Managemen</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the minimum requirements are invited to submit the following documents via email to atconvacancy@gmail.com or in person to our office:
+CV highlighting relevant educational background and work experience.
+Cover letter addressing qualifications and interest in the position.
+Copies of educational credentials and work experience testimonials.
+Incomplete CVs will not be considered.
+Location:
+Head Office – Setiti Mall Building, 2nd Floor
+Located around C.M.C area, in front of Michael Church, Addis Ababa
+For further inquiries, please contact us at Tel: 0116479490
+Application Deadline: October 30, 2026 G.C
+ </t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/j4Bief2YkP-architects-intermediate-level</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:14 UTC</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>HgAq98OQID</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Senior Architects (Senior)</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>AT-CON ENGINEERING &amp; ARCHITECTURE CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Senior(5-8 years)</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Architecture.; Civil Engineering, Construction Management, Architecture, Disaster Risk Managemen</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the minimum requirements are invited to submit the following documents via email to atconvacancy@gmail.com or in person to our office:
+CV highlighting relevant educational background and work experience.
+Cover letter addressing qualifications and interest in the position.
+Copies of educational credentials and work experience testimonials.
+Incomplete CVs will not be considered.
+Location:
+Head Office – Setiti Mall Building, 2nd Floor
+Located around C.M.C area, in front of Michael Church, Addis Ababa
+For further inquiries, please contact us at Tel: 0116479490
+Application Deadline: October 30, 2026 G.C
+ </t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/HgAq98OQID-senior-architects-senior</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:17 UTC</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>MOJwogI5s5</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Structural Engineer (Junior)</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>AT-CON ENGINEERING &amp; ARCHITECTURE CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Structural Engineering, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the minimum requirements are invited to submit the following documents via email to atconvacancy@gmail.com or in person to our office:
+CV highlighting relevant educational background and work experience.
+Cover letter addressing qualifications and interest in the position.
+Copies of educational credentials and work experience testimonials.
+Incomplete CVs will not be considered.
+Location:
+Head Office – Setiti Mall Building, 2nd Floor
+Located around C.M.C area, in front of Michael Church, Addis Ababa
+For further inquiries, please contact us at Tel: 0116479490
+Application Deadline: October 30, 2026 G.C
+ </t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/MOJwogI5s5-structural-engineer-junior</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:20 UTC</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>gtoQkozhm4</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Electrical Engineer (Junior)</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>AT-CON ENGINEERING &amp; ARCHITECTURE CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Electrical and Computer Engineering</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the minimum requirements are invited to submit the following documents via email to atconvacancy@gmail.com or in person to our office:
+CV highlighting relevant educational background and work experience.
+Cover letter addressing qualifications and interest in the position.
+Copies of educational credentials and work experience testimonials.
+Incomplete CVs will not be considered.
+Location:
+Head Office – Setiti Mall Building, 2nd Floor
+Located around C.M.C area, in front of Michael Church, Addis Ababa
+For further inquiries, please contact us at Tel: 0116479490
+Application Deadline: October 30, 2026 G.C
+ </t>
+        </is>
+      </c>
+      <c r="Q721" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/gtoQkozhm4-electrical-engineer-junior</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T721" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:24 UTC</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>lMWUXcAUr1</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Sales Engineer</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>RIES ENGINEERING SHARE COMPANY</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Natural Sciences; Engineering</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Mid Level(3-5 years)</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>Decision-making skills; Communication; Attention to detail; Analytical and problem-solving skills</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>Interested applicants are required to submit their application letter, updated CV, and supporting documents within 7 (five) working days from the date of this announcement via:
+Email: jobs@riesethiopia.com
+Only shortlisted candidates will be contacted.</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/lMWUXcAUr1-sales-engineer</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T722" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:27 UTC</t>
+        </is>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>oqhjGWKG86</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Sanitary Engineer (Junior)</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>AT-CON ENGINEERING &amp; ARCHITECTURE CONSULTANCY PLC</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Junior Level(1-3 years)</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Sanitary Engineering, Water Supply and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>October 30th, 2026</t>
+        </is>
+      </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interested applicants who meet the minimum requirements are invited to submit the following documents via email to atconvacancy@gmail.com or in person to our office:
+CV highlighting relevant educational background and work experience.
+Cover letter addressing qualifications and interest in the position.
+Copies of educational credentials and work experience testimonials.
+Incomplete CVs will not be considered.
+Location:
+Head Office – Setiti Mall Building, 2nd Floor
+Located around C.M.C area, in front of Michael Church, Addis Ababa
+For further inquiries, please contact us at Tel: 0116479490
+Application Deadline: October 30, 2026 G.C
+ </t>
+        </is>
+      </c>
+      <c r="Q723" t="inlineStr">
+        <is>
+          <t>https://ethiojobs.net/job/oqhjGWKG86-sanitary-engineer-junior</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>EthioJobs</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>a day ago by</t>
+        </is>
+      </c>
+      <c r="T723" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:30 UTC</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>dom_render</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -59889,7 +68922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60024,6 +69057,19 @@
       </c>
       <c r="C10" t="n">
         <v>626</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:41:31 UTC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
